--- a/BaoCao-KiemThu-CareerCompass.xlsx
+++ b/BaoCao-KiemThu-CareerCompass.xlsx
@@ -9,18 +9,21 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00. Tong quan" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01. BVA + Equiv Partition" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03. Decision Table (PhanA)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03b. Decision Table Token" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04. State Transition (PhanA)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04b. State Transition Token" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B1_CFG_va_Basis_Path" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B2_Coverage_Levels" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B3_Truoc_va_Sau" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B4_Coverage_Per_Class" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B5_Danh_Sach_Test_Whitebox" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05. API - Postman" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06. E2E - CodeceptJS" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07. Khiem khuyet" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01c. BVA Tieu de Mentor" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03. Decision Table (PhanA)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03b. Decision Table Token" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03c. Decision Table Tep" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04. State Transition (PhanA)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04b. State Transition Token" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04c. State Transition Onboard" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B1_CFG_va_Basis_Path" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B2_Coverage_Levels" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B3_Truoc_va_Sau" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B4_Coverage_Per_Class" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B5_Danh_Sach_Test_Whitebox" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05. API - Postman" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06. E2E - CodeceptJS" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07. Khiem khuyet" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,7 +33,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -120,6 +123,37 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00375623"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00404040"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="16">
@@ -328,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -470,6 +504,37 @@
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -837,7 +902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -864,6 +929,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -902,8 +968,8 @@
           <t>Sheet chi tiết</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -1036,7 +1102,7 @@
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Bảng quyết định</t>
+          <t>Giá trị biên — ngưỡng cắt tiêu đề</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -1045,7 +1111,7 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
@@ -1054,12 +1120,12 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>10 / 10</t>
+          <t>9 / 9</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>03, 03b</t>
+          <t>01c</t>
         </is>
       </c>
       <c r="G10" s="8" t="n"/>
@@ -1068,7 +1134,7 @@
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Chuyển đổi trạng thái — tiến độ node</t>
+          <t>Bảng quyết định</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -1077,7 +1143,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -1086,12 +1152,12 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>9 / 9</t>
+          <t>10 / 10</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03, 03b</t>
         </is>
       </c>
       <c r="G11" s="8" t="n"/>
@@ -1100,7 +1166,7 @@
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Chuyển đổi trạng thái — vòng đời token</t>
+          <t>Bảng quyết định — tệp bảng điểm</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -1109,7 +1175,7 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
@@ -1118,12 +1184,12 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>7 / 7</t>
+          <t>9 / 9</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>04b</t>
+          <t>03c</t>
         </is>
       </c>
       <c r="G12" s="8" t="n"/>
@@ -1132,7 +1198,7 @@
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Hộp trắng — đường cơ sở, CFG</t>
+          <t>Chuyển đổi trạng thái — tiến độ node</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -1140,24 +1206,22 @@
           <t>Đơn vị</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>xem B5</t>
-        </is>
+      <c r="C13" s="6" t="n">
+        <v>9</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>JUnit 5 + JaCoCo</t>
+          <t>JUnit 5</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>đạt</t>
+          <t>9 / 9</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>B1 → B5</t>
+          <t>04</t>
         </is>
       </c>
       <c r="G13" s="8" t="n"/>
@@ -1166,32 +1230,30 @@
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Kiểm thử API</t>
+          <t>Chuyển đổi trạng thái — vòng đời token</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Tích hợp</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>92 case</t>
-        </is>
+          <t>Đơn vị</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Postman / Newman</t>
+          <t>JUnit 5</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>358 phép kiểm</t>
+          <t>7 / 7</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04b</t>
         </is>
       </c>
       <c r="G14" s="8" t="n"/>
@@ -1200,178 +1262,192 @@
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Kiểm thử giao diện đầu-cuối</t>
+          <t>Chuyển đổi trạng thái — khai báo hồ sơ</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Hệ thống</t>
+          <t>Đơn vị</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>CodeceptJS + Playwright</t>
+          <t>JUnit 5</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>17 / 17</t>
+          <t>12 / 12</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>04c</t>
         </is>
       </c>
       <c r="G15" s="8" t="n"/>
       <c r="H15" s="9" t="n"/>
     </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Hộp trắng — đường cơ sở, CFG</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Đơn vị</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>xem B5</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>JUnit 5 + JaCoCo</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>đạt</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>B1 → B5</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="9" t="n"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Kiểm thử API</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Tích hợp</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>92 case</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Postman / Newman</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>358 phép kiểm</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="n"/>
+      <c r="H17" s="9" t="n"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Kiểm thử giao diện đầu-cuối</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Hệ thống</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>CodeceptJS + Playwright</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>17 / 17</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="9" t="n"/>
+    </row>
+    <row r="19"/>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>BẢNG 2 — ĐỘ BAO PHỦ MÃ NGUỒN (JaCoCo)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Chỉ số</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Trước</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Sau</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Tăng</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Nguồn</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Dòng lệnh (Line)</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>60,1%</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>75,5%</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>+15,4 điểm</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>docs/coverage/index.html</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="9" t="n"/>
-    </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Nhánh (Branch)</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>48,2%</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>67,5%</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>+19,3 điểm</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>docs/coverage/index.html</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="9" t="n"/>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Độ phức tạp được phủ</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>53,4%</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>67,4%</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>+14,0 điểm</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>docs/coverage/index.html</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="9" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Phương thức</t>
+          <t>Dòng lệnh (Line)</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>65,1%</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>78,5%</t>
+          <t>60,1%</t>
+        </is>
+      </c>
+      <c r="C22" s="63" t="inlineStr">
+        <is>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>+13,4 điểm</t>
+          <t>+18,5 điểm</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -1382,154 +1458,2298 @@
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="9" t="n"/>
     </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Nhánh (Branch)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>48,2%</t>
+        </is>
+      </c>
+      <c r="C23" s="63" t="inlineStr">
+        <is>
+          <t>72,5%</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>+24,3 điểm</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>docs/coverage/index.html</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="n"/>
+      <c r="H23" s="9" t="n"/>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Độ phức tạp được phủ</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>53,4%</t>
+        </is>
+      </c>
+      <c r="C24" s="63" t="inlineStr">
+        <is>
+          <t>71,0%</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>+17,6 điểm</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>docs/coverage/index.html</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="9" t="n"/>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Phương thức</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>65,1%</t>
+        </is>
+      </c>
+      <c r="C25" s="63" t="inlineStr">
+        <is>
+          <t>81,2%</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>+16,1 điểm</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>docs/coverage/index.html</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="n"/>
+      <c r="H25" s="9" t="n"/>
+    </row>
+    <row r="26"/>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>BẢNG 3 — TỔNG SỐ PHÉP KIỂM ĐÃ CHẠY</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Tầng</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Đơn vị đếm</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Số lượng</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Không đạt</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Đơn vị (JUnit)</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>test method</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n">
-        <v>378</v>
-      </c>
-      <c r="D26" s="7" t="n">
+      <c r="C29" s="6" t="n">
+        <v>408</v>
+      </c>
+      <c r="D29" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>Toàn bộ dự án, gồm cả hộp đen và hộp trắng</t>
         </is>
       </c>
-      <c r="G26" s="8" t="n"/>
-      <c r="H26" s="9" t="n"/>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="G29" s="8" t="n"/>
+      <c r="H29" s="9" t="n"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>Tích hợp (Postman)</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>phép kiểm</t>
         </is>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="C30" s="6" t="n">
         <v>358</v>
       </c>
-      <c r="D27" s="7" t="n">
+      <c r="D30" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>Chạy trên cơ sở dữ liệu vừa gieo lại</t>
         </is>
       </c>
-      <c r="G27" s="8" t="n"/>
-      <c r="H27" s="9" t="n"/>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="G30" s="8" t="n"/>
+      <c r="H30" s="9" t="n"/>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Hệ thống (CodeceptJS)</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>kịch bản</t>
         </is>
       </c>
-      <c r="C28" s="6" t="n">
+      <c r="C31" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="D28" s="7" t="n">
+      <c r="D31" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>Ba kịch bản từng đỏ đều là lỗi ứng dụng thật, nay đã sửa xong</t>
         </is>
       </c>
-      <c r="G28" s="8" t="n"/>
-      <c r="H28" s="9" t="n"/>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>Mười khiếm khuyết được phát hiện và đều đã khắc phục kèm test hồi quy. Chi tiết ở sheet 07. Khiem khuyet.</t>
+      <c r="G31" s="8" t="n"/>
+      <c r="H31" s="9" t="n"/>
+    </row>
+    <row r="32"/>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>Mười một khiếm khuyết được phát hiện và đều đã khắc phục kèm test hồi quy. Chi tiết ở sheet 07. Khiem khuyet.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A24:H24"/>
+  <mergeCells count="24">
+    <mergeCell ref="F18:H18"/>
     <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="F23:H23"/>
     <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="F13:H13"/>
-    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="F31:H31"/>
     <mergeCell ref="F9:H9"/>
-    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="F29:H29"/>
     <mergeCell ref="F11:H11"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="F25:H25"/>
     <mergeCell ref="A4:H4"/>
+    <mergeCell ref="F16:H16"/>
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="F6:H6"/>
-    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="A20:H20"/>
     <mergeCell ref="F12:H12"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F24:H24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>BẢNG B1 - ĐỒ THỊ LUỒNG ĐIỀU KHIỂN (CFG) VÀ ĐỘ PHỨC TẠP CYCLOMATIC</t>
+        </is>
+      </c>
+      <c r="B1" s="27" t="n"/>
+      <c r="C1" s="27" t="n"/>
+      <c r="D1" s="27" t="n"/>
+      <c r="E1" s="27" t="n"/>
+      <c r="F1" s="27" t="n"/>
+      <c r="G1" s="27" t="n"/>
+      <c r="H1" s="27" t="n"/>
+      <c r="I1" s="28" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>Nguồn: RoadmapService.java  |  Hai hàm được phân tích: calculatePercent() và isNodeLocked()</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>A - BẢNG CHỈ SỐ CFG (Control Flow Graph Metrics)</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="n"/>
+      <c r="C4" s="27" t="n"/>
+      <c r="D4" s="27" t="n"/>
+      <c r="E4" s="27" t="n"/>
+      <c r="F4" s="27" t="n"/>
+      <c r="G4" s="27" t="n"/>
+      <c r="H4" s="27" t="n"/>
+      <c r="I4" s="28" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>HÀM</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>File nguồn</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>Nút (N)</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>Cạnh (E)</t>
+        </is>
+      </c>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>Nút điều kiện (P)</t>
+        </is>
+      </c>
+      <c r="F5" s="31" t="inlineStr">
+        <is>
+          <t>Miền (R)</t>
+        </is>
+      </c>
+      <c r="G5" s="31" t="inlineStr">
+        <is>
+          <t>V(G)=E-N+2</t>
+        </is>
+      </c>
+      <c r="H5" s="31" t="inlineStr">
+        <is>
+          <t>V(G)=P+1</t>
+        </is>
+      </c>
+      <c r="I5" s="31" t="inlineStr">
+        <is>
+          <t>Số test tối thiểu</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>calculatePercent()</t>
+        </is>
+      </c>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>RoadmapService.java</t>
+        </is>
+      </c>
+      <c r="C6" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="34" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>isNodeLocked()</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="inlineStr">
+        <is>
+          <t>RoadmapService.java</t>
+        </is>
+      </c>
+      <c r="C7" s="37" t="n">
+        <v>14</v>
+      </c>
+      <c r="D7" s="37" t="n">
+        <v>19</v>
+      </c>
+      <c r="E7" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="G7" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" s="37" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>B - DANH SÁCH ĐƯỜNG CƠ SỞ (BASIS PATHS)</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="n"/>
+      <c r="C9" s="27" t="n"/>
+      <c r="D9" s="27" t="n"/>
+      <c r="E9" s="27" t="n"/>
+      <c r="F9" s="27" t="n"/>
+      <c r="G9" s="27" t="n"/>
+      <c r="H9" s="27" t="n"/>
+      <c r="I9" s="28" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>HÀM</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>Path ID</t>
+        </is>
+      </c>
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t>Điều kiện</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>Chi tiết luồng thực thi</t>
+        </is>
+      </c>
+      <c r="E10" s="31" t="inlineStr">
+        <is>
+          <t>Kết quả mong đợi</t>
+        </is>
+      </c>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>Test Method</t>
+        </is>
+      </c>
+      <c r="G10" s="31" t="inlineStr">
+        <is>
+          <t>Input ví dụ</t>
+        </is>
+      </c>
+      <c r="H10" s="31" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="I10" s="31" t="inlineStr">
+        <is>
+          <t>Pass/Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>calculatePercent()</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>total==0 TRUE</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="inlineStr">
+        <is>
+          <t>Start -&gt; [total==0 TRUE] -&gt; return 0.0 -&gt; End</t>
+        </is>
+      </c>
+      <c r="E11" s="33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F11" s="33" t="inlineStr">
+        <is>
+          <t>calculatePercent_totalZero</t>
+        </is>
+      </c>
+      <c r="G11" s="33" t="inlineStr">
+        <is>
+          <t>completed=0, total=0</t>
+        </is>
+      </c>
+      <c r="H11" s="34" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I11" s="34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>calculatePercent()</t>
+        </is>
+      </c>
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C12" s="36" t="inlineStr">
+        <is>
+          <t>total==0 FALSE</t>
+        </is>
+      </c>
+      <c r="D12" s="36" t="inlineStr">
+        <is>
+          <t>Start -&gt; [total==0 FALSE] -&gt; return Math.round -&gt; End</t>
+        </is>
+      </c>
+      <c r="E12" s="36" t="inlineStr">
+        <is>
+          <t>% hợp lệ</t>
+        </is>
+      </c>
+      <c r="F12" s="36" t="inlineStr">
+        <is>
+          <t>calculatePercent_normalCase</t>
+        </is>
+      </c>
+      <c r="G12" s="36" t="inlineStr">
+        <is>
+          <t>completed=5, total=10</t>
+        </is>
+      </c>
+      <c r="H12" s="37" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="I12" s="37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>isNodeLocked()</t>
+        </is>
+      </c>
+      <c r="B13" s="34" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>tier null -&gt; tier=1, tier&lt;=1 TRUE</t>
+        </is>
+      </c>
+      <c r="D13" s="33" t="inlineStr">
+        <is>
+          <t>Start -&gt; [tier null-&gt;1] -&gt; [tier&lt;=1 TRUE] -&gt; return false -&gt; End</t>
+        </is>
+      </c>
+      <c r="E13" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F13" s="33" t="inlineStr">
+        <is>
+          <t>isNodeLocked_tier1Null</t>
+        </is>
+      </c>
+      <c r="G13" s="33" t="inlineStr">
+        <is>
+          <t>node.tier=null</t>
+        </is>
+      </c>
+      <c r="H13" s="34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I13" s="34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>isNodeLocked()</t>
+        </is>
+      </c>
+      <c r="B14" s="37" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C14" s="36" t="inlineStr">
+        <is>
+          <t>tier=1, tier&lt;=1 TRUE</t>
+        </is>
+      </c>
+      <c r="D14" s="36" t="inlineStr">
+        <is>
+          <t>Start -&gt; [tier=1] -&gt; [tier&lt;=1 TRUE] -&gt; return false -&gt; End</t>
+        </is>
+      </c>
+      <c r="E14" s="36" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F14" s="36" t="inlineStr">
+        <is>
+          <t>isNodeLocked_explicitTier1</t>
+        </is>
+      </c>
+      <c r="G14" s="36" t="inlineStr">
+        <is>
+          <t>node.tier=1</t>
+        </is>
+      </c>
+      <c r="H14" s="37" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I14" s="37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>isNodeLocked()</t>
+        </is>
+      </c>
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>tier=2, tất cả tier1 DONE</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="inlineStr">
+        <is>
+          <t>Start -&gt; [tier=2] -&gt; doneNodeIds đầy đủ -&gt; anyMatch=FALSE -&gt; return false</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F15" s="33" t="inlineStr">
+        <is>
+          <t>isNodeLocked_tier2AllDone</t>
+        </is>
+      </c>
+      <c r="G15" s="33" t="inlineStr">
+        <is>
+          <t>node.tier=2, tier1 DONE</t>
+        </is>
+      </c>
+      <c r="H15" s="34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I15" s="34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>isNodeLocked()</t>
+        </is>
+      </c>
+      <c r="B16" s="37" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C16" s="36" t="inlineStr">
+        <is>
+          <t>tier=2, tier1 chưa DONE</t>
+        </is>
+      </c>
+      <c r="D16" s="36" t="inlineStr">
+        <is>
+          <t>Start -&gt; [tier=2] -&gt; doneNodeIds thiếu -&gt; anyMatch=TRUE -&gt; return true</t>
+        </is>
+      </c>
+      <c r="E16" s="36" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F16" s="36" t="inlineStr">
+        <is>
+          <t>isNodeLocked_tier2NotDone</t>
+        </is>
+      </c>
+      <c r="G16" s="36" t="inlineStr">
+        <is>
+          <t>node.tier=2, tier1 chưa DONE</t>
+        </is>
+      </c>
+      <c r="H16" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I16" s="37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="32" t="inlineStr">
+        <is>
+          <t>isNodeLocked()</t>
+        </is>
+      </c>
+      <c r="B17" s="34" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C17" s="33" t="inlineStr">
+        <is>
+          <t>tier=3, tier1 chưa DONE</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="inlineStr">
+        <is>
+          <t>Start -&gt; [tier=3] -&gt; anyMatch(tier&lt;3 AND !done)=TRUE -&gt; return true</t>
+        </is>
+      </c>
+      <c r="E17" s="33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F17" s="33" t="inlineStr">
+        <is>
+          <t>isNodeLocked_tier3Tier1NotDone</t>
+        </is>
+      </c>
+      <c r="G17" s="33" t="inlineStr">
+        <is>
+          <t>node.tier=3, tier1 chưa DONE</t>
+        </is>
+      </c>
+      <c r="H17" s="34" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I17" s="34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>isNodeLocked()</t>
+        </is>
+      </c>
+      <c r="B18" s="37" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C18" s="36" t="inlineStr">
+        <is>
+          <t>tier=3, tier2 chưa DONE</t>
+        </is>
+      </c>
+      <c r="D18" s="36" t="inlineStr">
+        <is>
+          <t>Start -&gt; [tier=3] -&gt; anyMatch(tier2 NOT done)=TRUE -&gt; return true</t>
+        </is>
+      </c>
+      <c r="E18" s="36" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F18" s="36" t="inlineStr">
+        <is>
+          <t>isNodeLocked_tier3Tier2NotDone</t>
+        </is>
+      </c>
+      <c r="G18" s="36" t="inlineStr">
+        <is>
+          <t>node.tier=3, tier2 chưa DONE</t>
+        </is>
+      </c>
+      <c r="H18" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I18" s="37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>isNodeLocked()</t>
+        </is>
+      </c>
+      <c r="B19" s="34" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="C19" s="33" t="inlineStr">
+        <is>
+          <t>tier=3, tất cả done</t>
+        </is>
+      </c>
+      <c r="D19" s="33" t="inlineStr">
+        <is>
+          <t>Start -&gt; [tier=3] -&gt; anyMatch=FALSE -&gt; return false</t>
+        </is>
+      </c>
+      <c r="E19" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F19" s="33" t="inlineStr">
+        <is>
+          <t>isNodeLocked_tier3AllDone</t>
+        </is>
+      </c>
+      <c r="G19" s="33" t="inlineStr">
+        <is>
+          <t>node.tier=3, tất cả DONE</t>
+        </is>
+      </c>
+      <c r="H19" s="34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I19" s="34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A9:I9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>BẢNG B2 - SO SÁNH CÁC MỨC BAO PHỦ (COVERAGE LEVELS)</t>
+        </is>
+      </c>
+      <c r="B1" s="27" t="n"/>
+      <c r="C1" s="27" t="n"/>
+      <c r="D1" s="27" t="n"/>
+      <c r="E1" s="27" t="n"/>
+      <c r="F1" s="27" t="n"/>
+      <c r="G1" s="27" t="n"/>
+      <c r="H1" s="27" t="n"/>
+      <c r="I1" s="27" t="n"/>
+      <c r="J1" s="28" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>Hàm minh họa: calculatePercent(completed, total) | Bảng phụ: Ma trận tổ hợp điều kiện isNodeLocked()</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>A - BẢNG SO SÁNH 4 MỨC BAO PHỦ</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="n"/>
+      <c r="C4" s="27" t="n"/>
+      <c r="D4" s="27" t="n"/>
+      <c r="E4" s="27" t="n"/>
+      <c r="F4" s="27" t="n"/>
+      <c r="G4" s="27" t="n"/>
+      <c r="H4" s="27" t="n"/>
+      <c r="I4" s="27" t="n"/>
+      <c r="J4" s="28" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>MỨC BAO PHỦ</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>Số test tối thiểu</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>Bộ Test Case</t>
+        </is>
+      </c>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>Lỗi bắt được</t>
+        </is>
+      </c>
+      <c r="F5" s="31" t="inlineStr">
+        <is>
+          <t>Lỗi bỏ sót</t>
+        </is>
+      </c>
+      <c r="G5" s="31" t="inlineStr">
+        <is>
+          <t>Áp dụng?</t>
+        </is>
+      </c>
+      <c r="H5" s="31" t="inlineStr">
+        <is>
+          <t>Mức tin cậy</t>
+        </is>
+      </c>
+      <c r="I5" s="31" t="inlineStr">
+        <is>
+          <t>Ưu điểm</t>
+        </is>
+      </c>
+      <c r="J5" s="31" t="inlineStr">
+        <is>
+          <t>Nhược điểm</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="38" t="inlineStr">
+        <is>
+          <t>Câu lệnh (Statement)</t>
+        </is>
+      </c>
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>Mỗi dòng lệnh được thực thi ít nhất 1 lần</t>
+        </is>
+      </c>
+      <c r="C6" s="40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="39" t="inlineStr">
+        <is>
+          <t>(completed=5, total=10)</t>
+        </is>
+      </c>
+      <c r="E6" s="39" t="inlineStr">
+        <is>
+          <t>Xác nhận đường tính % được thực thi</t>
+        </is>
+      </c>
+      <c r="F6" s="39" t="inlineStr">
+        <is>
+          <t>Không phát hiện total=0 gây chia cho 0</t>
+        </is>
+      </c>
+      <c r="G6" s="39" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="H6" s="39" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="I6" s="39" t="inlineStr">
+        <is>
+          <t>Đơn giản</t>
+        </is>
+      </c>
+      <c r="J6" s="39" t="inlineStr">
+        <is>
+          <t>Bỏ sót nhánh</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="41" t="inlineStr">
+        <is>
+          <t>Nhánh (Branch)</t>
+        </is>
+      </c>
+      <c r="B7" s="42" t="inlineStr">
+        <is>
+          <t>Mỗi nhánh True/False được đi qua</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="42" t="inlineStr">
+        <is>
+          <t>(0,0); (5,10)</t>
+        </is>
+      </c>
+      <c r="E7" s="42" t="inlineStr">
+        <is>
+          <t>Bao phủ cả nhánh total==0 và total!=0</t>
+        </is>
+      </c>
+      <c r="F7" s="42" t="inlineStr">
+        <is>
+          <t>Không đánh giá tương tác nhiều điều kiện</t>
+        </is>
+      </c>
+      <c r="G7" s="42" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="H7" s="42" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="I7" s="42" t="inlineStr">
+        <is>
+          <t>Phát hiện lỗi nhánh</t>
+        </is>
+      </c>
+      <c r="J7" s="42" t="inlineStr">
+        <is>
+          <t>Không phủ tổ hợp</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="38" t="inlineStr">
+        <is>
+          <t>Điều kiện (Condition)</t>
+        </is>
+      </c>
+      <c r="B8" s="39" t="inlineStr">
+        <is>
+          <t>Mỗi điều kiện đơn nhận đủ T/F</t>
+        </is>
+      </c>
+      <c r="C8" s="40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="39" t="inlineStr">
+        <is>
+          <t>(0,0); (1,3)</t>
+        </is>
+      </c>
+      <c r="E8" s="39" t="inlineStr">
+        <is>
+          <t>Điều kiện total==0 nhận đủ TRUE và FALSE</t>
+        </is>
+      </c>
+      <c r="F8" s="39" t="inlineStr">
+        <is>
+          <t>Không thay thế được tổ hợp biểu thức phức</t>
+        </is>
+      </c>
+      <c r="G8" s="39" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="H8" s="39" t="inlineStr">
+        <is>
+          <t>Khá</t>
+        </is>
+      </c>
+      <c r="I8" s="39" t="inlineStr">
+        <is>
+          <t>Kiểm tra từng điều kiện</t>
+        </is>
+      </c>
+      <c r="J8" s="39" t="inlineStr">
+        <is>
+          <t>Bỏ sót tổ hợp</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="41" t="inlineStr">
+        <is>
+          <t>Tổ hợp điều kiện (MC/DC)</t>
+        </is>
+      </c>
+      <c r="B9" s="42" t="inlineStr">
+        <is>
+          <t>Mỗi tổ hợp TRUE/FALSE của tất cả điều kiện</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="inlineStr">
+        <is>
+          <t>(0,0); (1,3)</t>
+        </is>
+      </c>
+      <c r="E9" s="42" t="inlineStr">
+        <is>
+          <t>Với calculatePercent chỉ có 1 điều kiện</t>
+        </is>
+      </c>
+      <c r="F9" s="42" t="inlineStr">
+        <is>
+          <t>Cần kiểm tra riêng các tổ hợp của isNodeLocked</t>
+        </is>
+      </c>
+      <c r="G9" s="42" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="H9" s="42" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="I9" s="42" t="inlineStr">
+        <is>
+          <t>Phát hiện lỗi tương tác</t>
+        </is>
+      </c>
+      <c r="J9" s="42" t="inlineStr">
+        <is>
+          <t>Số test tăng theo hàm mũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="30" t="inlineStr">
+        <is>
+          <t>B - MA TRẬN TỔ HỢP ĐIỀU KIỆN (MC/DC) cho isNodeLocked()</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="n"/>
+      <c r="C11" s="27" t="n"/>
+      <c r="D11" s="27" t="n"/>
+      <c r="E11" s="27" t="n"/>
+      <c r="F11" s="27" t="n"/>
+      <c r="G11" s="27" t="n"/>
+      <c r="H11" s="27" t="n"/>
+      <c r="I11" s="27" t="n"/>
+      <c r="J11" s="27" t="n"/>
+      <c r="K11" s="27" t="n"/>
+      <c r="L11" s="28" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="C12" s="31" t="inlineStr">
+        <is>
+          <t>t(tier)</t>
+        </is>
+      </c>
+      <c r="D12" s="31" t="inlineStr">
+        <is>
+          <t>tier1Done</t>
+        </is>
+      </c>
+      <c r="E12" s="31" t="inlineStr">
+        <is>
+          <t>tier2Done</t>
+        </is>
+      </c>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>A: !completed</t>
+        </is>
+      </c>
+      <c r="G12" s="31" t="inlineStr">
+        <is>
+          <t>B: t==2</t>
+        </is>
+      </c>
+      <c r="H12" s="31" t="inlineStr">
+        <is>
+          <t>C: !tier1Done</t>
+        </is>
+      </c>
+      <c r="I12" s="31" t="inlineStr">
+        <is>
+          <t>D: t&gt;=3</t>
+        </is>
+      </c>
+      <c r="J12" s="31" t="inlineStr">
+        <is>
+          <t>E: !(t1&amp;&amp;t2)</t>
+        </is>
+      </c>
+      <c r="K12" s="31" t="inlineStr">
+        <is>
+          <t>Expected locked?</t>
+        </is>
+      </c>
+      <c r="L12" s="31" t="inlineStr">
+        <is>
+          <t>Mô tả kịch bản</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="37" t="inlineStr">
+        <is>
+          <t>T2-01</t>
+        </is>
+      </c>
+      <c r="B13" s="37" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="C13" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="37" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E13" s="37" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F13" s="37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G13" s="37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="H13" s="37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I13" s="37" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J13" s="37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="K13" s="44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L13" s="36" t="inlineStr">
+        <is>
+          <t>Tier 2, tier1 chưa xong -&gt; khóa</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="inlineStr">
+        <is>
+          <t>T2-02</t>
+        </is>
+      </c>
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="C14" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E14" s="34" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F14" s="34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G14" s="34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="H14" s="34" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="I14" s="34" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J14" s="34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="K14" s="45" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="L14" s="33" t="inlineStr">
+        <is>
+          <t>Tier 2, tier1 đã xong -&gt; mở khóa</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="37" t="inlineStr">
+        <is>
+          <t>T3-01</t>
+        </is>
+      </c>
+      <c r="B15" s="37" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="C15" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="37" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E15" s="37" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F15" s="37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G15" s="37" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H15" s="37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I15" s="37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="J15" s="37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="K15" s="44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L15" s="36" t="inlineStr">
+        <is>
+          <t>Tier 3, tier1 chưa xong -&gt; khóa</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>T3-02</t>
+        </is>
+      </c>
+      <c r="B16" s="34" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="C16" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E16" s="34" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F16" s="34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G16" s="34" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H16" s="34" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="I16" s="34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="J16" s="34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="K16" s="44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L16" s="33" t="inlineStr">
+        <is>
+          <t>Tier 3, tier2 chưa xong -&gt; khóa</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="37" t="inlineStr">
+        <is>
+          <t>T3-03</t>
+        </is>
+      </c>
+      <c r="B17" s="37" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="C17" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E17" s="37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F17" s="37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G17" s="37" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H17" s="37" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="I17" s="37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="J17" s="37" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K17" s="45" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="L17" s="36" t="inlineStr">
+        <is>
+          <t>Tier 3, tất cả done -&gt; mở khóa</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="inlineStr">
+        <is>
+          <t>DONE-01</t>
+        </is>
+      </c>
+      <c r="B18" s="34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="C18" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="34" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E18" s="34" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F18" s="34" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G18" s="34" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H18" s="34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I18" s="34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="J18" s="34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="K18" s="45" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="L18" s="33" t="inlineStr">
+        <is>
+          <t>Node đã completed -&gt; không khóa</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="37" t="inlineStr">
+        <is>
+          <t>T1-01</t>
+        </is>
+      </c>
+      <c r="B19" s="37" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="C19" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="37" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E19" s="37" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F19" s="37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G19" s="37" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H19" s="37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I19" s="37" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J19" s="37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="K19" s="45" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="L19" s="36" t="inlineStr">
+        <is>
+          <t>Tier 1 -&gt; không bao giờ khóa</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>BẢNG B3 - ĐỘ BAO PHỦ TRƯỚC VÀ SAU KHI BỔ SUNG TEST</t>
+        </is>
+      </c>
+      <c r="B1" s="27" t="n"/>
+      <c r="C1" s="27" t="n"/>
+      <c r="D1" s="27" t="n"/>
+      <c r="E1" s="27" t="n"/>
+      <c r="F1" s="28" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>Trước: baseline  |  Sau: kết quả clean test ngày 2026-09-06 (370 tests, 0 failures)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>A - BẢNG SO SÁNH CHỈ SỐ BAO PHỦ (JaCoCo)</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="n"/>
+      <c r="C4" s="27" t="n"/>
+      <c r="D4" s="27" t="n"/>
+      <c r="E4" s="27" t="n"/>
+      <c r="F4" s="28" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>CHỈ SỐ BAO PHỦ</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>TRƯỚC</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>TĂNG (pp)</t>
+        </is>
+      </c>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>% TĂNG</t>
+        </is>
+      </c>
+      <c r="F5" s="31" t="inlineStr">
+        <is>
+          <t>NGUỒN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="38" t="inlineStr">
+        <is>
+          <t>Bao phủ Instruction</t>
+        </is>
+      </c>
+      <c r="B6" s="40" t="inlineStr">
+        <is>
+          <t>60.1%</t>
+        </is>
+      </c>
+      <c r="C6" s="40" t="inlineStr">
+        <is>
+          <t>76.1%</t>
+        </is>
+      </c>
+      <c r="D6" s="45" t="inlineStr">
+        <is>
+          <t>+16.0 pp</t>
+        </is>
+      </c>
+      <c r="E6" s="40" t="inlineStr">
+        <is>
+          <t>+26.6%</t>
+        </is>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>JaCoCo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>Bao phủ dòng lệnh (Line)</t>
+        </is>
+      </c>
+      <c r="B7" s="37" t="inlineStr">
+        <is>
+          <t>60.1%</t>
+        </is>
+      </c>
+      <c r="C7" s="37" t="inlineStr">
+        <is>
+          <t>75.5%</t>
+        </is>
+      </c>
+      <c r="D7" s="45" t="inlineStr">
+        <is>
+          <t>+15.4 pp</t>
+        </is>
+      </c>
+      <c r="E7" s="37" t="inlineStr">
+        <is>
+          <t>+25.6%</t>
+        </is>
+      </c>
+      <c r="F7" s="37" t="inlineStr">
+        <is>
+          <t>JaCoCo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="38" t="inlineStr">
+        <is>
+          <t>Bao phủ nhánh (Branch)</t>
+        </is>
+      </c>
+      <c r="B8" s="40" t="inlineStr">
+        <is>
+          <t>48.2%</t>
+        </is>
+      </c>
+      <c r="C8" s="40" t="inlineStr">
+        <is>
+          <t>67.5%</t>
+        </is>
+      </c>
+      <c r="D8" s="45" t="inlineStr">
+        <is>
+          <t>+19.3 pp</t>
+        </is>
+      </c>
+      <c r="E8" s="40" t="inlineStr">
+        <is>
+          <t>+40.0%</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>JaCoCo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>Độ phức tạp được phủ</t>
+        </is>
+      </c>
+      <c r="B9" s="37" t="inlineStr">
+        <is>
+          <t>53.4%</t>
+        </is>
+      </c>
+      <c r="C9" s="37" t="inlineStr">
+        <is>
+          <t>67.4%</t>
+        </is>
+      </c>
+      <c r="D9" s="45" t="inlineStr">
+        <is>
+          <t>+14.0 pp</t>
+        </is>
+      </c>
+      <c r="E9" s="37" t="inlineStr">
+        <is>
+          <t>+26.3%</t>
+        </is>
+      </c>
+      <c r="F9" s="37" t="inlineStr">
+        <is>
+          <t>JaCoCo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="38" t="inlineStr">
+        <is>
+          <t>Số phương thức được phủ</t>
+        </is>
+      </c>
+      <c r="B10" s="40" t="inlineStr">
+        <is>
+          <t>65.1%</t>
+        </is>
+      </c>
+      <c r="C10" s="40" t="inlineStr">
+        <is>
+          <t>78.5%</t>
+        </is>
+      </c>
+      <c r="D10" s="45" t="inlineStr">
+        <is>
+          <t>+13.4 pp</t>
+        </is>
+      </c>
+      <c r="E10" s="40" t="inlineStr">
+        <is>
+          <t>+20.6%</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>JaCoCo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>B - KẾT QUẢ CHẠY TEST SUITE</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="n"/>
+      <c r="C12" s="27" t="n"/>
+      <c r="D12" s="27" t="n"/>
+      <c r="E12" s="27" t="n"/>
+      <c r="F12" s="28" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>CHỈ SỐ</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="inlineStr">
+        <is>
+          <t>GIÁ TRỊ</t>
+        </is>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>NGƯỠNG</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>KẾT QUẢ</t>
+        </is>
+      </c>
+      <c r="E13" s="31" t="inlineStr">
+        <is>
+          <t>GHI CHÚ</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>NGUỒN</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t>Tổng số test</t>
+        </is>
+      </c>
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="C14" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E14" s="33" t="inlineStr">
+        <is>
+          <t>Bao gồm unit + slice tests</t>
+        </is>
+      </c>
+      <c r="F14" s="33" t="inlineStr">
+        <is>
+          <t>Maven Surefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>Test thất bại</t>
+        </is>
+      </c>
+      <c r="B15" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C15" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D15" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E15" s="36" t="inlineStr">
+        <is>
+          <t>Không có test nào bị đỏ</t>
+        </is>
+      </c>
+      <c r="F15" s="36" t="inlineStr">
+        <is>
+          <t>Maven Surefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>Branch coverage</t>
+        </is>
+      </c>
+      <c r="B16" s="34" t="inlineStr">
+        <is>
+          <t>67.5%</t>
+        </is>
+      </c>
+      <c r="C16" s="34" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="D16" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E16" s="33" t="inlineStr">
+        <is>
+          <t>Vượt ngưỡng JaCoCo check</t>
+        </is>
+      </c>
+      <c r="F16" s="33" t="inlineStr">
+        <is>
+          <t>JaCoCo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>Line coverage</t>
+        </is>
+      </c>
+      <c r="B17" s="37" t="inlineStr">
+        <is>
+          <t>75.5%</t>
+        </is>
+      </c>
+      <c r="C17" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E17" s="36" t="inlineStr">
+        <is>
+          <t>Không đặt ngưỡng riêng</t>
+        </is>
+      </c>
+      <c r="F17" s="36" t="inlineStr">
+        <is>
+          <t>JaCoCo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>Kết quả build</t>
+        </is>
+      </c>
+      <c r="B18" s="34" t="inlineStr">
+        <is>
+          <t>BUILD SUCCESS</t>
+        </is>
+      </c>
+      <c r="C18" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D18" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E18" s="33" t="inlineStr">
+        <is>
+          <t>mvn clean test thành công</t>
+        </is>
+      </c>
+      <c r="F18" s="33" t="inlineStr">
+        <is>
+          <t>Maven</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>C - NHẬN XÉT VÀ KẾT LUẬN</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="n"/>
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="28" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>VẤN ĐỀ</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="inlineStr">
+        <is>
+          <t>NỘI DUNG NHẬN XÉT</t>
+        </is>
+      </c>
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="27" t="n"/>
+      <c r="F21" s="28" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="32" t="inlineStr">
+        <is>
+          <t>Branch coverage tăng 19.3 pp (48.2% -&gt; 67.5%)</t>
+        </is>
+      </c>
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>Đây là mức tăng lớn nhất, cho thấy việc bổ sung test white-box đã bao phủ được nhiều nhánh if/else bị bỏ sót.</t>
+        </is>
+      </c>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="27" t="n"/>
+      <c r="F22" s="28" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="35" t="inlineStr">
+        <is>
+          <t>370 test, 0 failures</t>
+        </is>
+      </c>
+      <c r="B23" s="36" t="inlineStr">
+        <is>
+          <t>Toàn bộ bộ test ổn định, không có regression (lỗi hồi quy).</t>
+        </is>
+      </c>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="27" t="n"/>
+      <c r="E23" s="27" t="n"/>
+      <c r="F23" s="28" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="32" t="inlineStr">
+        <is>
+          <t>Branch gate 65% đạt (67.5%)</t>
+        </is>
+      </c>
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>JaCoCo check sẽ fail build nếu branch &lt; 65%. Project vượt ngưỡng này, đảm bảo CI/CD hoạt động trơn tru.</t>
+        </is>
+      </c>
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="27" t="n"/>
+      <c r="F24" s="28" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="35" t="inlineStr">
+        <is>
+          <t>GlobalExceptionHandler 100%</t>
+        </is>
+      </c>
+      <c r="B25" s="36" t="inlineStr">
+        <is>
+          <t>File mới thêm đã được test đầy đủ 16/16 nhánh, 158/158 instruction.</t>
+        </is>
+      </c>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="28" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="A20:F20"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1571,7 +3791,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="30" t="inlineStr">
         <is>
@@ -4076,7 +6295,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72"/>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
@@ -4120,7 +6338,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4154,7 +6372,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="30" t="inlineStr">
         <is>
@@ -5028,7 +7245,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5729,7 +7946,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6509,7 +8726,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6542,6 +8759,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -6960,20 +9178,59 @@
       </c>
       <c r="H14" s="9" t="n"/>
     </row>
+    <row r="15" ht="78" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>DEF-011</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Tệp bảng điểm không có phần mở rộng (ví dụ "bangdiem") làm lastIndexOf(".") trả -1, kéo theo substring(-1) ném StringIndexOutOfBoundsException — người dùng nhận lỗi 500 thay vì thông báo 400 thân thiện.</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Bảng quyết định — cột R8 của bảng định dạng tệp bảng điểm</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Chạy test R8 trên bản mã chưa sửa: đỏ, nhận StringIndexOutOfBoundsException. Trên bản đã sửa: xanh. Nhánh OnboardingService 75,0% (9/12) → 100,0% (14/14).</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>ĐÃ SỬA</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Coi "không có đuôi" là đuôi rỗng để rơi đúng vào nhánh báo lỗi định dạng có sẵn. Test cũ trong OnboardingServiceTest từng khoá hành vi lỗi, nay đã đổi sang khẳng định hành vi đúng.</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="n"/>
+    </row>
     <row r="16" ht="44" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>Cả mười khiếm khuyết đã được khắc phục và có test hồi quy đi kèm. Ba khiếm khuyết DEF-001, DEF-009 và DEF-010 đều do KIỂM THỬ GIAO DIỆN tìm ra — đây là tầng duy nhất chạm tới HTML nên là tầng duy nhất thấy được rằng template đang đọc những thuộc tính không hề tồn tại trong model. Unit test và kiểm thử API không thể phát hiện loại lỗi này vì chúng không render giao diện.</t>
+          <t>Cả mười một khiếm khuyết đã được khắc phục và có test hồi quy đi kèm. Ba khiếm khuyết DEF-001, DEF-009 và DEF-010 đều do KIỂM THỬ GIAO DIỆN tìm ra — đây là tầng duy nhất chạm tới HTML nên là tầng duy nhất thấy được chúng; suốt thời gian đó test đơn vị và test API vẫn xanh. DEF-011 đáng chú ý theo cách ngược lại: test hộp trắng đã GHI ĐÚNG nguyên nhân từ trước nhưng lại chốt luôn hành vi lỗi bằng một khẳng định, nên bộ test vẫn xanh và khiếm khuyết nằm im. Phải tới khi dựng bảng quyết định — nơi mỗi cột buộc phải có một hành động xác định — nó mới bị buộc phải sửa.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="G11:H11"/>
     <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="A16:H16"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="G6:H6"/>
@@ -7018,7 +9275,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -7197,7 +9453,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
@@ -7362,7 +9617,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
@@ -7861,7 +10115,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
@@ -8129,7 +10382,6 @@
         </is>
       </c>
     </row>
-    <row r="49"/>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
@@ -8429,7 +10681,6 @@
         </is>
       </c>
     </row>
-    <row r="60"/>
     <row r="61" ht="24" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
@@ -9224,6 +11475,780 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>BVA — bảng thứ hai: ngưỡng cắt tiêu đề phiên trò chuyện</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="53" t="inlineStr">
+        <is>
+          <t>MentorService.sendMessage(). Bảng thiết kế theo mẫu slide 23 và 24, trường hợp một biến (n = 1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="54" t="inlineStr">
+        <is>
+          <t>TỔNG KẾT THI HÀNH — 9 test đã chạy, 9 PASS, 0 fail. 7 case thuộc bảng giá trị biên, 2 case kiểm tra bổ sung ngoài bảng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Lớp test trong source</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Số test</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Kỹ thuật áp dụng</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>MentorTitleStandardBvaTest</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Standard + Robustness BVA · 1 biến</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="55" t="inlineStr">
+        <is>
+          <t>Số test được đối chiếu tự động với target/surefire-reports khi sinh lại sheet bằng tools/gen_sheets_bo_sung.py — source chạy ra số khác thì script dừng và báo lỗi. Chạy lại để kiểm chứng:  mvnw test -Dtest=MentorTitleStandardBvaTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>VÌ SAO CHỌN HÀM NÀY LÀM ĐỐI TƯỢNG BVA THỨ HAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="56" t="inlineStr">
+        <is>
+          <t>Toàn bộ ràng buộc @Size của dự án đều nằm ở RegisterFormDTO và đã phủ trọn ở sheet 01. Muốn tìm thêm biên phải soi các NGƯỠNG CỨNG viết thẳng trong tầng service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="56" t="inlineStr">
+        <is>
+          <t>Ngưỡng 60 ký tự này là ngưỡng sạch nhất trong số đó: một biến duy nhất, một phép so sánh, kết quả quan sát trực tiếp bằng chuỗi tiêu đề — không phải gọi dịch vụ ngoài, không phải dựng tệp PDF giả như các ngưỡng 6000 / 3000 / 200 ở TranscriptAnalysisService và PortfolioService.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="56" t="inlineStr">
+        <is>
+          <t>Giá trị của phép thử: lỗi lệch-một-đơn-vị ở substring là lỗi kinh điển. Mã nguồn dùng '&gt;' chứ không phải '&gt;=', nên chuỗi dài ĐÚNG 60 ký tự phải giữ nguyên văn. Chỉ case ở đúng biên mới phân biệt được hai cách viết đó — case nominal 30 ký tự thì cả hai đều cho cùng kết quả.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>BẢNG 1 — ĐỊNH NGHĨA GIÁ TRỊ BIÊN CỦA BIẾN ĐANG XÉT</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Giá trị</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>userText (số ký tự)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>câu hỏi ngắn nhất có nghĩa</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>min+</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>ngay trên min</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>giá trị điển hình, giữa miền</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>max-</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>ngay dưới ngưỡng cắt</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>đúng ngưỡng cắt — vẫn KHÔNG bị cắt vì mã dùng '&gt;'</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="55" t="inlineStr">
+        <is>
+          <t>Ràng buộc gốc: session.setTitle(userText.length() &gt; 60 ? userText.substring(0, 60) + '…' : userText). Đây là ngưỡng CẮT chứ không phải ngưỡng HỢP LỆ — vượt qua không bị từ chối, mà bị rút gọn. Vì thế cột Expected Output ghi hình dạng chuỗi kết quả thay vì Hợp lệ / Không hợp lệ như sheet 01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>BẢNG 2 — STANDARD BVA TEST CASES (mẫu slide 23) · số case = 4n + 1 = 4×1 + 1 = 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>userText (ký tự)</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Biến đang xét</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Expected Output</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Độ dài tiêu đề</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Kết quả thực tế</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Method trong code</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>độ dài = min</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Giữ NGUYÊN VĂN, không có dấu …</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>standardBva_khongCat</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>độ dài = min+</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Giữ NGUYÊN VĂN, không có dấu …</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>standardBva_khongCat</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="57" t="n">
+        <v>30</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>độ dài = nom</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Giữ NGUYÊN VĂN, không có dấu …</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>standardBva_khongCat</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" s="57" t="n">
+        <v>59</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>độ dài = max-</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Giữ NGUYÊN VĂN, không có dấu …</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>standardBva_khongCat</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" s="57" t="n">
+        <v>60</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>độ dài = max (đúng ngưỡng)</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Giữ NGUYÊN VĂN, không có dấu …</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>standardBva_khongCat</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="55" t="inlineStr">
+        <is>
+          <t>CÁCH ĐỌC: n = 1 nên không có ô 'tất cả nominal' riêng — case 3 vừa là nom của biến duy nhất, vừa là ô trung tâm của bảng. Ô tô tím là giá trị đang được đẩy tới biên. Cả 5 case đều là clean test case: kết quả mong đợi giống nhau, chỉ khác nhau ở chỗ chúng ép mã nguồn chọn đúng nhánh 'không cắt'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>BẢNG 3 — ROBUSTNESS BVA, phần BỔ SUNG (mẫu slide 24) · 6n + 1 = 6×1 + 1 = 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>userText (ký tự)</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Biến đang xét</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Expected Output</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Độ dài tiêu đề</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Kết quả thực tế</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Method trong code</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B34" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>độ dài = min- (chuỗi rỗng)</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Giữ nguyên văn — tiêu đề thành rỗng</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>robustnessBva_ngoaiBien</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B35" s="20" t="n">
+        <v>61</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>độ dài = max+</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>BỊ CẮT: 60 ký tự đầu + dấu …</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>robustnessBva_ngoaiBien</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="55" t="inlineStr">
+        <is>
+          <t>GHI NHẬN Ở CASE 6 (min-): chuỗi rỗng làm tiêu đề thành rỗng. KHÔNG xếp là khiếm khuyết — chính điều kiện isBlank() ngay phía trên sẽ đặt lại tiêu đề ở tin nhắn kế tiếp, hệ thống tự phục hồi; ngoài ra tầng controller đã chặn tin nhắn rỗng. Ghi lại ở đây để người đọc báo cáo biết case này đã được cân nhắc chứ không bị bỏ sót.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="56" t="inlineStr">
+        <is>
+          <t>CASE 7 LÀ CASE ĐÁNG GIÁ NHẤT của bảng. Nó là case DUY NHẤT chạy vào nhánh cắt chuỗi. Cặp (case 5, case 7) — 60 và 61 ký tự — chính là phép thử phân biệt '&gt;' với '&gt;=': nếu ai đó sửa mã thành '&gt;=' thì case 5 đỏ ngay, còn mọi case nominal vẫn xanh. Đó là lý do BVA tồn tại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>BẢNG 4 — KIỂM TRA BỔ SUNG, nằm ngoài bảng giá trị biên</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Tiêu đề phiên trước đó</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>userText (ký tự)</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Expected Output</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>Kết quả thực tế</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Method trong code</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Đã có tiêu đề thật</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>KHÔNG ghi đè — ngưỡng 60 không còn tác dụng</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr"/>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi</t>
+        </is>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>boSung_tieuDeDaDat_khongGhiDe</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Đã có tiêu đề thật</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>KHÔNG ghi đè — ngưỡng 60 không còn tác dụng</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr"/>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>boSung_tieuDeDaDat_khongGhiDe</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="55" t="inlineStr">
+        <is>
+          <t>Ngưỡng 60 chỉ áp dụng khi tiêu đề còn là mặc định 'Cuộc trò chuyện mới'. Hai case này chốt điều đó: phiên đã có tiêu đề thật thì tin nhắn dài bao nhiêu cũng không được ghi đè — nếu không, mọi câu hỏi sau đều đổi tên phiên và người dùng không tìm lại được cuộc trò chuyện cũ. Để ngoài bảng BVA vì chúng đổi ĐIỀU KIỆN VÀO nhánh, không đổi giá trị của biên.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A32:H32"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -9251,7 +12276,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -9316,7 +12340,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
@@ -9602,7 +12625,6 @@
       </c>
       <c r="H16" s="5" t="n"/>
     </row>
-    <row r="17"/>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
@@ -9755,7 +12777,6 @@
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="6" t="n"/>
     </row>
-    <row r="25"/>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
@@ -9774,7 +12795,6 @@
       <c r="G26" s="6" t="n"/>
       <c r="H26" s="6" t="n"/>
     </row>
-    <row r="27"/>
     <row r="28" ht="44" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
@@ -9795,7 +12815,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9828,7 +12848,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -9893,7 +12912,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
@@ -10119,7 +13137,6 @@
       </c>
       <c r="H16" s="5" t="n"/>
     </row>
-    <row r="17"/>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
@@ -10272,7 +13289,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
@@ -10292,7 +13308,6 @@
       <c r="G26" s="6" t="n"/>
       <c r="H26" s="6" t="n"/>
     </row>
-    <row r="27"/>
     <row r="28" ht="44" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
@@ -10329,7 +13344,929 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Decision Table Testing — bảng thứ ba: tệp bảng điểm</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="53" t="inlineStr">
+        <is>
+          <t>OnboardingService.saveTranscript(). Bảng thiết kế theo mẫu slide 44, có bước rút gọn rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="54" t="inlineStr">
+        <is>
+          <t>TỔNG KẾT THI HÀNH — 9 test đã chạy, 9 PASS, 0 fail. 8 test ứng với 8 rule của bảng, 1 test kiểm tra bổ sung ngoài bảng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Lớp test trong source</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Số test</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Kỹ thuật áp dụng</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>TranscriptFileDecisionTableTest</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Bảng quyết định · 8 rule</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="55" t="inlineStr">
+        <is>
+          <t>Số test được đối chiếu tự động với target/surefire-reports khi sinh lại sheet bằng tools/gen_sheets_bo_sung.py — source chạy ra số khác thì script dừng và báo lỗi. Chạy lại để kiểm chứng:  mvnw test -Dtest=TranscriptFileDecisionTableTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>VÌ SAO CHỌN HÀM NÀY — CON SỐ ĐO ĐƯỢC</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ số OnboardingService</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Trước khi có bảng này</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Sau khi có bảng này</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Nguồn</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Bao phủ nhánh</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>75,0 %  (9/12)</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>100,0 %  (14/14)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>target/site/jacoco/jacoco.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Bao phủ dòng</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>94,7 %  (18/19)</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>100,0 %  (19/19)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>target/site/jacoco/jacoco.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="56" t="inlineStr">
+        <is>
+          <t>Báo cáo độ bao phủ (docs/coverage/README.md) đã chỉ đích danh: ba nhánh còn thiếu của OnboardingService nằm gọn ở dòng kiểm đuôi tệp, vì MỌI test trước đây đều đặt tên tệp là 'transcript.pdf' — ba nhánh .png, .jpg, .jpeg chưa bao giờ được thử. Mẫu số tăng từ 12 lên 14 vì bản sửa DEF-011 thêm một nhánh mới.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>BẢNG QUYẾT ĐỊNH ĐẦY ĐỦ — mẫu slide 44 · 8 rule sau khi rút gọn</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Condition / Action</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>C1 · Tên tệp = null</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>C2 · Đuôi tệp</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>.png</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>.jpg</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>.jpeg</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>hợp lệ</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>khác</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>C3 · Dung lượng ≤ 10MB</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>A1 · Lưu tệp, trả đường dẫn</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>A2 · Lỗi 'Tên file không hợp lệ'</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>A3 · Lỗi 'Vượt quá 10MB'</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>A4 · Lỗi 'Chỉ chấp nhận PDF, PNG hoặc JPG'</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Kết quả chạy test</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Method trong code</t>
+        </is>
+      </c>
+      <c r="B25" s="58" t="inlineStr">
+        <is>
+          <t>rule1_tenTepNull_tuChoi</t>
+        </is>
+      </c>
+      <c r="C25" s="58" t="inlineStr">
+        <is>
+          <t>rule2_duoiPdf_luuThanhCong</t>
+        </is>
+      </c>
+      <c r="D25" s="58" t="inlineStr">
+        <is>
+          <t>rule3_duoiPng_luuThanhCong</t>
+        </is>
+      </c>
+      <c r="E25" s="58" t="inlineStr">
+        <is>
+          <t>rule4_duoiJpg_luuThanhCong</t>
+        </is>
+      </c>
+      <c r="F25" s="58" t="inlineStr">
+        <is>
+          <t>rule5_duoiJpeg_luuThanhCong</t>
+        </is>
+      </c>
+      <c r="G25" s="58" t="inlineStr">
+        <is>
+          <t>rule6_duoiHopLe_dungLuongQuaLon_tuChoi</t>
+        </is>
+      </c>
+      <c r="H25" s="58" t="inlineStr">
+        <is>
+          <t>rule7_duoiKhongHopLe_tuChoi</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="59" t="inlineStr">
+        <is>
+          <t>RULE R8 — CỘT TÁCH RIÊNG VÌ NÓ BUỘC PHẢI SỬA MỘT KHIẾM KHUYẾT</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Condition / Action</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Hành vi TRƯỚC khi sửa</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Hành vi SAU khi sửa</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Method trong code</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>C1 · Tên tệp = null</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="6" t="inlineStr"/>
+      <c r="H28" s="58" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>C2 · Đuôi tệp</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>không có dấu chấm</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="6" t="inlineStr"/>
+      <c r="H29" s="58" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>C3 · Dung lượng ≤ 10MB</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="6" t="inlineStr"/>
+      <c r="H30" s="58" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>A4 · Lỗi 'Chỉ chấp nhận PDF, PNG hoặc JPG'</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="inlineStr">
+        <is>
+          <t>StringIndexOutOfBoundsException → lỗi 500</t>
+        </is>
+      </c>
+      <c r="D31" s="60" t="inlineStr">
+        <is>
+          <t>IllegalArgumentException → lỗi 400</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H31" s="58" t="inlineStr">
+        <is>
+          <t>rule8_tenTepKhongCoDuoi_tuChoi</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>GHI CHÚ TRUNG THỰC VỀ DEF-011 — AI PHÁT HIỆN, AI SỬA</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="56" t="inlineStr">
+        <is>
+          <t>Bảng quyết định KHÔNG phải nơi phát hiện lỗi này. Test hộp trắng OnboardingServiceTest đã ghi đúng nguyên nhân từ trước, nguyên văn trong mã nguồn: "BUG?: filename thiếu phần mở rộng (vd 'resume') làm substring(lastIndexOf('.')) với index=-1 ném StringIndexOutOfBoundsException. Nên guard lastIndexOf('.') &lt; 0 để trả IllegalArgumentException cho đồng nhất."</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="56" t="inlineStr">
+        <is>
+          <t>Nhưng chính test đó lại CHỐT HÀNH VI LỖI: assertThatThrownBy(...).isInstanceOf(StringIndexOutOfBoundsException.class). Bộ test vì thế vẫn xanh, và khiếm khuyết nằm im suốt thời gian đó — một ghi chú 'BUG?' có thể sống mãi trong mã nguồn mà không ai bị buộc phải xử lý.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="56" t="inlineStr">
+        <is>
+          <t>ĐÓNG GÓP THẬT CỦA KỸ THUẬT NÀY là buộc phải sửa: mỗi cột của bảng quyết định phải ứng với một hành động xác định trong nhóm A1–A4. Không thể để một ô là 'sập 500'. Một ô trống trong bảng quyết định thì không sống sót qua khâu duyệt như một dòng chú thích.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="42" customHeight="1">
+      <c r="A37" s="56" t="inlineStr">
+        <is>
+          <t>Kiểm chứng: chạy test R8 trên bản mã CHƯA sửa → đỏ (nhận StringIndexOutOfBoundsException). Chạy trên bản đã sửa → xanh. Test cũ trong OnboardingServiceTest cũng đã được đổi sang khẳng định hành vi ĐÚNG thay vì khoá hành vi lỗi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>VỀ SỐ RULE — VÌ SAO 24 RÚT CÒN 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="56" t="inlineStr">
+        <is>
+          <t>Số rule tối đa = 2 (C1) × 6 (C2) × 2 (C3) = 24. Khác hai bảng quyết định trước, ở đây điều kiện C2 có SÁU giá trị chứ không nhị phân, nên công thức 2^n không dùng được — phải NHÂN số giá trị của từng điều kiện, đúng như bảng ProgressService ở sheet 03 (3 × 2 = 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="42" customHeight="1">
+      <c r="A41" s="56" t="inlineStr">
+        <is>
+          <t>Rút gọn về 8 nhờ mã nguồn kiểm ba điều kiện TUẦN TỰ và thoát ngay khi gặp lỗi: khi một điều kiện phía trước đã quyết định kết quả thì các điều kiện phía sau thành 'không quan tâm' (dấu –). R1 gộp 12 tổ hợp (tên null thì đuôi và dung lượng vô nghĩa); R7 và R8 mỗi cột gộp 2 tổ hợp (đuôi sai thì chặn trước khi tới phép kiểm dung lượng).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="56" t="inlineStr">
+        <is>
+          <t>R6 LÀ RULE GỘP THEO KIỂU KHÁC: bốn đuôi hợp lệ khi vượt dung lượng đều cho cùng một hành động, nên bốn rule con thu về một, ô C2 ghi 'hợp lệ' thay vì một đuôi cụ thể. Đây đúng là bước rút gọn bảng quyết định của chương IV — giống cách sheet 03b gộp R2, R3, R4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="42" customHeight="1">
+      <c r="A43" s="56" t="inlineStr">
+        <is>
+          <t>QUAN HỆ VỚI SHEET GIÁ TRỊ BIÊN: điều kiện C3 ở bảng này chỉ lấy giá trị NOMINAL (1 byte và 11 MB) để phân biệt nhánh. Các giá trị sát biên 10 MB (max-1, max, max+1) thuộc về OnboardingFileSizeBvaTest ở sheet 01. Hai kỹ thuật bổ sung nhau chứ không trùng: bảng quyết định hỏi 'tổ hợp nào dẫn tới hành động nào', giá trị biên hỏi 'lằn ranh nằm chính xác ở đâu'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>KIỂM TRA BỔ SUNG — ngoài bảng quyết định</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Trường hợp</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Đầu vào</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Expected Output</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr"/>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Kết quả thực tế</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>Method trong code</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Đuôi viết HOA</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>BANGDIEM.PDF</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Được chấp nhận (mã gọi toLowerCase)</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr"/>
+      <c r="E47" s="5" t="inlineStr"/>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi</t>
+        </is>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>boSung_duoiVietHoa_duocChapNhan</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="55" t="inlineStr">
+        <is>
+          <t>Không đưa vào bảng vì đây là biến thể TRÌNH BÀY của C2, không phải rule độc lập: nếu tách ra thì bảng phải nhân đôi số cột mà không sinh thêm hành động mới nào.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A34:H34"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10362,7 +14299,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -10427,7 +14363,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
@@ -10855,7 +14790,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
@@ -10898,7 +14832,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10931,7 +14865,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -10989,7 +14922,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -11087,7 +15019,6 @@
       </c>
       <c r="H11" s="9" t="n"/>
     </row>
-    <row r="12"/>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
@@ -11154,7 +15085,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
@@ -11484,7 +15414,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34" ht="44" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
@@ -11535,2060 +15464,897 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="26" t="inlineStr">
-        <is>
-          <t>BẢNG B1 - ĐỒ THỊ LUỒNG ĐIỀU KHIỂN (CFG) VÀ ĐỘ PHỨC TẠP CYCLOMATIC</t>
-        </is>
-      </c>
-      <c r="B1" s="27" t="n"/>
-      <c r="C1" s="27" t="n"/>
-      <c r="D1" s="27" t="n"/>
-      <c r="E1" s="27" t="n"/>
-      <c r="F1" s="27" t="n"/>
-      <c r="G1" s="27" t="n"/>
-      <c r="H1" s="27" t="n"/>
-      <c r="I1" s="28" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="29" t="inlineStr">
-        <is>
-          <t>Nguồn: RoadmapService.java  |  Hai hàm được phân tích: calculatePercent() và isNodeLocked()</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="30" t="inlineStr">
-        <is>
-          <t>A - BẢNG CHỈ SỐ CFG (Control Flow Graph Metrics)</t>
-        </is>
-      </c>
-      <c r="B4" s="27" t="n"/>
-      <c r="C4" s="27" t="n"/>
-      <c r="D4" s="27" t="n"/>
-      <c r="E4" s="27" t="n"/>
-      <c r="F4" s="27" t="n"/>
-      <c r="G4" s="27" t="n"/>
-      <c r="H4" s="27" t="n"/>
-      <c r="I4" s="28" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="31" t="inlineStr">
-        <is>
-          <t>HÀM</t>
-        </is>
-      </c>
-      <c r="B5" s="31" t="inlineStr">
-        <is>
-          <t>File nguồn</t>
-        </is>
-      </c>
-      <c r="C5" s="31" t="inlineStr">
-        <is>
-          <t>Nút (N)</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="inlineStr">
-        <is>
-          <t>Cạnh (E)</t>
-        </is>
-      </c>
-      <c r="E5" s="31" t="inlineStr">
-        <is>
-          <t>Nút điều kiện (P)</t>
-        </is>
-      </c>
-      <c r="F5" s="31" t="inlineStr">
-        <is>
-          <t>Miền (R)</t>
-        </is>
-      </c>
-      <c r="G5" s="31" t="inlineStr">
-        <is>
-          <t>V(G)=E-N+2</t>
-        </is>
-      </c>
-      <c r="H5" s="31" t="inlineStr">
-        <is>
-          <t>V(G)=P+1</t>
-        </is>
-      </c>
-      <c r="I5" s="31" t="inlineStr">
-        <is>
-          <t>Số test tối thiểu</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="32" t="inlineStr">
-        <is>
-          <t>calculatePercent()</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="inlineStr">
-        <is>
-          <t>RoadmapService.java</t>
-        </is>
-      </c>
-      <c r="C6" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" s="34" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="35" t="inlineStr">
-        <is>
-          <t>isNodeLocked()</t>
-        </is>
-      </c>
-      <c r="B7" s="36" t="inlineStr">
-        <is>
-          <t>RoadmapService.java</t>
-        </is>
-      </c>
-      <c r="C7" s="37" t="n">
-        <v>14</v>
-      </c>
-      <c r="D7" s="37" t="n">
-        <v>19</v>
-      </c>
-      <c r="E7" s="37" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" s="37" t="n">
-        <v>7</v>
-      </c>
-      <c r="G7" s="37" t="n">
-        <v>7</v>
-      </c>
-      <c r="H7" s="37" t="n">
-        <v>7</v>
-      </c>
-      <c r="I7" s="37" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" s="30" t="inlineStr">
-        <is>
-          <t>B - DANH SÁCH ĐƯỜNG CƠ SỞ (BASIS PATHS)</t>
-        </is>
-      </c>
-      <c r="B9" s="27" t="n"/>
-      <c r="C9" s="27" t="n"/>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="27" t="n"/>
-      <c r="F9" s="27" t="n"/>
-      <c r="G9" s="27" t="n"/>
-      <c r="H9" s="27" t="n"/>
-      <c r="I9" s="28" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="31" t="inlineStr">
-        <is>
-          <t>HÀM</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="inlineStr">
-        <is>
-          <t>Path ID</t>
-        </is>
-      </c>
-      <c r="C10" s="31" t="inlineStr">
-        <is>
-          <t>Điều kiện</t>
-        </is>
-      </c>
-      <c r="D10" s="31" t="inlineStr">
-        <is>
-          <t>Chi tiết luồng thực thi</t>
-        </is>
-      </c>
-      <c r="E10" s="31" t="inlineStr">
-        <is>
-          <t>Kết quả mong đợi</t>
-        </is>
-      </c>
-      <c r="F10" s="31" t="inlineStr">
-        <is>
-          <t>Test Method</t>
-        </is>
-      </c>
-      <c r="G10" s="31" t="inlineStr">
-        <is>
-          <t>Input ví dụ</t>
-        </is>
-      </c>
-      <c r="H10" s="31" t="inlineStr">
-        <is>
-          <t>Output</t>
-        </is>
-      </c>
-      <c r="I10" s="31" t="inlineStr">
-        <is>
-          <t>Pass/Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="32" t="inlineStr">
-        <is>
-          <t>calculatePercent()</t>
-        </is>
-      </c>
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C11" s="33" t="inlineStr">
-        <is>
-          <t>total==0 TRUE</t>
-        </is>
-      </c>
-      <c r="D11" s="33" t="inlineStr">
-        <is>
-          <t>Start -&gt; [total==0 TRUE] -&gt; return 0.0 -&gt; End</t>
-        </is>
-      </c>
-      <c r="E11" s="33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F11" s="33" t="inlineStr">
-        <is>
-          <t>calculatePercent_totalZero</t>
-        </is>
-      </c>
-      <c r="G11" s="33" t="inlineStr">
-        <is>
-          <t>completed=0, total=0</t>
-        </is>
-      </c>
-      <c r="H11" s="34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I11" s="34" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="35" t="inlineStr">
-        <is>
-          <t>calculatePercent()</t>
-        </is>
-      </c>
-      <c r="B12" s="37" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C12" s="36" t="inlineStr">
-        <is>
-          <t>total==0 FALSE</t>
-        </is>
-      </c>
-      <c r="D12" s="36" t="inlineStr">
-        <is>
-          <t>Start -&gt; [total==0 FALSE] -&gt; return Math.round -&gt; End</t>
-        </is>
-      </c>
-      <c r="E12" s="36" t="inlineStr">
-        <is>
-          <t>% hợp lệ</t>
-        </is>
-      </c>
-      <c r="F12" s="36" t="inlineStr">
-        <is>
-          <t>calculatePercent_normalCase</t>
-        </is>
-      </c>
-      <c r="G12" s="36" t="inlineStr">
-        <is>
-          <t>completed=5, total=10</t>
-        </is>
-      </c>
-      <c r="H12" s="37" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="I12" s="37" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="32" t="inlineStr">
-        <is>
-          <t>isNodeLocked()</t>
-        </is>
-      </c>
-      <c r="B13" s="34" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C13" s="33" t="inlineStr">
-        <is>
-          <t>tier null -&gt; tier=1, tier&lt;=1 TRUE</t>
-        </is>
-      </c>
-      <c r="D13" s="33" t="inlineStr">
-        <is>
-          <t>Start -&gt; [tier null-&gt;1] -&gt; [tier&lt;=1 TRUE] -&gt; return false -&gt; End</t>
-        </is>
-      </c>
-      <c r="E13" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F13" s="33" t="inlineStr">
-        <is>
-          <t>isNodeLocked_tier1Null</t>
-        </is>
-      </c>
-      <c r="G13" s="33" t="inlineStr">
-        <is>
-          <t>node.tier=null</t>
-        </is>
-      </c>
-      <c r="H13" s="34" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I13" s="34" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="35" t="inlineStr">
-        <is>
-          <t>isNodeLocked()</t>
-        </is>
-      </c>
-      <c r="B14" s="37" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C14" s="36" t="inlineStr">
-        <is>
-          <t>tier=1, tier&lt;=1 TRUE</t>
-        </is>
-      </c>
-      <c r="D14" s="36" t="inlineStr">
-        <is>
-          <t>Start -&gt; [tier=1] -&gt; [tier&lt;=1 TRUE] -&gt; return false -&gt; End</t>
-        </is>
-      </c>
-      <c r="E14" s="36" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F14" s="36" t="inlineStr">
-        <is>
-          <t>isNodeLocked_explicitTier1</t>
-        </is>
-      </c>
-      <c r="G14" s="36" t="inlineStr">
-        <is>
-          <t>node.tier=1</t>
-        </is>
-      </c>
-      <c r="H14" s="37" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I14" s="37" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="32" t="inlineStr">
-        <is>
-          <t>isNodeLocked()</t>
-        </is>
-      </c>
-      <c r="B15" s="34" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C15" s="33" t="inlineStr">
-        <is>
-          <t>tier=2, tất cả tier1 DONE</t>
-        </is>
-      </c>
-      <c r="D15" s="33" t="inlineStr">
-        <is>
-          <t>Start -&gt; [tier=2] -&gt; doneNodeIds đầy đủ -&gt; anyMatch=FALSE -&gt; return false</t>
-        </is>
-      </c>
-      <c r="E15" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F15" s="33" t="inlineStr">
-        <is>
-          <t>isNodeLocked_tier2AllDone</t>
-        </is>
-      </c>
-      <c r="G15" s="33" t="inlineStr">
-        <is>
-          <t>node.tier=2, tier1 DONE</t>
-        </is>
-      </c>
-      <c r="H15" s="34" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I15" s="34" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="35" t="inlineStr">
-        <is>
-          <t>isNodeLocked()</t>
-        </is>
-      </c>
-      <c r="B16" s="37" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="C16" s="36" t="inlineStr">
-        <is>
-          <t>tier=2, tier1 chưa DONE</t>
-        </is>
-      </c>
-      <c r="D16" s="36" t="inlineStr">
-        <is>
-          <t>Start -&gt; [tier=2] -&gt; doneNodeIds thiếu -&gt; anyMatch=TRUE -&gt; return true</t>
-        </is>
-      </c>
-      <c r="E16" s="36" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F16" s="36" t="inlineStr">
-        <is>
-          <t>isNodeLocked_tier2NotDone</t>
-        </is>
-      </c>
-      <c r="G16" s="36" t="inlineStr">
-        <is>
-          <t>node.tier=2, tier1 chưa DONE</t>
-        </is>
-      </c>
-      <c r="H16" s="37" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I16" s="37" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="32" t="inlineStr">
-        <is>
-          <t>isNodeLocked()</t>
-        </is>
-      </c>
-      <c r="B17" s="34" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="C17" s="33" t="inlineStr">
-        <is>
-          <t>tier=3, tier1 chưa DONE</t>
-        </is>
-      </c>
-      <c r="D17" s="33" t="inlineStr">
-        <is>
-          <t>Start -&gt; [tier=3] -&gt; anyMatch(tier&lt;3 AND !done)=TRUE -&gt; return true</t>
-        </is>
-      </c>
-      <c r="E17" s="33" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F17" s="33" t="inlineStr">
-        <is>
-          <t>isNodeLocked_tier3Tier1NotDone</t>
-        </is>
-      </c>
-      <c r="G17" s="33" t="inlineStr">
-        <is>
-          <t>node.tier=3, tier1 chưa DONE</t>
-        </is>
-      </c>
-      <c r="H17" s="34" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I17" s="34" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="35" t="inlineStr">
-        <is>
-          <t>isNodeLocked()</t>
-        </is>
-      </c>
-      <c r="B18" s="37" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="C18" s="36" t="inlineStr">
-        <is>
-          <t>tier=3, tier2 chưa DONE</t>
-        </is>
-      </c>
-      <c r="D18" s="36" t="inlineStr">
-        <is>
-          <t>Start -&gt; [tier=3] -&gt; anyMatch(tier2 NOT done)=TRUE -&gt; return true</t>
-        </is>
-      </c>
-      <c r="E18" s="36" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F18" s="36" t="inlineStr">
-        <is>
-          <t>isNodeLocked_tier3Tier2NotDone</t>
-        </is>
-      </c>
-      <c r="G18" s="36" t="inlineStr">
-        <is>
-          <t>node.tier=3, tier2 chưa DONE</t>
-        </is>
-      </c>
-      <c r="H18" s="37" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I18" s="37" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="32" t="inlineStr">
-        <is>
-          <t>isNodeLocked()</t>
-        </is>
-      </c>
-      <c r="B19" s="34" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="C19" s="33" t="inlineStr">
-        <is>
-          <t>tier=3, tất cả done</t>
-        </is>
-      </c>
-      <c r="D19" s="33" t="inlineStr">
-        <is>
-          <t>Start -&gt; [tier=3] -&gt; anyMatch=FALSE -&gt; return false</t>
-        </is>
-      </c>
-      <c r="E19" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F19" s="33" t="inlineStr">
-        <is>
-          <t>isNodeLocked_tier3AllDone</t>
-        </is>
-      </c>
-      <c r="G19" s="33" t="inlineStr">
-        <is>
-          <t>node.tier=3, tất cả DONE</t>
-        </is>
-      </c>
-      <c r="H19" s="34" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I19" s="34" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A9:I9"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="36" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="26" t="inlineStr">
-        <is>
-          <t>BẢNG B2 - SO SÁNH CÁC MỨC BAO PHỦ (COVERAGE LEVELS)</t>
-        </is>
-      </c>
-      <c r="B1" s="27" t="n"/>
-      <c r="C1" s="27" t="n"/>
-      <c r="D1" s="27" t="n"/>
-      <c r="E1" s="27" t="n"/>
-      <c r="F1" s="27" t="n"/>
-      <c r="G1" s="27" t="n"/>
-      <c r="H1" s="27" t="n"/>
-      <c r="I1" s="27" t="n"/>
-      <c r="J1" s="28" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="29" t="inlineStr">
-        <is>
-          <t>Hàm minh họa: calculatePercent(completed, total) | Bảng phụ: Ma trận tổ hợp điều kiện isNodeLocked()</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="30" t="inlineStr">
-        <is>
-          <t>A - BẢNG SO SÁNH 4 MỨC BAO PHỦ</t>
-        </is>
-      </c>
-      <c r="B4" s="27" t="n"/>
-      <c r="C4" s="27" t="n"/>
-      <c r="D4" s="27" t="n"/>
-      <c r="E4" s="27" t="n"/>
-      <c r="F4" s="27" t="n"/>
-      <c r="G4" s="27" t="n"/>
-      <c r="H4" s="27" t="n"/>
-      <c r="I4" s="27" t="n"/>
-      <c r="J4" s="28" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="31" t="inlineStr">
-        <is>
-          <t>MỨC BAO PHỦ</t>
-        </is>
-      </c>
-      <c r="B5" s="31" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
-        </is>
-      </c>
-      <c r="C5" s="31" t="inlineStr">
-        <is>
-          <t>Số test tối thiểu</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="inlineStr">
-        <is>
-          <t>Bộ Test Case</t>
-        </is>
-      </c>
-      <c r="E5" s="31" t="inlineStr">
-        <is>
-          <t>Lỗi bắt được</t>
-        </is>
-      </c>
-      <c r="F5" s="31" t="inlineStr">
-        <is>
-          <t>Lỗi bỏ sót</t>
-        </is>
-      </c>
-      <c r="G5" s="31" t="inlineStr">
-        <is>
-          <t>Áp dụng?</t>
-        </is>
-      </c>
-      <c r="H5" s="31" t="inlineStr">
-        <is>
-          <t>Mức tin cậy</t>
-        </is>
-      </c>
-      <c r="I5" s="31" t="inlineStr">
-        <is>
-          <t>Ưu điểm</t>
-        </is>
-      </c>
-      <c r="J5" s="31" t="inlineStr">
-        <is>
-          <t>Nhược điểm</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="38" t="inlineStr">
-        <is>
-          <t>Câu lệnh (Statement)</t>
-        </is>
-      </c>
-      <c r="B6" s="39" t="inlineStr">
-        <is>
-          <t>Mỗi dòng lệnh được thực thi ít nhất 1 lần</t>
-        </is>
-      </c>
-      <c r="C6" s="40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" s="39" t="inlineStr">
-        <is>
-          <t>(completed=5, total=10)</t>
-        </is>
-      </c>
-      <c r="E6" s="39" t="inlineStr">
-        <is>
-          <t>Xác nhận đường tính % được thực thi</t>
-        </is>
-      </c>
-      <c r="F6" s="39" t="inlineStr">
-        <is>
-          <t>Không phát hiện total=0 gây chia cho 0</t>
-        </is>
-      </c>
-      <c r="G6" s="39" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="H6" s="39" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="I6" s="39" t="inlineStr">
-        <is>
-          <t>Đơn giản</t>
-        </is>
-      </c>
-      <c r="J6" s="39" t="inlineStr">
-        <is>
-          <t>Bỏ sót nhánh</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="41" t="inlineStr">
-        <is>
-          <t>Nhánh (Branch)</t>
-        </is>
-      </c>
-      <c r="B7" s="42" t="inlineStr">
-        <is>
-          <t>Mỗi nhánh True/False được đi qua</t>
-        </is>
-      </c>
-      <c r="C7" s="43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D7" s="42" t="inlineStr">
-        <is>
-          <t>(0,0); (5,10)</t>
-        </is>
-      </c>
-      <c r="E7" s="42" t="inlineStr">
-        <is>
-          <t>Bao phủ cả nhánh total==0 và total!=0</t>
-        </is>
-      </c>
-      <c r="F7" s="42" t="inlineStr">
-        <is>
-          <t>Không đánh giá tương tác nhiều điều kiện</t>
-        </is>
-      </c>
-      <c r="G7" s="42" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="H7" s="42" t="inlineStr">
-        <is>
-          <t>Trung bình</t>
-        </is>
-      </c>
-      <c r="I7" s="42" t="inlineStr">
-        <is>
-          <t>Phát hiện lỗi nhánh</t>
-        </is>
-      </c>
-      <c r="J7" s="42" t="inlineStr">
-        <is>
-          <t>Không phủ tổ hợp</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="38" t="inlineStr">
-        <is>
-          <t>Điều kiện (Condition)</t>
-        </is>
-      </c>
-      <c r="B8" s="39" t="inlineStr">
-        <is>
-          <t>Mỗi điều kiện đơn nhận đủ T/F</t>
-        </is>
-      </c>
-      <c r="C8" s="40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D8" s="39" t="inlineStr">
-        <is>
-          <t>(0,0); (1,3)</t>
-        </is>
-      </c>
-      <c r="E8" s="39" t="inlineStr">
-        <is>
-          <t>Điều kiện total==0 nhận đủ TRUE và FALSE</t>
-        </is>
-      </c>
-      <c r="F8" s="39" t="inlineStr">
-        <is>
-          <t>Không thay thế được tổ hợp biểu thức phức</t>
-        </is>
-      </c>
-      <c r="G8" s="39" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="H8" s="39" t="inlineStr">
-        <is>
-          <t>Khá</t>
-        </is>
-      </c>
-      <c r="I8" s="39" t="inlineStr">
-        <is>
-          <t>Kiểm tra từng điều kiện</t>
-        </is>
-      </c>
-      <c r="J8" s="39" t="inlineStr">
-        <is>
-          <t>Bỏ sót tổ hợp</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="41" t="inlineStr">
-        <is>
-          <t>Tổ hợp điều kiện (MC/DC)</t>
-        </is>
-      </c>
-      <c r="B9" s="42" t="inlineStr">
-        <is>
-          <t>Mỗi tổ hợp TRUE/FALSE của tất cả điều kiện</t>
-        </is>
-      </c>
-      <c r="C9" s="43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D9" s="42" t="inlineStr">
-        <is>
-          <t>(0,0); (1,3)</t>
-        </is>
-      </c>
-      <c r="E9" s="42" t="inlineStr">
-        <is>
-          <t>Với calculatePercent chỉ có 1 điều kiện</t>
-        </is>
-      </c>
-      <c r="F9" s="42" t="inlineStr">
-        <is>
-          <t>Cần kiểm tra riêng các tổ hợp của isNodeLocked</t>
-        </is>
-      </c>
-      <c r="G9" s="42" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="H9" s="42" t="inlineStr">
-        <is>
-          <t>Cao</t>
-        </is>
-      </c>
-      <c r="I9" s="42" t="inlineStr">
-        <is>
-          <t>Phát hiện lỗi tương tác</t>
-        </is>
-      </c>
-      <c r="J9" s="42" t="inlineStr">
-        <is>
-          <t>Số test tăng theo hàm mũ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="30" t="inlineStr">
-        <is>
-          <t>B - MA TRẬN TỔ HỢP ĐIỀU KIỆN (MC/DC) cho isNodeLocked()</t>
-        </is>
-      </c>
-      <c r="B11" s="27" t="n"/>
-      <c r="C11" s="27" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="27" t="n"/>
-      <c r="F11" s="27" t="n"/>
-      <c r="G11" s="27" t="n"/>
-      <c r="H11" s="27" t="n"/>
-      <c r="I11" s="27" t="n"/>
-      <c r="J11" s="27" t="n"/>
-      <c r="K11" s="27" t="n"/>
-      <c r="L11" s="28" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="31" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="B12" s="31" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="C12" s="31" t="inlineStr">
-        <is>
-          <t>t(tier)</t>
-        </is>
-      </c>
-      <c r="D12" s="31" t="inlineStr">
-        <is>
-          <t>tier1Done</t>
-        </is>
-      </c>
-      <c r="E12" s="31" t="inlineStr">
-        <is>
-          <t>tier2Done</t>
-        </is>
-      </c>
-      <c r="F12" s="31" t="inlineStr">
-        <is>
-          <t>A: !completed</t>
-        </is>
-      </c>
-      <c r="G12" s="31" t="inlineStr">
-        <is>
-          <t>B: t==2</t>
-        </is>
-      </c>
-      <c r="H12" s="31" t="inlineStr">
-        <is>
-          <t>C: !tier1Done</t>
-        </is>
-      </c>
-      <c r="I12" s="31" t="inlineStr">
-        <is>
-          <t>D: t&gt;=3</t>
-        </is>
-      </c>
-      <c r="J12" s="31" t="inlineStr">
-        <is>
-          <t>E: !(t1&amp;&amp;t2)</t>
-        </is>
-      </c>
-      <c r="K12" s="31" t="inlineStr">
-        <is>
-          <t>Expected locked?</t>
-        </is>
-      </c>
-      <c r="L12" s="31" t="inlineStr">
-        <is>
-          <t>Mô tả kịch bản</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="37" t="inlineStr">
-        <is>
-          <t>T2-01</t>
-        </is>
-      </c>
-      <c r="B13" s="37" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="C13" s="37" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="37" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E13" s="37" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="F13" s="37" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G13" s="37" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="H13" s="37" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I13" s="37" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="J13" s="37" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="K13" s="44" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="L13" s="36" t="inlineStr">
-        <is>
-          <t>Tier 2, tier1 chưa xong -&gt; khóa</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="34" t="inlineStr">
-        <is>
-          <t>T2-02</t>
-        </is>
-      </c>
-      <c r="B14" s="34" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="C14" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" s="34" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E14" s="34" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="F14" s="34" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G14" s="34" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="H14" s="34" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="I14" s="34" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="J14" s="34" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="K14" s="45" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="L14" s="33" t="inlineStr">
-        <is>
-          <t>Tier 2, tier1 đã xong -&gt; mở khóa</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="37" t="inlineStr">
-        <is>
-          <t>T3-01</t>
-        </is>
-      </c>
-      <c r="B15" s="37" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="C15" s="37" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" s="37" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E15" s="37" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="F15" s="37" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G15" s="37" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H15" s="37" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I15" s="37" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="J15" s="37" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="K15" s="44" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="L15" s="36" t="inlineStr">
-        <is>
-          <t>Tier 3, tier1 chưa xong -&gt; khóa</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="34" t="inlineStr">
-        <is>
-          <t>T3-02</t>
-        </is>
-      </c>
-      <c r="B16" s="34" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="C16" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" s="34" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E16" s="34" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="F16" s="34" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G16" s="34" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H16" s="34" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="I16" s="34" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="J16" s="34" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="K16" s="44" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="L16" s="33" t="inlineStr">
-        <is>
-          <t>Tier 3, tier2 chưa xong -&gt; khóa</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="37" t="inlineStr">
-        <is>
-          <t>T3-03</t>
-        </is>
-      </c>
-      <c r="B17" s="37" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="C17" s="37" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" s="37" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E17" s="37" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="F17" s="37" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G17" s="37" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H17" s="37" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="I17" s="37" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="J17" s="37" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="K17" s="45" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="L17" s="36" t="inlineStr">
-        <is>
-          <t>Tier 3, tất cả done -&gt; mở khóa</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="34" t="inlineStr">
-        <is>
-          <t>DONE-01</t>
-        </is>
-      </c>
-      <c r="B18" s="34" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="C18" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" s="34" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E18" s="34" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="F18" s="34" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="G18" s="34" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H18" s="34" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I18" s="34" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="J18" s="34" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="K18" s="45" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="L18" s="33" t="inlineStr">
-        <is>
-          <t>Node đã completed -&gt; không khóa</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="37" t="inlineStr">
-        <is>
-          <t>T1-01</t>
-        </is>
-      </c>
-      <c r="B19" s="37" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="C19" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="37" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E19" s="37" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="F19" s="37" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G19" s="37" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H19" s="37" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I19" s="37" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="J19" s="37" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="K19" s="45" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="L19" s="36" t="inlineStr">
-        <is>
-          <t>Tier 1 -&gt; không bao giờ khóa</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A2:J2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="26" t="inlineStr">
-        <is>
-          <t>BẢNG B3 - ĐỘ BAO PHỦ TRƯỚC VÀ SAU KHI BỔ SUNG TEST</t>
-        </is>
-      </c>
-      <c r="B1" s="27" t="n"/>
-      <c r="C1" s="27" t="n"/>
-      <c r="D1" s="27" t="n"/>
-      <c r="E1" s="27" t="n"/>
-      <c r="F1" s="28" t="n"/>
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>State Transition Testing — bảng thứ ba: ba bước khai báo hồ sơ</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="29" t="inlineStr">
-        <is>
-          <t>Trước: baseline  |  Sau: kết quả clean test ngày 2026-09-06 (370 tests, 0 failures)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="30" t="inlineStr">
-        <is>
-          <t>A - BẢNG SO SÁNH CHỈ SỐ BAO PHỦ (JaCoCo)</t>
-        </is>
-      </c>
-      <c r="B4" s="27" t="n"/>
-      <c r="C4" s="27" t="n"/>
-      <c r="D4" s="27" t="n"/>
-      <c r="E4" s="27" t="n"/>
-      <c r="F4" s="28" t="n"/>
+      <c r="A2" s="53" t="inlineStr">
+        <is>
+          <t>OnboardingController, /onboarding/step1..3. Bảng thiết kế theo mẫu slide 39.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="54" t="inlineStr">
+        <is>
+          <t>TỔNG KẾT THI HÀNH — 12 test đã chạy, 12 PASS, 0 fail. Dòng ST-06 là test tham số hoá, chạy 5 lần cho 5 điểm vào nên 8 dòng thiết kế sinh ra 12 test thực tế.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="31" t="inlineStr">
-        <is>
-          <t>CHỈ SỐ BAO PHỦ</t>
-        </is>
-      </c>
-      <c r="B5" s="31" t="inlineStr">
-        <is>
-          <t>TRƯỚC</t>
-        </is>
-      </c>
-      <c r="C5" s="31" t="inlineStr">
-        <is>
-          <t>SAU</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="inlineStr">
-        <is>
-          <t>TĂNG (pp)</t>
-        </is>
-      </c>
-      <c r="E5" s="31" t="inlineStr">
-        <is>
-          <t>% TĂNG</t>
-        </is>
-      </c>
-      <c r="F5" s="31" t="inlineStr">
-        <is>
-          <t>NGUỒN</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Lớp test trong source</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Số test</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Kỹ thuật áp dụng</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="inlineStr">
-        <is>
-          <t>Bao phủ Instruction</t>
-        </is>
-      </c>
-      <c r="B6" s="40" t="inlineStr">
-        <is>
-          <t>60.1%</t>
-        </is>
-      </c>
-      <c r="C6" s="40" t="inlineStr">
-        <is>
-          <t>76.1%</t>
-        </is>
-      </c>
-      <c r="D6" s="45" t="inlineStr">
-        <is>
-          <t>+16.0 pp</t>
-        </is>
-      </c>
-      <c r="E6" s="40" t="inlineStr">
-        <is>
-          <t>+26.6%</t>
-        </is>
-      </c>
-      <c r="F6" s="40" t="inlineStr">
-        <is>
-          <t>JaCoCo</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="35" t="inlineStr">
-        <is>
-          <t>Bao phủ dòng lệnh (Line)</t>
-        </is>
-      </c>
-      <c r="B7" s="37" t="inlineStr">
-        <is>
-          <t>60.1%</t>
-        </is>
-      </c>
-      <c r="C7" s="37" t="inlineStr">
-        <is>
-          <t>75.5%</t>
-        </is>
-      </c>
-      <c r="D7" s="45" t="inlineStr">
-        <is>
-          <t>+15.4 pp</t>
-        </is>
-      </c>
-      <c r="E7" s="37" t="inlineStr">
-        <is>
-          <t>+25.6%</t>
-        </is>
-      </c>
-      <c r="F7" s="37" t="inlineStr">
-        <is>
-          <t>JaCoCo</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="38" t="inlineStr">
-        <is>
-          <t>Bao phủ nhánh (Branch)</t>
-        </is>
-      </c>
-      <c r="B8" s="40" t="inlineStr">
-        <is>
-          <t>48.2%</t>
-        </is>
-      </c>
-      <c r="C8" s="40" t="inlineStr">
-        <is>
-          <t>67.5%</t>
-        </is>
-      </c>
-      <c r="D8" s="45" t="inlineStr">
-        <is>
-          <t>+19.3 pp</t>
-        </is>
-      </c>
-      <c r="E8" s="40" t="inlineStr">
-        <is>
-          <t>+40.0%</t>
-        </is>
-      </c>
-      <c r="F8" s="40" t="inlineStr">
-        <is>
-          <t>JaCoCo</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="35" t="inlineStr">
-        <is>
-          <t>Độ phức tạp được phủ</t>
-        </is>
-      </c>
-      <c r="B9" s="37" t="inlineStr">
-        <is>
-          <t>53.4%</t>
-        </is>
-      </c>
-      <c r="C9" s="37" t="inlineStr">
-        <is>
-          <t>67.4%</t>
-        </is>
-      </c>
-      <c r="D9" s="45" t="inlineStr">
-        <is>
-          <t>+14.0 pp</t>
-        </is>
-      </c>
-      <c r="E9" s="37" t="inlineStr">
-        <is>
-          <t>+26.3%</t>
-        </is>
-      </c>
-      <c r="F9" s="37" t="inlineStr">
-        <is>
-          <t>JaCoCo</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>OnboardingStateTransitionTest</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Chuyển đổi trạng thái · 8 dòng thiết kế</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="55" t="inlineStr">
+        <is>
+          <t>Số test được đối chiếu tự động với target/surefire-reports khi sinh lại sheet bằng tools/gen_sheets_bo_sung.py — source chạy ra số khác thì script dừng và báo lỗi. Chạy lại để kiểm chứng:  mvnw test -Dtest=OnboardingStateTransitionTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>BẢNG 1 — MÁY TRẠNG THÁI NÀY KHÁC HAI MÁY TRƯỚC Ở ĐÂU</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="inlineStr">
-        <is>
-          <t>Số phương thức được phủ</t>
-        </is>
-      </c>
-      <c r="B10" s="40" t="inlineStr">
-        <is>
-          <t>65.1%</t>
-        </is>
-      </c>
-      <c r="C10" s="40" t="inlineStr">
-        <is>
-          <t>78.5%</t>
-        </is>
-      </c>
-      <c r="D10" s="45" t="inlineStr">
-        <is>
-          <t>+13.4 pp</t>
-        </is>
-      </c>
-      <c r="E10" s="40" t="inlineStr">
-        <is>
-          <t>+20.6%</t>
-        </is>
-      </c>
-      <c r="F10" s="40" t="inlineStr">
-        <is>
-          <t>JaCoCo</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Máy trạng thái</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Trạng thái nằm ở đâu</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Số trạng thái</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Đặc điểm riêng</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Tiến độ node kỹ năng</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Một cột enum ProgressStatus</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Đủ cả 6 cạnh hai chiều giữa 3 trạng thái</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr"/>
+    </row>
     <row r="12">
-      <c r="A12" s="30" t="inlineStr">
-        <is>
-          <t>B - KẾT QUẢ CHẠY TEST SUITE</t>
-        </is>
-      </c>
-      <c r="B12" s="27" t="n"/>
-      <c r="C12" s="27" t="n"/>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="27" t="n"/>
-      <c r="F12" s="28" t="n"/>
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Vòng đời token</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>04b</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Hai cờ boolean: used, expiresAt</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Một chiều — không cạnh nào đi ngược</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
-        <is>
-          <t>CHỈ SỐ</t>
-        </is>
-      </c>
-      <c r="B13" s="31" t="inlineStr">
-        <is>
-          <t>GIÁ TRỊ</t>
-        </is>
-      </c>
-      <c r="C13" s="31" t="inlineStr">
-        <is>
-          <t>NGƯỠNG</t>
-        </is>
-      </c>
-      <c r="D13" s="31" t="inlineStr">
-        <is>
-          <t>KẾT QUẢ</t>
-        </is>
-      </c>
-      <c r="E13" s="31" t="inlineStr">
-        <is>
-          <t>GHI CHÚ</t>
-        </is>
-      </c>
-      <c r="F13" s="31" t="inlineStr">
-        <is>
-          <t>NGUỒN</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="32" t="inlineStr">
-        <is>
-          <t>Tổng số test</t>
-        </is>
-      </c>
-      <c r="B14" s="34" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="C14" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="40" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Khai báo hồ sơ lần đầu</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>04c</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>TỔ HỢP nhiều cờ trên bản ghi User</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Có trạng thái HẤP THỤ: vào rồi không ra được</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="55" t="inlineStr">
+        <is>
+          <t>Điểm mới của bảng này: trạng thái KHÔNG nằm trong một cột enum mà là tổ hợp cờ targetRoleId + transcriptPath/githubUsername + onboardingCompleted. Phải tự đặt tên bốn trạng thái trước khi vẽ được sơ đồ — bước mà hai máy trước không cần làm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>BỐN TRẠNG THÁI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Tên trạng thái</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Định nghĩa bằng dữ liệu</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="61" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>MOI_TAO</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>onboardingCompleted = false, chưa qua bước nào</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>trạng thái khởi đầu</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="61" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>DA_CHON_NGHE</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>đã gửi bước 1</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="61" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>DA_NAP_NGUON</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>đã gửi bước 2 (bảng điểm và/hoặc GitHub)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="61" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>HOAN_TAT</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>onboardingCompleted = true</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="25" t="inlineStr">
+        <is>
+          <t>TRẠNG THÁI HẤP THỤ — không có đường ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>SƠ ĐỒ TRẠNG THÁI</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        S1 MOI_TAO  ──[POST step1, chọn nghề]──►  S2 DA_CHON_NGHE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         │    ▲                                          │</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         │    └──[không chọn gì] / [bấm Bỏ qua]          │  [POST step2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         │                                                ▼</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         └──────[GET step3, nhảy cóc]───────►  S3 DA_NAP_NGUON</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                          │  [POST step3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                          ▼</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                              S4 HOAN_TAT  ◄──┐</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                   │          │</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                   └──[mọi điểm vào]──┘  → chuyển hướng về /</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="55" t="inlineStr">
+        <is>
+          <t>Hai cạnh tự lặp ở S1 cùng đích nhưng KHÁC hành động, nên bảng bên dưới tách thành hai dòng ST-02 và ST-03. Cạnh vòng ở S4 là cạnh quan trọng nhất của cả sơ đồ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>BẢNG CHUYỂN TRẠNG THÁI — mẫu slide 39 · 5 cạnh hợp lệ, 2 nhóm cạnh bị chặn</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Test Case No.</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Start State</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Event / Input</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>End State / Exp Output</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Hợp lệ</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Tác dụng phụ kiểm chứng</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Method trong code</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>ST-01</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>MOI_TAO</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>POST step1 — chọn nghề hợp lệ</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>DA_CHON_NGHE</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>Gọi setTargetRole, chuyển sang bước 2</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E14" s="33" t="inlineStr">
-        <is>
-          <t>Bao gồm unit + slice tests</t>
-        </is>
-      </c>
-      <c r="F14" s="33" t="inlineStr">
-        <is>
-          <t>Maven Surefire</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="35" t="inlineStr">
-        <is>
-          <t>Test thất bại</t>
-        </is>
-      </c>
-      <c r="B15" s="37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C15" s="37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D15" s="40" t="inlineStr">
+      <c r="H38" s="58" t="inlineStr">
+        <is>
+          <t>st01_moiTao_chonNghe_sangBuoc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>ST-02</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>MOI_TAO</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>POST step1 — không chọn gì</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>MOI_TAO (tự lặp)</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Hiện lỗi 'Vui lòng chọn một vị trí nghề nghiệp.', KHÔNG ghi hồ sơ</t>
+        </is>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E15" s="36" t="inlineStr">
-        <is>
-          <t>Không có test nào bị đỏ</t>
-        </is>
-      </c>
-      <c r="F15" s="36" t="inlineStr">
-        <is>
-          <t>Maven Surefire</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="32" t="inlineStr">
-        <is>
-          <t>Branch coverage</t>
-        </is>
-      </c>
-      <c r="B16" s="34" t="inlineStr">
-        <is>
-          <t>67.5%</t>
-        </is>
-      </c>
-      <c r="C16" s="34" t="inlineStr">
-        <is>
-          <t>65%</t>
-        </is>
-      </c>
-      <c r="D16" s="40" t="inlineStr">
+      <c r="H39" s="58" t="inlineStr">
+        <is>
+          <t>st02_moiTao_khongChonGi_tuLap</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>ST-03</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>MOI_TAO</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>POST step1 — bấm Bỏ qua</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>MOI_TAO (tự lặp)</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Sang bước 2 nhưng KHÔNG lưu định hướng, không báo lỗi</t>
+        </is>
+      </c>
+      <c r="G40" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E16" s="33" t="inlineStr">
-        <is>
-          <t>Vượt ngưỡng JaCoCo check</t>
-        </is>
-      </c>
-      <c r="F16" s="33" t="inlineStr">
-        <is>
-          <t>JaCoCo</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="35" t="inlineStr">
-        <is>
-          <t>Line coverage</t>
-        </is>
-      </c>
-      <c r="B17" s="37" t="inlineStr">
-        <is>
-          <t>75.5%</t>
-        </is>
-      </c>
-      <c r="C17" s="37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="40" t="inlineStr">
+      <c r="H40" s="58" t="inlineStr">
+        <is>
+          <t>st03_moiTao_boQua_tuLap</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>ST-04</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>DA_CHON_NGHE</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>POST step2 — không nạp gì</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>DA_NAP_NGUON</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Không gọi storeTranscript, không gọi setGithub — bước 2 hoàn toàn tuỳ chọn</t>
+        </is>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E17" s="36" t="inlineStr">
-        <is>
-          <t>Không đặt ngưỡng riêng</t>
-        </is>
-      </c>
-      <c r="F17" s="36" t="inlineStr">
-        <is>
-          <t>JaCoCo</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="32" t="inlineStr">
-        <is>
-          <t>Kết quả build</t>
-        </is>
-      </c>
-      <c r="B18" s="34" t="inlineStr">
-        <is>
-          <t>BUILD SUCCESS</t>
-        </is>
-      </c>
-      <c r="C18" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D18" s="40" t="inlineStr">
+      <c r="H41" s="58" t="inlineStr">
+        <is>
+          <t>st04_daChonNghe_napNguon_sangBuoc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>ST-05</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>DA_NAP_NGUON</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>POST step3 — chọn kỹ năng</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>HOAN_TAT</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Gọi replaceSkills rồi completeOnboarding, về trang chủ</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E18" s="33" t="inlineStr">
-        <is>
-          <t>mvn clean test thành công</t>
-        </is>
-      </c>
-      <c r="F18" s="33" t="inlineStr">
-        <is>
-          <t>Maven</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="30" t="inlineStr">
-        <is>
-          <t>C - NHẬN XÉT VÀ KẾT LUẬN</t>
-        </is>
-      </c>
-      <c r="B20" s="27" t="n"/>
-      <c r="C20" s="27" t="n"/>
-      <c r="D20" s="27" t="n"/>
-      <c r="E20" s="27" t="n"/>
-      <c r="F20" s="28" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="31" t="inlineStr">
-        <is>
-          <t>VẤN ĐỀ</t>
-        </is>
-      </c>
-      <c r="B21" s="31" t="inlineStr">
-        <is>
-          <t>NỘI DUNG NHẬN XÉT</t>
-        </is>
-      </c>
-      <c r="C21" s="27" t="n"/>
-      <c r="D21" s="27" t="n"/>
-      <c r="E21" s="27" t="n"/>
-      <c r="F21" s="28" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="32" t="inlineStr">
-        <is>
-          <t>Branch coverage tăng 19.3 pp (48.2% -&gt; 67.5%)</t>
-        </is>
-      </c>
-      <c r="B22" s="33" t="inlineStr">
-        <is>
-          <t>Đây là mức tăng lớn nhất, cho thấy việc bổ sung test white-box đã bao phủ được nhiều nhánh if/else bị bỏ sót.</t>
-        </is>
-      </c>
-      <c r="C22" s="27" t="n"/>
-      <c r="D22" s="27" t="n"/>
-      <c r="E22" s="27" t="n"/>
-      <c r="F22" s="28" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="35" t="inlineStr">
-        <is>
-          <t>370 test, 0 failures</t>
-        </is>
-      </c>
-      <c r="B23" s="36" t="inlineStr">
-        <is>
-          <t>Toàn bộ bộ test ổn định, không có regression (lỗi hồi quy).</t>
-        </is>
-      </c>
-      <c r="C23" s="27" t="n"/>
-      <c r="D23" s="27" t="n"/>
-      <c r="E23" s="27" t="n"/>
-      <c r="F23" s="28" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="32" t="inlineStr">
-        <is>
-          <t>Branch gate 65% đạt (67.5%)</t>
-        </is>
-      </c>
-      <c r="B24" s="33" t="inlineStr">
-        <is>
-          <t>JaCoCo check sẽ fail build nếu branch &lt; 65%. Project vượt ngưỡng này, đảm bảo CI/CD hoạt động trơn tru.</t>
-        </is>
-      </c>
-      <c r="C24" s="27" t="n"/>
-      <c r="D24" s="27" t="n"/>
-      <c r="E24" s="27" t="n"/>
-      <c r="F24" s="28" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="35" t="inlineStr">
-        <is>
-          <t>GlobalExceptionHandler 100%</t>
-        </is>
-      </c>
-      <c r="B25" s="36" t="inlineStr">
-        <is>
-          <t>File mới thêm đã được test đầy đủ 16/16 nhánh, 158/158 instruction.</t>
-        </is>
-      </c>
-      <c r="C25" s="27" t="n"/>
-      <c r="D25" s="27" t="n"/>
-      <c r="E25" s="27" t="n"/>
-      <c r="F25" s="28" t="n"/>
+      <c r="H42" s="58" t="inlineStr">
+        <is>
+          <t>st05_daNapNguon_chonKyNang_hoanTat</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>ST-06</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>HOAN_TAT</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>GET step1 / GET step2 / GET step3 / POST step1 / POST step2</t>
+        </is>
+      </c>
+      <c r="D43" s="25" t="inlineStr">
+        <is>
+          <t>Bị chặn — chuyển hướng về /</t>
+        </is>
+      </c>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>KHÔNG</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>5 điểm vào, không điểm nào đụng vào hồ sơ đã hoàn tất</t>
+        </is>
+      </c>
+      <c r="G43" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H43" s="58" t="inlineStr">
+        <is>
+          <t>st06_hoanTat_moiDiemVaoBiChan</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>ST-07</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>HOAN_TAT</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>POST step3 lần nữa</t>
+        </is>
+      </c>
+      <c r="D44" s="25" t="inlineStr">
+        <is>
+          <t>Bị chặn — chuyển hướng về /</t>
+        </is>
+      </c>
+      <c r="E44" s="20" t="inlineStr">
+        <is>
+          <t>KHÔNG</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>KHÔNG gọi replaceSkills — danh sách kỹ năng cũ nguyên vẹn</t>
+        </is>
+      </c>
+      <c r="G44" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H44" s="58" t="inlineStr">
+        <is>
+          <t>st07_hoanTat_guiLaiBuoc3_khongXoaKyNang</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>ST-08</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>MOI_TAO</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>GET step3 — nhảy cóc bỏ bước 1 và 2</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>MOI_TAO — vào được</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Hiển thị bước 3 với currentStep = 3 (hành vi CỐ Ý, xem ghi chú)</t>
+        </is>
+      </c>
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H45" s="58" t="inlineStr">
+        <is>
+          <t>st08_moiTao_nhayCocSangBuoc3_duocPhep</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>TIÊU CHÍ ĐỦ VÀ HAI GHI CHÚ QUAN TRỌNG</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="44" customHeight="1">
+      <c r="A48" s="56" t="inlineStr">
+        <is>
+          <t>TIÊU CHÍ ĐỦ: phủ hết cạnh của sơ đồ. ST-01 → ST-05 phủ trọn đường đi thuận S1 → S2 → S3 → S4, cộng hai cạnh tự lặp. ST-06 và ST-07 phủ cạnh vòng ở trạng thái hấp thụ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="44" customHeight="1">
+      <c r="A49" s="56" t="inlineStr">
+        <is>
+          <t>ST-06 VÀ ST-07 LÀ PHẦN ĐẮT GIÁ NHẤT. S4 phải là trạng thái hấp thụ: cả SÁU điểm vào (GET và POST của ba bước) đều phải chặn — ST-06 phủ năm điểm, ST-07 phủ điểm thứ sáu. Tách riêng vì nếu bỏ sót chốt chặn ở đúng điểm thứ sáu ấy — POST step3 — thì replaceSkills() sẽ XOÁ SẠCH danh sách kỹ năng người dùng đã chọn. Kiểm thử chỉ đi đường thuận không bao giờ chạm tới cạnh này, vì đường thuận kết thúc ngay khi vào S4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="44" customHeight="1">
+      <c r="A50" s="56" t="inlineStr">
+        <is>
+          <t>ST-08 — ĐIỀU ĐÃ KIỂM CHỨNG VÀ BÁC BỎ. Ban đầu việc GET step3 thiếu chốt chặn bị NGHI là khiếm khuyết: gõ thẳng URL là vào được bước 3 mà chưa qua bước 1 và 2. Dựng máy trạng thái xong mới thấy KHÔNG phải lỗi — bước 1 có sẵn nút 'Bỏ qua' (skip=true) và mọi trường ở bước 2 đều tuỳ chọn, nên đi đúng luồng giao diện cũng tới được bước 3 với hồ sơ trống. Nhảy cóc không giành thêm quyền gì. ST-08 được giữ lại làm test hồi quy, chốt rằng đây là hành vi CỐ Ý chứ không phải sơ suất.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="44" customHeight="1">
+      <c r="A51" s="56" t="inlineStr">
+        <is>
+          <t>Ghi ST-08 vào báo cáo dù nó KHÔNG tìm ra lỗi là có chủ đích: một nghi vấn đã kiểm chứng và bác bỏ cũng là kết quả kiểm thử. Nếu về sau ai đó thêm chốt chặn vào GET step3 mà không hiểu ngữ cảnh, test này đỏ và buộc họ đọc lại lý do.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="44" customHeight="1">
+      <c r="A52" s="56" t="inlineStr">
+        <is>
+          <t>GHI CHÚ VỀ ĐIỀU KIỆN CANH: giống bảng ở sheet 04 và 04b, điều kiện phụ được gộp vào cột Event / Input chứ không tách thành cột riêng — giữ đúng bốn cột lõi của slide 39.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="A20:F20"/>
+  <mergeCells count="24">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BaoCao-KiemThu-CareerCompass.xlsx
+++ b/BaoCao-KiemThu-CareerCompass.xlsx
@@ -9,21 +9,20 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00. Tong quan" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01. BVA + Equiv Partition" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01c. BVA Tieu de Mentor" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03. Decision Table (PhanA)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03b. Decision Table Token" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03c. Decision Table Tep" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04. State Transition (PhanA)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04b. State Transition Token" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04c. State Transition Onboard" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B1_CFG_va_Basis_Path" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B2_Coverage_Levels" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B3_Truoc_va_Sau" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B4_Coverage_Per_Class" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B5_Danh_Sach_Test_Whitebox" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05. API - Postman" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06. E2E - CodeceptJS" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07. Khiem khuyet" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03. Decision Table (PhanA)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03b. Decision Table Token" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03c. Decision Table Tep" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04. State Transition (PhanA)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04b. State Transition Token" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04c. State Transition Onboard" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B1_CFG_va_Basis_Path" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B2_Coverage_Levels" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B3_Truoc_va_Sau" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B4_Coverage_Per_Class" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B5_Danh_Sach_Test_Whitebox" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05. API - Postman" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06. E2E - CodeceptJS" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07. Khiem khuyet" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -902,7 +901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1102,7 +1101,7 @@
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Giá trị biên — ngưỡng cắt tiêu đề</t>
+          <t>Bảng quyết định</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -1111,7 +1110,7 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
@@ -1120,12 +1119,12 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>9 / 9</t>
+          <t>10 / 10</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>01c</t>
+          <t>03, 03b</t>
         </is>
       </c>
       <c r="G10" s="8" t="n"/>
@@ -1134,7 +1133,7 @@
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Bảng quyết định</t>
+          <t>Bảng quyết định — tệp bảng điểm</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -1143,7 +1142,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -1152,12 +1151,12 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>10 / 10</t>
+          <t>9 / 9</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>03, 03b</t>
+          <t>03c</t>
         </is>
       </c>
       <c r="G11" s="8" t="n"/>
@@ -1166,7 +1165,7 @@
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Bảng quyết định — tệp bảng điểm</t>
+          <t>Chuyển đổi trạng thái — tiến độ node</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -1189,7 +1188,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>03c</t>
+          <t>04</t>
         </is>
       </c>
       <c r="G12" s="8" t="n"/>
@@ -1198,7 +1197,7 @@
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Chuyển đổi trạng thái — tiến độ node</t>
+          <t>Chuyển đổi trạng thái — vòng đời token</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -1207,7 +1206,7 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
@@ -1216,12 +1215,12 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>9 / 9</t>
+          <t>7 / 7</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>04b</t>
         </is>
       </c>
       <c r="G13" s="8" t="n"/>
@@ -1230,7 +1229,7 @@
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Chuyển đổi trạng thái — vòng đời token</t>
+          <t>Chuyển đổi trạng thái — khai báo hồ sơ</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -1239,7 +1238,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
@@ -1248,12 +1247,12 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>7 / 7</t>
+          <t>12 / 12</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>04b</t>
+          <t>04c</t>
         </is>
       </c>
       <c r="G14" s="8" t="n"/>
@@ -1262,7 +1261,7 @@
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Chuyển đổi trạng thái — khai báo hồ sơ</t>
+          <t>Hộp trắng — đường cơ sở, CFG</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -1270,22 +1269,24 @@
           <t>Đơn vị</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n">
-        <v>12</v>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>xem B5</t>
+        </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>JUnit 5</t>
+          <t>JUnit 5 + JaCoCo</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>12 / 12</t>
+          <t>đạt</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>04c</t>
+          <t>B1 → B5</t>
         </is>
       </c>
       <c r="G15" s="8" t="n"/>
@@ -1294,32 +1295,32 @@
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Hộp trắng — đường cơ sở, CFG</t>
+          <t>Kiểm thử API</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Đơn vị</t>
+          <t>Tích hợp</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>xem B5</t>
+          <t>92 case</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>JUnit 5 + JaCoCo</t>
+          <t>Postman / Newman</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>đạt</t>
+          <t>358 phép kiểm</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>B1 → B5</t>
+          <t>05</t>
         </is>
       </c>
       <c r="G16" s="8" t="n"/>
@@ -1328,126 +1329,121 @@
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Kiểm thử API</t>
+          <t>Kiểm thử giao diện đầu-cuối</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Tích hợp</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>92 case</t>
-        </is>
+          <t>Hệ thống</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>17</v>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Postman / Newman</t>
+          <t>CodeceptJS + Playwright</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>358 phép kiểm</t>
+          <t>17 / 17</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>06</t>
         </is>
       </c>
       <c r="G17" s="8" t="n"/>
       <c r="H17" s="9" t="n"/>
     </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Kiểm thử giao diện đầu-cuối</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Hệ thống</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>CodeceptJS + Playwright</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>17 / 17</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="9" t="n"/>
-    </row>
-    <row r="19"/>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="18"/>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>BẢNG 2 — ĐỘ BAO PHỦ MÃ NGUỒN (JaCoCo)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Chỉ số</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Trước</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Sau</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Tăng</t>
         </is>
       </c>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Nguồn</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Dòng lệnh (Line)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>60,1%</t>
+        </is>
+      </c>
+      <c r="C21" s="63" t="inlineStr">
+        <is>
+          <t>78,6%</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>+18,5 điểm</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>docs/coverage/index.html</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="n"/>
+      <c r="H21" s="9" t="n"/>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Dòng lệnh (Line)</t>
+          <t>Nhánh (Branch)</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="C22" s="63" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>+18,5 điểm</t>
+          <t>+24,3 điểm</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -1461,22 +1457,22 @@
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Nhánh (Branch)</t>
+          <t>Độ phức tạp được phủ</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="C23" s="63" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>+24,3 điểm</t>
+          <t>+17,6 điểm</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -1490,22 +1486,22 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Độ phức tạp được phủ</t>
+          <t>Phương thức</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="C24" s="63" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>+17,6 điểm</t>
+          <t>+16,1 điểm</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -1516,93 +1512,89 @@
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="9" t="n"/>
     </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Phương thức</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>65,1%</t>
-        </is>
-      </c>
-      <c r="C25" s="63" t="inlineStr">
-        <is>
-          <t>81,2%</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>+16,1 điểm</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>docs/coverage/index.html</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="n"/>
-      <c r="H25" s="9" t="n"/>
-    </row>
-    <row r="26"/>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="25"/>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>BẢNG 3 — TỔNG SỐ PHÉP KIỂM ĐÃ CHẠY</t>
         </is>
       </c>
     </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Tầng</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Đơn vị đếm</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Số lượng</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Không đạt</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+    </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Tầng</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Đơn vị đếm</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Số lượng</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Không đạt</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Ghi chú</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Đơn vị (JUnit)</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>test method</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>399</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Toàn bộ dự án, gồm cả hộp đen và hộp trắng</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="n"/>
+      <c r="H28" s="9" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>Đơn vị (JUnit)</t>
+          <t>Tích hợp (Postman)</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>test method</t>
+          <t>phép kiểm</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>408</v>
+        <v>358</v>
       </c>
       <c r="D29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Toàn bộ dự án, gồm cả hộp đen và hộp trắng</t>
+          <t>Chạy trên cơ sở dữ liệu vừa gieo lại</t>
         </is>
       </c>
       <c r="G29" s="8" t="n"/>
@@ -1611,85 +1603,59 @@
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>Tích hợp (Postman)</t>
+          <t>Hệ thống (CodeceptJS)</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>phép kiểm</t>
+          <t>kịch bản</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>358</v>
+        <v>17</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Chạy trên cơ sở dữ liệu vừa gieo lại</t>
+          <t>Ba kịch bản từng đỏ đều là lỗi ứng dụng thật, nay đã sửa xong</t>
         </is>
       </c>
       <c r="G30" s="8" t="n"/>
       <c r="H30" s="9" t="n"/>
     </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>Hệ thống (CodeceptJS)</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>kịch bản</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="D31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Ba kịch bản từng đỏ đều là lỗi ứng dụng thật, nay đã sửa xong</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="n"/>
-      <c r="H31" s="9" t="n"/>
-    </row>
-    <row r="32"/>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
+    <row r="31"/>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>Mười một khiếm khuyết được phát hiện và đều đã khắc phục kèm test hồi quy. Chi tiết ở sheet 07. Khiem khuyet.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="F18:H18"/>
+  <mergeCells count="23">
+    <mergeCell ref="F21:H21"/>
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="F22:H22"/>
     <mergeCell ref="F13:H13"/>
-    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F30:H30"/>
     <mergeCell ref="F9:H9"/>
-    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A26:H26"/>
     <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A32:H32"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="F11:H11"/>
-    <mergeCell ref="F25:H25"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="F16:H16"/>
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="F6:H6"/>
-    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A19:H19"/>
     <mergeCell ref="F12:H12"/>
-    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F7:H7"/>
     <mergeCell ref="F15:H15"/>
     <mergeCell ref="F24:H24"/>
   </mergeCells>
@@ -1698,672 +1664,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="26" t="inlineStr">
-        <is>
-          <t>BẢNG B1 - ĐỒ THỊ LUỒNG ĐIỀU KHIỂN (CFG) VÀ ĐỘ PHỨC TẠP CYCLOMATIC</t>
-        </is>
-      </c>
-      <c r="B1" s="27" t="n"/>
-      <c r="C1" s="27" t="n"/>
-      <c r="D1" s="27" t="n"/>
-      <c r="E1" s="27" t="n"/>
-      <c r="F1" s="27" t="n"/>
-      <c r="G1" s="27" t="n"/>
-      <c r="H1" s="27" t="n"/>
-      <c r="I1" s="28" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="29" t="inlineStr">
-        <is>
-          <t>Nguồn: RoadmapService.java  |  Hai hàm được phân tích: calculatePercent() và isNodeLocked()</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="30" t="inlineStr">
-        <is>
-          <t>A - BẢNG CHỈ SỐ CFG (Control Flow Graph Metrics)</t>
-        </is>
-      </c>
-      <c r="B4" s="27" t="n"/>
-      <c r="C4" s="27" t="n"/>
-      <c r="D4" s="27" t="n"/>
-      <c r="E4" s="27" t="n"/>
-      <c r="F4" s="27" t="n"/>
-      <c r="G4" s="27" t="n"/>
-      <c r="H4" s="27" t="n"/>
-      <c r="I4" s="28" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="31" t="inlineStr">
-        <is>
-          <t>HÀM</t>
-        </is>
-      </c>
-      <c r="B5" s="31" t="inlineStr">
-        <is>
-          <t>File nguồn</t>
-        </is>
-      </c>
-      <c r="C5" s="31" t="inlineStr">
-        <is>
-          <t>Nút (N)</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="inlineStr">
-        <is>
-          <t>Cạnh (E)</t>
-        </is>
-      </c>
-      <c r="E5" s="31" t="inlineStr">
-        <is>
-          <t>Nút điều kiện (P)</t>
-        </is>
-      </c>
-      <c r="F5" s="31" t="inlineStr">
-        <is>
-          <t>Miền (R)</t>
-        </is>
-      </c>
-      <c r="G5" s="31" t="inlineStr">
-        <is>
-          <t>V(G)=E-N+2</t>
-        </is>
-      </c>
-      <c r="H5" s="31" t="inlineStr">
-        <is>
-          <t>V(G)=P+1</t>
-        </is>
-      </c>
-      <c r="I5" s="31" t="inlineStr">
-        <is>
-          <t>Số test tối thiểu</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="32" t="inlineStr">
-        <is>
-          <t>calculatePercent()</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="inlineStr">
-        <is>
-          <t>RoadmapService.java</t>
-        </is>
-      </c>
-      <c r="C6" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" s="34" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="35" t="inlineStr">
-        <is>
-          <t>isNodeLocked()</t>
-        </is>
-      </c>
-      <c r="B7" s="36" t="inlineStr">
-        <is>
-          <t>RoadmapService.java</t>
-        </is>
-      </c>
-      <c r="C7" s="37" t="n">
-        <v>14</v>
-      </c>
-      <c r="D7" s="37" t="n">
-        <v>19</v>
-      </c>
-      <c r="E7" s="37" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" s="37" t="n">
-        <v>7</v>
-      </c>
-      <c r="G7" s="37" t="n">
-        <v>7</v>
-      </c>
-      <c r="H7" s="37" t="n">
-        <v>7</v>
-      </c>
-      <c r="I7" s="37" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="30" t="inlineStr">
-        <is>
-          <t>B - DANH SÁCH ĐƯỜNG CƠ SỞ (BASIS PATHS)</t>
-        </is>
-      </c>
-      <c r="B9" s="27" t="n"/>
-      <c r="C9" s="27" t="n"/>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="27" t="n"/>
-      <c r="F9" s="27" t="n"/>
-      <c r="G9" s="27" t="n"/>
-      <c r="H9" s="27" t="n"/>
-      <c r="I9" s="28" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="31" t="inlineStr">
-        <is>
-          <t>HÀM</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="inlineStr">
-        <is>
-          <t>Path ID</t>
-        </is>
-      </c>
-      <c r="C10" s="31" t="inlineStr">
-        <is>
-          <t>Điều kiện</t>
-        </is>
-      </c>
-      <c r="D10" s="31" t="inlineStr">
-        <is>
-          <t>Chi tiết luồng thực thi</t>
-        </is>
-      </c>
-      <c r="E10" s="31" t="inlineStr">
-        <is>
-          <t>Kết quả mong đợi</t>
-        </is>
-      </c>
-      <c r="F10" s="31" t="inlineStr">
-        <is>
-          <t>Test Method</t>
-        </is>
-      </c>
-      <c r="G10" s="31" t="inlineStr">
-        <is>
-          <t>Input ví dụ</t>
-        </is>
-      </c>
-      <c r="H10" s="31" t="inlineStr">
-        <is>
-          <t>Output</t>
-        </is>
-      </c>
-      <c r="I10" s="31" t="inlineStr">
-        <is>
-          <t>Pass/Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="32" t="inlineStr">
-        <is>
-          <t>calculatePercent()</t>
-        </is>
-      </c>
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C11" s="33" t="inlineStr">
-        <is>
-          <t>total==0 TRUE</t>
-        </is>
-      </c>
-      <c r="D11" s="33" t="inlineStr">
-        <is>
-          <t>Start -&gt; [total==0 TRUE] -&gt; return 0.0 -&gt; End</t>
-        </is>
-      </c>
-      <c r="E11" s="33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F11" s="33" t="inlineStr">
-        <is>
-          <t>calculatePercent_totalZero</t>
-        </is>
-      </c>
-      <c r="G11" s="33" t="inlineStr">
-        <is>
-          <t>completed=0, total=0</t>
-        </is>
-      </c>
-      <c r="H11" s="34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I11" s="34" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="35" t="inlineStr">
-        <is>
-          <t>calculatePercent()</t>
-        </is>
-      </c>
-      <c r="B12" s="37" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C12" s="36" t="inlineStr">
-        <is>
-          <t>total==0 FALSE</t>
-        </is>
-      </c>
-      <c r="D12" s="36" t="inlineStr">
-        <is>
-          <t>Start -&gt; [total==0 FALSE] -&gt; return Math.round -&gt; End</t>
-        </is>
-      </c>
-      <c r="E12" s="36" t="inlineStr">
-        <is>
-          <t>% hợp lệ</t>
-        </is>
-      </c>
-      <c r="F12" s="36" t="inlineStr">
-        <is>
-          <t>calculatePercent_normalCase</t>
-        </is>
-      </c>
-      <c r="G12" s="36" t="inlineStr">
-        <is>
-          <t>completed=5, total=10</t>
-        </is>
-      </c>
-      <c r="H12" s="37" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="I12" s="37" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="32" t="inlineStr">
-        <is>
-          <t>isNodeLocked()</t>
-        </is>
-      </c>
-      <c r="B13" s="34" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C13" s="33" t="inlineStr">
-        <is>
-          <t>tier null -&gt; tier=1, tier&lt;=1 TRUE</t>
-        </is>
-      </c>
-      <c r="D13" s="33" t="inlineStr">
-        <is>
-          <t>Start -&gt; [tier null-&gt;1] -&gt; [tier&lt;=1 TRUE] -&gt; return false -&gt; End</t>
-        </is>
-      </c>
-      <c r="E13" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F13" s="33" t="inlineStr">
-        <is>
-          <t>isNodeLocked_tier1Null</t>
-        </is>
-      </c>
-      <c r="G13" s="33" t="inlineStr">
-        <is>
-          <t>node.tier=null</t>
-        </is>
-      </c>
-      <c r="H13" s="34" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I13" s="34" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="35" t="inlineStr">
-        <is>
-          <t>isNodeLocked()</t>
-        </is>
-      </c>
-      <c r="B14" s="37" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C14" s="36" t="inlineStr">
-        <is>
-          <t>tier=1, tier&lt;=1 TRUE</t>
-        </is>
-      </c>
-      <c r="D14" s="36" t="inlineStr">
-        <is>
-          <t>Start -&gt; [tier=1] -&gt; [tier&lt;=1 TRUE] -&gt; return false -&gt; End</t>
-        </is>
-      </c>
-      <c r="E14" s="36" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F14" s="36" t="inlineStr">
-        <is>
-          <t>isNodeLocked_explicitTier1</t>
-        </is>
-      </c>
-      <c r="G14" s="36" t="inlineStr">
-        <is>
-          <t>node.tier=1</t>
-        </is>
-      </c>
-      <c r="H14" s="37" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I14" s="37" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="32" t="inlineStr">
-        <is>
-          <t>isNodeLocked()</t>
-        </is>
-      </c>
-      <c r="B15" s="34" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C15" s="33" t="inlineStr">
-        <is>
-          <t>tier=2, tất cả tier1 DONE</t>
-        </is>
-      </c>
-      <c r="D15" s="33" t="inlineStr">
-        <is>
-          <t>Start -&gt; [tier=2] -&gt; doneNodeIds đầy đủ -&gt; anyMatch=FALSE -&gt; return false</t>
-        </is>
-      </c>
-      <c r="E15" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F15" s="33" t="inlineStr">
-        <is>
-          <t>isNodeLocked_tier2AllDone</t>
-        </is>
-      </c>
-      <c r="G15" s="33" t="inlineStr">
-        <is>
-          <t>node.tier=2, tier1 DONE</t>
-        </is>
-      </c>
-      <c r="H15" s="34" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I15" s="34" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="35" t="inlineStr">
-        <is>
-          <t>isNodeLocked()</t>
-        </is>
-      </c>
-      <c r="B16" s="37" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="C16" s="36" t="inlineStr">
-        <is>
-          <t>tier=2, tier1 chưa DONE</t>
-        </is>
-      </c>
-      <c r="D16" s="36" t="inlineStr">
-        <is>
-          <t>Start -&gt; [tier=2] -&gt; doneNodeIds thiếu -&gt; anyMatch=TRUE -&gt; return true</t>
-        </is>
-      </c>
-      <c r="E16" s="36" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F16" s="36" t="inlineStr">
-        <is>
-          <t>isNodeLocked_tier2NotDone</t>
-        </is>
-      </c>
-      <c r="G16" s="36" t="inlineStr">
-        <is>
-          <t>node.tier=2, tier1 chưa DONE</t>
-        </is>
-      </c>
-      <c r="H16" s="37" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I16" s="37" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="32" t="inlineStr">
-        <is>
-          <t>isNodeLocked()</t>
-        </is>
-      </c>
-      <c r="B17" s="34" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="C17" s="33" t="inlineStr">
-        <is>
-          <t>tier=3, tier1 chưa DONE</t>
-        </is>
-      </c>
-      <c r="D17" s="33" t="inlineStr">
-        <is>
-          <t>Start -&gt; [tier=3] -&gt; anyMatch(tier&lt;3 AND !done)=TRUE -&gt; return true</t>
-        </is>
-      </c>
-      <c r="E17" s="33" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F17" s="33" t="inlineStr">
-        <is>
-          <t>isNodeLocked_tier3Tier1NotDone</t>
-        </is>
-      </c>
-      <c r="G17" s="33" t="inlineStr">
-        <is>
-          <t>node.tier=3, tier1 chưa DONE</t>
-        </is>
-      </c>
-      <c r="H17" s="34" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I17" s="34" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="35" t="inlineStr">
-        <is>
-          <t>isNodeLocked()</t>
-        </is>
-      </c>
-      <c r="B18" s="37" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="C18" s="36" t="inlineStr">
-        <is>
-          <t>tier=3, tier2 chưa DONE</t>
-        </is>
-      </c>
-      <c r="D18" s="36" t="inlineStr">
-        <is>
-          <t>Start -&gt; [tier=3] -&gt; anyMatch(tier2 NOT done)=TRUE -&gt; return true</t>
-        </is>
-      </c>
-      <c r="E18" s="36" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F18" s="36" t="inlineStr">
-        <is>
-          <t>isNodeLocked_tier3Tier2NotDone</t>
-        </is>
-      </c>
-      <c r="G18" s="36" t="inlineStr">
-        <is>
-          <t>node.tier=3, tier2 chưa DONE</t>
-        </is>
-      </c>
-      <c r="H18" s="37" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I18" s="37" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="32" t="inlineStr">
-        <is>
-          <t>isNodeLocked()</t>
-        </is>
-      </c>
-      <c r="B19" s="34" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="C19" s="33" t="inlineStr">
-        <is>
-          <t>tier=3, tất cả done</t>
-        </is>
-      </c>
-      <c r="D19" s="33" t="inlineStr">
-        <is>
-          <t>Start -&gt; [tier=3] -&gt; anyMatch=FALSE -&gt; return false</t>
-        </is>
-      </c>
-      <c r="E19" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F19" s="33" t="inlineStr">
-        <is>
-          <t>isNodeLocked_tier3AllDone</t>
-        </is>
-      </c>
-      <c r="G19" s="33" t="inlineStr">
-        <is>
-          <t>node.tier=3, tất cả DONE</t>
-        </is>
-      </c>
-      <c r="H19" s="34" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I19" s="34" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A9:I9"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3196,7 +2496,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3749,7 +3049,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6338,7 +5638,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7245,7 +6545,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7946,7 +7246,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8726,7 +8026,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11475,780 +10775,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>BVA — bảng thứ hai: ngưỡng cắt tiêu đề phiên trò chuyện</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="53" t="inlineStr">
-        <is>
-          <t>MentorService.sendMessage(). Bảng thiết kế theo mẫu slide 23 và 24, trường hợp một biến (n = 1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="54" t="inlineStr">
-        <is>
-          <t>TỔNG KẾT THI HÀNH — 9 test đã chạy, 9 PASS, 0 fail. 7 case thuộc bảng giá trị biên, 2 case kiểm tra bổ sung ngoài bảng.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Lớp test trong source</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Số test</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Kỹ thuật áp dụng</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>MentorTitleStandardBvaTest</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Standard + Robustness BVA · 1 biến</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="55" t="inlineStr">
-        <is>
-          <t>Số test được đối chiếu tự động với target/surefire-reports khi sinh lại sheet bằng tools/gen_sheets_bo_sung.py — source chạy ra số khác thì script dừng và báo lỗi. Chạy lại để kiểm chứng:  mvnw test -Dtest=MentorTitleStandardBvaTest</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>VÌ SAO CHỌN HÀM NÀY LÀM ĐỐI TƯỢNG BVA THỨ HAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="56" t="inlineStr">
-        <is>
-          <t>Toàn bộ ràng buộc @Size của dự án đều nằm ở RegisterFormDTO và đã phủ trọn ở sheet 01. Muốn tìm thêm biên phải soi các NGƯỠNG CỨNG viết thẳng trong tầng service.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="56" t="inlineStr">
-        <is>
-          <t>Ngưỡng 60 ký tự này là ngưỡng sạch nhất trong số đó: một biến duy nhất, một phép so sánh, kết quả quan sát trực tiếp bằng chuỗi tiêu đề — không phải gọi dịch vụ ngoài, không phải dựng tệp PDF giả như các ngưỡng 6000 / 3000 / 200 ở TranscriptAnalysisService và PortfolioService.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="56" t="inlineStr">
-        <is>
-          <t>Giá trị của phép thử: lỗi lệch-một-đơn-vị ở substring là lỗi kinh điển. Mã nguồn dùng '&gt;' chứ không phải '&gt;=', nên chuỗi dài ĐÚNG 60 ký tự phải giữ nguyên văn. Chỉ case ở đúng biên mới phân biệt được hai cách viết đó — case nominal 30 ký tự thì cả hai đều cho cùng kết quả.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>BẢNG 1 — ĐỊNH NGHĨA GIÁ TRỊ BIÊN CỦA BIẾN ĐANG XÉT</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Giá trị</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>userText (số ký tự)</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Ghi chú</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>câu hỏi ngắn nhất có nghĩa</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>min+</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>ngay trên min</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>nom</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>giá trị điển hình, giữa miền</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>max-</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="C19" s="5" t="inlineStr"/>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="5" t="inlineStr"/>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>ngay dưới ngưỡng cắt</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>max</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="C20" s="5" t="inlineStr"/>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="5" t="inlineStr"/>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>đúng ngưỡng cắt — vẫn KHÔNG bị cắt vì mã dùng '&gt;'</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="55" t="inlineStr">
-        <is>
-          <t>Ràng buộc gốc: session.setTitle(userText.length() &gt; 60 ? userText.substring(0, 60) + '…' : userText). Đây là ngưỡng CẮT chứ không phải ngưỡng HỢP LỆ — vượt qua không bị từ chối, mà bị rút gọn. Vì thế cột Expected Output ghi hình dạng chuỗi kết quả thay vì Hợp lệ / Không hợp lệ như sheet 01.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>BẢNG 2 — STANDARD BVA TEST CASES (mẫu slide 23) · số case = 4n + 1 = 4×1 + 1 = 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>userText (ký tự)</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Biến đang xét</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Expected Output</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Độ dài tiêu đề</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Kết quả thực tế</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Method trong code</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B25" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>độ dài = min</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Giữ NGUYÊN VĂN, không có dấu …</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Đúng như mong đợi</t>
-        </is>
-      </c>
-      <c r="G25" s="13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>standardBva_khongCat</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B26" s="57" t="n">
-        <v>2</v>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>độ dài = min+</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Giữ NGUYÊN VĂN, không có dấu …</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>Đúng như mong đợi</t>
-        </is>
-      </c>
-      <c r="G26" s="13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>standardBva_khongCat</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B27" s="57" t="n">
-        <v>30</v>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>độ dài = nom</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Giữ NGUYÊN VĂN, không có dấu …</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Đúng như mong đợi</t>
-        </is>
-      </c>
-      <c r="G27" s="13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>standardBva_khongCat</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B28" s="57" t="n">
-        <v>59</v>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>độ dài = max-</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Giữ NGUYÊN VĂN, không có dấu …</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>Đúng như mong đợi</t>
-        </is>
-      </c>
-      <c r="G28" s="13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>standardBva_khongCat</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B29" s="57" t="n">
-        <v>60</v>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>độ dài = max (đúng ngưỡng)</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Giữ NGUYÊN VĂN, không có dấu …</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Đúng như mong đợi</t>
-        </is>
-      </c>
-      <c r="G29" s="13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>standardBva_khongCat</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="55" t="inlineStr">
-        <is>
-          <t>CÁCH ĐỌC: n = 1 nên không có ô 'tất cả nominal' riêng — case 3 vừa là nom của biến duy nhất, vừa là ô trung tâm của bảng. Ô tô tím là giá trị đang được đẩy tới biên. Cả 5 case đều là clean test case: kết quả mong đợi giống nhau, chỉ khác nhau ở chỗ chúng ép mã nguồn chọn đúng nhánh 'không cắt'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>BẢNG 3 — ROBUSTNESS BVA, phần BỔ SUNG (mẫu slide 24) · 6n + 1 = 6×1 + 1 = 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>userText (ký tự)</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Biến đang xét</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>Expected Output</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>Độ dài tiêu đề</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Kết quả thực tế</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>Method trong code</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B34" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>độ dài = min- (chuỗi rỗng)</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>Giữ nguyên văn — tiêu đề thành rỗng</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>Đúng như mong đợi</t>
-        </is>
-      </c>
-      <c r="G34" s="13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>robustnessBva_ngoaiBien</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B35" s="20" t="n">
-        <v>61</v>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>độ dài = max+</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>BỊ CẮT: 60 ký tự đầu + dấu …</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="n">
-        <v>61</v>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>Đúng như mong đợi</t>
-        </is>
-      </c>
-      <c r="G35" s="13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>robustnessBva_ngoaiBien</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="55" t="inlineStr">
-        <is>
-          <t>GHI NHẬN Ở CASE 6 (min-): chuỗi rỗng làm tiêu đề thành rỗng. KHÔNG xếp là khiếm khuyết — chính điều kiện isBlank() ngay phía trên sẽ đặt lại tiêu đề ở tin nhắn kế tiếp, hệ thống tự phục hồi; ngoài ra tầng controller đã chặn tin nhắn rỗng. Ghi lại ở đây để người đọc báo cáo biết case này đã được cân nhắc chứ không bị bỏ sót.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="56" t="inlineStr">
-        <is>
-          <t>CASE 7 LÀ CASE ĐÁNG GIÁ NHẤT của bảng. Nó là case DUY NHẤT chạy vào nhánh cắt chuỗi. Cặp (case 5, case 7) — 60 và 61 ký tự — chính là phép thử phân biệt '&gt;' với '&gt;=': nếu ai đó sửa mã thành '&gt;=' thì case 5 đỏ ngay, còn mọi case nominal vẫn xanh. Đó là lý do BVA tồn tại.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>BẢNG 4 — KIỂM TRA BỔ SUNG, nằm ngoài bảng giá trị biên</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>Tiêu đề phiên trước đó</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>userText (ký tự)</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>Expected Output</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr"/>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>Kết quả thực tế</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>Method trong code</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>Đã có tiêu đề thật</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>KHÔNG ghi đè — ngưỡng 60 không còn tác dụng</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>Đúng như mong đợi</t>
-        </is>
-      </c>
-      <c r="G41" s="13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>boSung_tieuDeDaDat_khongGhiDe</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>Đã có tiêu đề thật</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="n">
-        <v>61</v>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>KHÔNG ghi đè — ngưỡng 60 không còn tác dụng</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr"/>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>Đúng như mong đợi</t>
-        </is>
-      </c>
-      <c r="G42" s="13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>boSung_tieuDeDaDat_khongGhiDe</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="A43" s="55" t="inlineStr">
-        <is>
-          <t>Ngưỡng 60 chỉ áp dụng khi tiêu đề còn là mặc định 'Cuộc trò chuyện mới'. Hai case này chốt điều đó: phiên đã có tiêu đề thật thì tin nhắn dài bao nhiêu cũng không được ghi đè — nếu không, mọi câu hỏi sau đều đổi tên phiên và người dùng không tìm lại được cuộc trò chuyện cũ. Để ngoài bảng BVA vì chúng đổi ĐIỀU KIỆN VÀO nhánh, không đổi giá trị của biên.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A43:H43"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A32:H32"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -12815,7 +11341,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13344,7 +11870,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14266,7 +12792,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14832,7 +13358,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15464,7 +13990,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16358,4 +14884,670 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>BẢNG B1 - ĐỒ THỊ LUỒNG ĐIỀU KHIỂN (CFG) VÀ ĐỘ PHỨC TẠP CYCLOMATIC</t>
+        </is>
+      </c>
+      <c r="B1" s="27" t="n"/>
+      <c r="C1" s="27" t="n"/>
+      <c r="D1" s="27" t="n"/>
+      <c r="E1" s="27" t="n"/>
+      <c r="F1" s="27" t="n"/>
+      <c r="G1" s="27" t="n"/>
+      <c r="H1" s="27" t="n"/>
+      <c r="I1" s="28" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>Nguồn: RoadmapService.java  |  Hai hàm được phân tích: calculatePercent() và isNodeLocked()</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>A - BẢNG CHỈ SỐ CFG (Control Flow Graph Metrics)</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="n"/>
+      <c r="C4" s="27" t="n"/>
+      <c r="D4" s="27" t="n"/>
+      <c r="E4" s="27" t="n"/>
+      <c r="F4" s="27" t="n"/>
+      <c r="G4" s="27" t="n"/>
+      <c r="H4" s="27" t="n"/>
+      <c r="I4" s="28" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>HÀM</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>File nguồn</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>Nút (N)</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>Cạnh (E)</t>
+        </is>
+      </c>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>Nút điều kiện (P)</t>
+        </is>
+      </c>
+      <c r="F5" s="31" t="inlineStr">
+        <is>
+          <t>Miền (R)</t>
+        </is>
+      </c>
+      <c r="G5" s="31" t="inlineStr">
+        <is>
+          <t>V(G)=E-N+2</t>
+        </is>
+      </c>
+      <c r="H5" s="31" t="inlineStr">
+        <is>
+          <t>V(G)=P+1</t>
+        </is>
+      </c>
+      <c r="I5" s="31" t="inlineStr">
+        <is>
+          <t>Số test tối thiểu</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>calculatePercent()</t>
+        </is>
+      </c>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>RoadmapService.java</t>
+        </is>
+      </c>
+      <c r="C6" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="34" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>isNodeLocked()</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="inlineStr">
+        <is>
+          <t>RoadmapService.java</t>
+        </is>
+      </c>
+      <c r="C7" s="37" t="n">
+        <v>14</v>
+      </c>
+      <c r="D7" s="37" t="n">
+        <v>19</v>
+      </c>
+      <c r="E7" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="G7" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" s="37" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>B - DANH SÁCH ĐƯỜNG CƠ SỞ (BASIS PATHS)</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="n"/>
+      <c r="C9" s="27" t="n"/>
+      <c r="D9" s="27" t="n"/>
+      <c r="E9" s="27" t="n"/>
+      <c r="F9" s="27" t="n"/>
+      <c r="G9" s="27" t="n"/>
+      <c r="H9" s="27" t="n"/>
+      <c r="I9" s="28" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>HÀM</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>Path ID</t>
+        </is>
+      </c>
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t>Điều kiện</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>Chi tiết luồng thực thi</t>
+        </is>
+      </c>
+      <c r="E10" s="31" t="inlineStr">
+        <is>
+          <t>Kết quả mong đợi</t>
+        </is>
+      </c>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>Test Method</t>
+        </is>
+      </c>
+      <c r="G10" s="31" t="inlineStr">
+        <is>
+          <t>Input ví dụ</t>
+        </is>
+      </c>
+      <c r="H10" s="31" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="I10" s="31" t="inlineStr">
+        <is>
+          <t>Pass/Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>calculatePercent()</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>total==0 TRUE</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="inlineStr">
+        <is>
+          <t>Start -&gt; [total==0 TRUE] -&gt; return 0.0 -&gt; End</t>
+        </is>
+      </c>
+      <c r="E11" s="33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F11" s="33" t="inlineStr">
+        <is>
+          <t>calculatePercent_totalZero</t>
+        </is>
+      </c>
+      <c r="G11" s="33" t="inlineStr">
+        <is>
+          <t>completed=0, total=0</t>
+        </is>
+      </c>
+      <c r="H11" s="34" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I11" s="34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>calculatePercent()</t>
+        </is>
+      </c>
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C12" s="36" t="inlineStr">
+        <is>
+          <t>total==0 FALSE</t>
+        </is>
+      </c>
+      <c r="D12" s="36" t="inlineStr">
+        <is>
+          <t>Start -&gt; [total==0 FALSE] -&gt; return Math.round -&gt; End</t>
+        </is>
+      </c>
+      <c r="E12" s="36" t="inlineStr">
+        <is>
+          <t>% hợp lệ</t>
+        </is>
+      </c>
+      <c r="F12" s="36" t="inlineStr">
+        <is>
+          <t>calculatePercent_normalCase</t>
+        </is>
+      </c>
+      <c r="G12" s="36" t="inlineStr">
+        <is>
+          <t>completed=5, total=10</t>
+        </is>
+      </c>
+      <c r="H12" s="37" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="I12" s="37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>isNodeLocked()</t>
+        </is>
+      </c>
+      <c r="B13" s="34" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>tier null -&gt; tier=1, tier&lt;=1 TRUE</t>
+        </is>
+      </c>
+      <c r="D13" s="33" t="inlineStr">
+        <is>
+          <t>Start -&gt; [tier null-&gt;1] -&gt; [tier&lt;=1 TRUE] -&gt; return false -&gt; End</t>
+        </is>
+      </c>
+      <c r="E13" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F13" s="33" t="inlineStr">
+        <is>
+          <t>isNodeLocked_tier1Null</t>
+        </is>
+      </c>
+      <c r="G13" s="33" t="inlineStr">
+        <is>
+          <t>node.tier=null</t>
+        </is>
+      </c>
+      <c r="H13" s="34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I13" s="34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>isNodeLocked()</t>
+        </is>
+      </c>
+      <c r="B14" s="37" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C14" s="36" t="inlineStr">
+        <is>
+          <t>tier=1, tier&lt;=1 TRUE</t>
+        </is>
+      </c>
+      <c r="D14" s="36" t="inlineStr">
+        <is>
+          <t>Start -&gt; [tier=1] -&gt; [tier&lt;=1 TRUE] -&gt; return false -&gt; End</t>
+        </is>
+      </c>
+      <c r="E14" s="36" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F14" s="36" t="inlineStr">
+        <is>
+          <t>isNodeLocked_explicitTier1</t>
+        </is>
+      </c>
+      <c r="G14" s="36" t="inlineStr">
+        <is>
+          <t>node.tier=1</t>
+        </is>
+      </c>
+      <c r="H14" s="37" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I14" s="37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>isNodeLocked()</t>
+        </is>
+      </c>
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>tier=2, tất cả tier1 DONE</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="inlineStr">
+        <is>
+          <t>Start -&gt; [tier=2] -&gt; doneNodeIds đầy đủ -&gt; anyMatch=FALSE -&gt; return false</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F15" s="33" t="inlineStr">
+        <is>
+          <t>isNodeLocked_tier2AllDone</t>
+        </is>
+      </c>
+      <c r="G15" s="33" t="inlineStr">
+        <is>
+          <t>node.tier=2, tier1 DONE</t>
+        </is>
+      </c>
+      <c r="H15" s="34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I15" s="34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>isNodeLocked()</t>
+        </is>
+      </c>
+      <c r="B16" s="37" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C16" s="36" t="inlineStr">
+        <is>
+          <t>tier=2, tier1 chưa DONE</t>
+        </is>
+      </c>
+      <c r="D16" s="36" t="inlineStr">
+        <is>
+          <t>Start -&gt; [tier=2] -&gt; doneNodeIds thiếu -&gt; anyMatch=TRUE -&gt; return true</t>
+        </is>
+      </c>
+      <c r="E16" s="36" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F16" s="36" t="inlineStr">
+        <is>
+          <t>isNodeLocked_tier2NotDone</t>
+        </is>
+      </c>
+      <c r="G16" s="36" t="inlineStr">
+        <is>
+          <t>node.tier=2, tier1 chưa DONE</t>
+        </is>
+      </c>
+      <c r="H16" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I16" s="37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="32" t="inlineStr">
+        <is>
+          <t>isNodeLocked()</t>
+        </is>
+      </c>
+      <c r="B17" s="34" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C17" s="33" t="inlineStr">
+        <is>
+          <t>tier=3, tier1 chưa DONE</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="inlineStr">
+        <is>
+          <t>Start -&gt; [tier=3] -&gt; anyMatch(tier&lt;3 AND !done)=TRUE -&gt; return true</t>
+        </is>
+      </c>
+      <c r="E17" s="33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F17" s="33" t="inlineStr">
+        <is>
+          <t>isNodeLocked_tier3Tier1NotDone</t>
+        </is>
+      </c>
+      <c r="G17" s="33" t="inlineStr">
+        <is>
+          <t>node.tier=3, tier1 chưa DONE</t>
+        </is>
+      </c>
+      <c r="H17" s="34" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I17" s="34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>isNodeLocked()</t>
+        </is>
+      </c>
+      <c r="B18" s="37" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C18" s="36" t="inlineStr">
+        <is>
+          <t>tier=3, tier2 chưa DONE</t>
+        </is>
+      </c>
+      <c r="D18" s="36" t="inlineStr">
+        <is>
+          <t>Start -&gt; [tier=3] -&gt; anyMatch(tier2 NOT done)=TRUE -&gt; return true</t>
+        </is>
+      </c>
+      <c r="E18" s="36" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F18" s="36" t="inlineStr">
+        <is>
+          <t>isNodeLocked_tier3Tier2NotDone</t>
+        </is>
+      </c>
+      <c r="G18" s="36" t="inlineStr">
+        <is>
+          <t>node.tier=3, tier2 chưa DONE</t>
+        </is>
+      </c>
+      <c r="H18" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I18" s="37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>isNodeLocked()</t>
+        </is>
+      </c>
+      <c r="B19" s="34" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="C19" s="33" t="inlineStr">
+        <is>
+          <t>tier=3, tất cả done</t>
+        </is>
+      </c>
+      <c r="D19" s="33" t="inlineStr">
+        <is>
+          <t>Start -&gt; [tier=3] -&gt; anyMatch=FALSE -&gt; return false</t>
+        </is>
+      </c>
+      <c r="E19" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F19" s="33" t="inlineStr">
+        <is>
+          <t>isNodeLocked_tier3AllDone</t>
+        </is>
+      </c>
+      <c r="G19" s="33" t="inlineStr">
+        <is>
+          <t>node.tier=3, tất cả DONE</t>
+        </is>
+      </c>
+      <c r="H19" s="34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I19" s="34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A9:I9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/BaoCao-KiemThu-CareerCompass.xlsx
+++ b/BaoCao-KiemThu-CareerCompass.xlsx
@@ -8,21 +8,22 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00. Tong quan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01. BVA + Equiv Partition" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03. Decision Table (PhanA)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03b. Decision Table Token" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03c. Decision Table Tep" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04. State Transition (PhanA)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04b. State Transition Token" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04c. State Transition Onboard" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B1_CFG_va_Basis_Path" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B2_Coverage_Levels" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B3_Truoc_va_Sau" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B4_Coverage_Per_Class" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B5_Danh_Sach_Test_Whitebox" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05. API - Postman" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06. E2E - CodeceptJS" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07. Khiem khuyet" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00b. Phan cong nhom" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01. BVA + Equiv Partition" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03. Decision Table (PhanA)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03b. Decision Table Token" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03c. Decision Table Tep" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04. State Transition (PhanA)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04b. State Transition Token" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04c. State Transition Onboard" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B1_CFG_va_Basis_Path" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B2_Coverage_Levels" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B3_Truoc_va_Sau" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B4_Coverage_Per_Class" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B5_Danh_Sach_Test_Whitebox" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05. API - Postman" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06. E2E - CodeceptJS" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07. Khiem khuyet" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -928,7 +929,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1358,7 +1358,6 @@
       <c r="G17" s="8" t="n"/>
       <c r="H17" s="9" t="n"/>
     </row>
-    <row r="18"/>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
@@ -1512,7 +1511,6 @@
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="9" t="n"/>
     </row>
-    <row r="25"/>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -1625,7 +1623,6 @@
       <c r="G30" s="8" t="n"/>
       <c r="H30" s="9" t="n"/>
     </row>
-    <row r="31"/>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
@@ -1635,15 +1632,15 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="F21:H21"/>
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F22:H22"/>
     <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F22:H22"/>
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="F9:H9"/>
+    <mergeCell ref="F15:H15"/>
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="A32:H32"/>
@@ -1656,7 +1653,7 @@
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="F12:H12"/>
     <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F21:H21"/>
     <mergeCell ref="F24:H24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1664,6 +1661,672 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>BẢNG B1 - ĐỒ THỊ LUỒNG ĐIỀU KHIỂN (CFG) VÀ ĐỘ PHỨC TẠP CYCLOMATIC</t>
+        </is>
+      </c>
+      <c r="B1" s="27" t="n"/>
+      <c r="C1" s="27" t="n"/>
+      <c r="D1" s="27" t="n"/>
+      <c r="E1" s="27" t="n"/>
+      <c r="F1" s="27" t="n"/>
+      <c r="G1" s="27" t="n"/>
+      <c r="H1" s="27" t="n"/>
+      <c r="I1" s="28" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>Nguồn: RoadmapService.java  |  Hai hàm được phân tích: calculatePercent() và isNodeLocked()</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>A - BẢNG CHỈ SỐ CFG (Control Flow Graph Metrics)</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="n"/>
+      <c r="C4" s="27" t="n"/>
+      <c r="D4" s="27" t="n"/>
+      <c r="E4" s="27" t="n"/>
+      <c r="F4" s="27" t="n"/>
+      <c r="G4" s="27" t="n"/>
+      <c r="H4" s="27" t="n"/>
+      <c r="I4" s="28" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>HÀM</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>File nguồn</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>Nút (N)</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>Cạnh (E)</t>
+        </is>
+      </c>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>Nút điều kiện (P)</t>
+        </is>
+      </c>
+      <c r="F5" s="31" t="inlineStr">
+        <is>
+          <t>Miền (R)</t>
+        </is>
+      </c>
+      <c r="G5" s="31" t="inlineStr">
+        <is>
+          <t>V(G)=E-N+2</t>
+        </is>
+      </c>
+      <c r="H5" s="31" t="inlineStr">
+        <is>
+          <t>V(G)=P+1</t>
+        </is>
+      </c>
+      <c r="I5" s="31" t="inlineStr">
+        <is>
+          <t>Số test tối thiểu</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>calculatePercent()</t>
+        </is>
+      </c>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>RoadmapService.java</t>
+        </is>
+      </c>
+      <c r="C6" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="34" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>isNodeLocked()</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="inlineStr">
+        <is>
+          <t>RoadmapService.java</t>
+        </is>
+      </c>
+      <c r="C7" s="37" t="n">
+        <v>14</v>
+      </c>
+      <c r="D7" s="37" t="n">
+        <v>19</v>
+      </c>
+      <c r="E7" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="G7" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" s="37" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>B - DANH SÁCH ĐƯỜNG CƠ SỞ (BASIS PATHS)</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="n"/>
+      <c r="C9" s="27" t="n"/>
+      <c r="D9" s="27" t="n"/>
+      <c r="E9" s="27" t="n"/>
+      <c r="F9" s="27" t="n"/>
+      <c r="G9" s="27" t="n"/>
+      <c r="H9" s="27" t="n"/>
+      <c r="I9" s="28" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>HÀM</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>Path ID</t>
+        </is>
+      </c>
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t>Điều kiện</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>Chi tiết luồng thực thi</t>
+        </is>
+      </c>
+      <c r="E10" s="31" t="inlineStr">
+        <is>
+          <t>Kết quả mong đợi</t>
+        </is>
+      </c>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>Test Method</t>
+        </is>
+      </c>
+      <c r="G10" s="31" t="inlineStr">
+        <is>
+          <t>Input ví dụ</t>
+        </is>
+      </c>
+      <c r="H10" s="31" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="I10" s="31" t="inlineStr">
+        <is>
+          <t>Pass/Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>calculatePercent()</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>total==0 TRUE</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="inlineStr">
+        <is>
+          <t>Start -&gt; [total==0 TRUE] -&gt; return 0.0 -&gt; End</t>
+        </is>
+      </c>
+      <c r="E11" s="33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F11" s="33" t="inlineStr">
+        <is>
+          <t>calculatePercent_totalZero</t>
+        </is>
+      </c>
+      <c r="G11" s="33" t="inlineStr">
+        <is>
+          <t>completed=0, total=0</t>
+        </is>
+      </c>
+      <c r="H11" s="34" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I11" s="34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>calculatePercent()</t>
+        </is>
+      </c>
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C12" s="36" t="inlineStr">
+        <is>
+          <t>total==0 FALSE</t>
+        </is>
+      </c>
+      <c r="D12" s="36" t="inlineStr">
+        <is>
+          <t>Start -&gt; [total==0 FALSE] -&gt; return Math.round -&gt; End</t>
+        </is>
+      </c>
+      <c r="E12" s="36" t="inlineStr">
+        <is>
+          <t>% hợp lệ</t>
+        </is>
+      </c>
+      <c r="F12" s="36" t="inlineStr">
+        <is>
+          <t>calculatePercent_normalCase</t>
+        </is>
+      </c>
+      <c r="G12" s="36" t="inlineStr">
+        <is>
+          <t>completed=5, total=10</t>
+        </is>
+      </c>
+      <c r="H12" s="37" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="I12" s="37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>isNodeLocked()</t>
+        </is>
+      </c>
+      <c r="B13" s="34" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>tier null -&gt; tier=1, tier&lt;=1 TRUE</t>
+        </is>
+      </c>
+      <c r="D13" s="33" t="inlineStr">
+        <is>
+          <t>Start -&gt; [tier null-&gt;1] -&gt; [tier&lt;=1 TRUE] -&gt; return false -&gt; End</t>
+        </is>
+      </c>
+      <c r="E13" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F13" s="33" t="inlineStr">
+        <is>
+          <t>isNodeLocked_tier1Null</t>
+        </is>
+      </c>
+      <c r="G13" s="33" t="inlineStr">
+        <is>
+          <t>node.tier=null</t>
+        </is>
+      </c>
+      <c r="H13" s="34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I13" s="34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>isNodeLocked()</t>
+        </is>
+      </c>
+      <c r="B14" s="37" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C14" s="36" t="inlineStr">
+        <is>
+          <t>tier=1, tier&lt;=1 TRUE</t>
+        </is>
+      </c>
+      <c r="D14" s="36" t="inlineStr">
+        <is>
+          <t>Start -&gt; [tier=1] -&gt; [tier&lt;=1 TRUE] -&gt; return false -&gt; End</t>
+        </is>
+      </c>
+      <c r="E14" s="36" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F14" s="36" t="inlineStr">
+        <is>
+          <t>isNodeLocked_explicitTier1</t>
+        </is>
+      </c>
+      <c r="G14" s="36" t="inlineStr">
+        <is>
+          <t>node.tier=1</t>
+        </is>
+      </c>
+      <c r="H14" s="37" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I14" s="37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>isNodeLocked()</t>
+        </is>
+      </c>
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>tier=2, tất cả tier1 DONE</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="inlineStr">
+        <is>
+          <t>Start -&gt; [tier=2] -&gt; doneNodeIds đầy đủ -&gt; anyMatch=FALSE -&gt; return false</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F15" s="33" t="inlineStr">
+        <is>
+          <t>isNodeLocked_tier2AllDone</t>
+        </is>
+      </c>
+      <c r="G15" s="33" t="inlineStr">
+        <is>
+          <t>node.tier=2, tier1 DONE</t>
+        </is>
+      </c>
+      <c r="H15" s="34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I15" s="34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>isNodeLocked()</t>
+        </is>
+      </c>
+      <c r="B16" s="37" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C16" s="36" t="inlineStr">
+        <is>
+          <t>tier=2, tier1 chưa DONE</t>
+        </is>
+      </c>
+      <c r="D16" s="36" t="inlineStr">
+        <is>
+          <t>Start -&gt; [tier=2] -&gt; doneNodeIds thiếu -&gt; anyMatch=TRUE -&gt; return true</t>
+        </is>
+      </c>
+      <c r="E16" s="36" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F16" s="36" t="inlineStr">
+        <is>
+          <t>isNodeLocked_tier2NotDone</t>
+        </is>
+      </c>
+      <c r="G16" s="36" t="inlineStr">
+        <is>
+          <t>node.tier=2, tier1 chưa DONE</t>
+        </is>
+      </c>
+      <c r="H16" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I16" s="37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="32" t="inlineStr">
+        <is>
+          <t>isNodeLocked()</t>
+        </is>
+      </c>
+      <c r="B17" s="34" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C17" s="33" t="inlineStr">
+        <is>
+          <t>tier=3, tier1 chưa DONE</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="inlineStr">
+        <is>
+          <t>Start -&gt; [tier=3] -&gt; anyMatch(tier&lt;3 AND !done)=TRUE -&gt; return true</t>
+        </is>
+      </c>
+      <c r="E17" s="33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F17" s="33" t="inlineStr">
+        <is>
+          <t>isNodeLocked_tier3Tier1NotDone</t>
+        </is>
+      </c>
+      <c r="G17" s="33" t="inlineStr">
+        <is>
+          <t>node.tier=3, tier1 chưa DONE</t>
+        </is>
+      </c>
+      <c r="H17" s="34" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I17" s="34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>isNodeLocked()</t>
+        </is>
+      </c>
+      <c r="B18" s="37" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C18" s="36" t="inlineStr">
+        <is>
+          <t>tier=3, tier2 chưa DONE</t>
+        </is>
+      </c>
+      <c r="D18" s="36" t="inlineStr">
+        <is>
+          <t>Start -&gt; [tier=3] -&gt; anyMatch(tier2 NOT done)=TRUE -&gt; return true</t>
+        </is>
+      </c>
+      <c r="E18" s="36" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F18" s="36" t="inlineStr">
+        <is>
+          <t>isNodeLocked_tier3Tier2NotDone</t>
+        </is>
+      </c>
+      <c r="G18" s="36" t="inlineStr">
+        <is>
+          <t>node.tier=3, tier2 chưa DONE</t>
+        </is>
+      </c>
+      <c r="H18" s="37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I18" s="37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>isNodeLocked()</t>
+        </is>
+      </c>
+      <c r="B19" s="34" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="C19" s="33" t="inlineStr">
+        <is>
+          <t>tier=3, tất cả done</t>
+        </is>
+      </c>
+      <c r="D19" s="33" t="inlineStr">
+        <is>
+          <t>Start -&gt; [tier=3] -&gt; anyMatch=FALSE -&gt; return false</t>
+        </is>
+      </c>
+      <c r="E19" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F19" s="33" t="inlineStr">
+        <is>
+          <t>isNodeLocked_tier3AllDone</t>
+        </is>
+      </c>
+      <c r="G19" s="33" t="inlineStr">
+        <is>
+          <t>node.tier=3, tất cả DONE</t>
+        </is>
+      </c>
+      <c r="H19" s="34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I19" s="34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A9:I9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2496,7 +3159,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3049,7 +3712,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5638,7 +6301,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6545,7 +7208,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7246,7 +7909,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8026,7 +8689,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8059,7 +8722,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -8543,6 +9205,756 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Phân công thực hiện trong nhóm</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="53" t="inlineStr">
+        <is>
+          <t>Người thực hiện từng phần được xác định từ lịch sử Git (tác giả commit đầu tiên tạo ra tệp nguồn tương ứng), không ghi theo trí nhớ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="54" t="inlineStr">
+        <is>
+          <t>KỲ BÁO CÁO — từ 22/07/2026, 71 commit của 3 thành viên, 399 trường hợp kiểm thử tự động</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>BẢNG 1 — THÀNH VIÊN VÀ MẢNG CÔNG VIỆC CHÍNH</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Thành viên</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Mảng công việc chính</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Nguyễn Thành Phát</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị tầng dịch vụ · Kiểm thử hộp đen chương IV · Kiểm thử giao diện đầu-cuối · Khắc phục khiếm khuyết</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Vòng Minh Quân</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Kiểm thử hộp trắng · Kiểm thử tầng điều khiển · Kiểm thử giá trị biên · Sửa lỗi giao diện · Các báo cáo dạng bảng</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>NhwNgocc</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Bản thuyết minh kiểm chứng phần mềm bằng văn bản, gồm bốn phần</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="55" t="inlineStr">
+        <is>
+          <t>SỐ COMMIT KHÔNG TỶ LỆ VỚI KHỐI LƯỢNG CÔNG VIỆC. Một bản thuyết minh dài hơn trăm đoạn kèm bảng biểu và ảnh chụp màn hình chỉ chiếm một đến hai commit, trong khi một đợt chỉnh sửa cách trình bày báo cáo có thể sinh ra hơn mười commit nhỏ. Hai bảng bên dưới phản ánh đóng góp chính xác hơn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>BẢNG 2 — NGƯỜI THỰC HIỆN TỪNG SHEET CỦA BÁO CÁO NÀY</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Nội dung</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Người thực hiện</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>00. Tong quan</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Tổng hợp bốn tầng kiểm thử, độ bao phủ, số phép kiểm</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Nguyễn Thành Phát</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>01. BVA + Equiv Partition</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Giá trị biên và phân hoạch lớp tương đương cho biểu mẫu đăng ký; giá trị biên cho dung lượng tệp</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Nguyễn Thành Phát · Vòng Minh Quân</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>03. Decision Table (PhanA)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Bảng quyết định — luật chặn cập nhật tiến độ học</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Nguyễn Thành Phát</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>03b. Decision Table Token</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Bảng quyết định — hiệu lực mã đặt lại mật khẩu</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Nguyễn Thành Phát</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>03c. Decision Table Tep</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Bảng quyết định — định dạng và dung lượng tệp bảng điểm</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Nguyễn Thành Phát</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>04. State Transition (PhanA)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Chuyển đổi trạng thái — tiến độ node kỹ năng</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Nguyễn Thành Phát</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>04b. State Transition Token</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Chuyển đổi trạng thái — vòng đời mã đặt lại mật khẩu</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Nguyễn Thành Phát</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>04c. State Transition Onboard</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Chuyển đổi trạng thái — quy trình khai báo hồ sơ</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Nguyễn Thành Phát</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>B1_CFG_va_Basis_Path</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Đồ thị dòng điều khiển, độ phức tạp Cyclomatic, 9 đường cơ sở</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Vòng Minh Quân</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>B2_Coverage_Levels</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>So sánh bốn mức bao phủ và ma trận tổ hợp điều kiện MC/DC</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Vòng Minh Quân</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>B3_Truoc_va_Sau</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Độ bao phủ trước và sau khi bổ sung kiểm thử, kèm nhận xét</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Vòng Minh Quân</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>B4_Coverage_Per_Class</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Độ bao phủ chi tiết theo từng lớp</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Vòng Minh Quân</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>B5_Danh_Sach_Test_Whitebox</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Danh mục tệp kiểm thử thuộc phạm vi hộp trắng</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Vòng Minh Quân</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>05. API - Postman</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Kiểm thử API: phân bổ theo nhóm chức năng, phép kiểm, lỗi</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Nguyễn Thành Phát · Vòng Minh Quân</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>06. E2E - CodeceptJS</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Kiểm thử giao diện đầu-cuối: 17 kịch bản, ma trận truy vết</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Nguyễn Thành Phát</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>07. Khiem khuyet</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>11 khiếm khuyết: mô tả, kỹ thuật phát hiện, cách khắc phục</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Nguyễn Thành Phát</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="55" t="inlineStr">
+        <is>
+          <t>Năm sheet B1–B5 là phần kiểm thử hộp trắng: đồ thị dòng điều khiển, độ phức tạp Cyclomatic, đường cơ sở, ma trận tổ hợp điều kiện MC/DC và đối chiếu độ bao phủ trước–sau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>BẢNG 3 — CÁC PHẦN VIỆC KHÔNG HIỆN THÀNH SHEET RIÊNG</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Phần việc</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Nội dung</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Người thực hiện</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị tầng dịch vụ</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>24 lớp kiểm thử, phủ 9 phân hệ nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Nguyễn Thành Phát</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Kiểm thử tầng điều khiển</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>8 lớp kiểm thử, kèm 2 lớp hỗ trợ CSRF và bảo mật</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Vòng Minh Quân</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Kiểm thử bộ xử lý ngoại lệ</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Đối chiếu loại ngoại lệ với mã trạng thái HTTP</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Vòng Minh Quân</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr"/>
+      <c r="G37" s="5" t="inlineStr"/>
+      <c r="H37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Bản thuyết minh bằng văn bản</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Bốn phần: đơn vị, API, giao diện, kỹ thuật dựa trên kinh nghiệm</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>NhwNgocc</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Sửa lỗi và tái cấu trúc giao diện</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Lỗi rời trang KCPMS-22, trang cố vấn AI</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Vòng Minh Quân</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Quy trình CI/CD và triển khai</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>GitHub Actions, Docker, VPS, chặn deploy khi đỏ</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Vòng Minh Quân · Nguyễn Thành Phát</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Phân tích tĩnh và đo bao phủ</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>SonarCloud, JaCoCo, ngưỡng chặn 65% nhánh</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Nguyễn Thành Phát</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr"/>
+      <c r="G41" s="5" t="inlineStr"/>
+      <c r="H41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Khắc phục khiếm khuyết ứng dụng</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>11 khiếm khuyết, kèm kiểm thử hồi quy</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Nguyễn Thành Phát</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="55" t="inlineStr">
+        <is>
+          <t>Các phần trên nằm trong mã nguồn và tài liệu kèm theo, không trình bày thành bảng riêng trong tệp Excel này. Chi tiết theo tuần xem tệp BaoCao-CongViec-Theo-Tuan.docx.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="58">
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="D35:E35"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10769,7 +12181,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11341,7 +12753,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11870,7 +13282,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12792,7 +14204,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13358,7 +14770,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13990,7 +15402,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14884,670 +16296,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="26" t="inlineStr">
-        <is>
-          <t>BẢNG B1 - ĐỒ THỊ LUỒNG ĐIỀU KHIỂN (CFG) VÀ ĐỘ PHỨC TẠP CYCLOMATIC</t>
-        </is>
-      </c>
-      <c r="B1" s="27" t="n"/>
-      <c r="C1" s="27" t="n"/>
-      <c r="D1" s="27" t="n"/>
-      <c r="E1" s="27" t="n"/>
-      <c r="F1" s="27" t="n"/>
-      <c r="G1" s="27" t="n"/>
-      <c r="H1" s="27" t="n"/>
-      <c r="I1" s="28" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="29" t="inlineStr">
-        <is>
-          <t>Nguồn: RoadmapService.java  |  Hai hàm được phân tích: calculatePercent() và isNodeLocked()</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="30" t="inlineStr">
-        <is>
-          <t>A - BẢNG CHỈ SỐ CFG (Control Flow Graph Metrics)</t>
-        </is>
-      </c>
-      <c r="B4" s="27" t="n"/>
-      <c r="C4" s="27" t="n"/>
-      <c r="D4" s="27" t="n"/>
-      <c r="E4" s="27" t="n"/>
-      <c r="F4" s="27" t="n"/>
-      <c r="G4" s="27" t="n"/>
-      <c r="H4" s="27" t="n"/>
-      <c r="I4" s="28" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="31" t="inlineStr">
-        <is>
-          <t>HÀM</t>
-        </is>
-      </c>
-      <c r="B5" s="31" t="inlineStr">
-        <is>
-          <t>File nguồn</t>
-        </is>
-      </c>
-      <c r="C5" s="31" t="inlineStr">
-        <is>
-          <t>Nút (N)</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="inlineStr">
-        <is>
-          <t>Cạnh (E)</t>
-        </is>
-      </c>
-      <c r="E5" s="31" t="inlineStr">
-        <is>
-          <t>Nút điều kiện (P)</t>
-        </is>
-      </c>
-      <c r="F5" s="31" t="inlineStr">
-        <is>
-          <t>Miền (R)</t>
-        </is>
-      </c>
-      <c r="G5" s="31" t="inlineStr">
-        <is>
-          <t>V(G)=E-N+2</t>
-        </is>
-      </c>
-      <c r="H5" s="31" t="inlineStr">
-        <is>
-          <t>V(G)=P+1</t>
-        </is>
-      </c>
-      <c r="I5" s="31" t="inlineStr">
-        <is>
-          <t>Số test tối thiểu</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="32" t="inlineStr">
-        <is>
-          <t>calculatePercent()</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="inlineStr">
-        <is>
-          <t>RoadmapService.java</t>
-        </is>
-      </c>
-      <c r="C6" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" s="34" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="35" t="inlineStr">
-        <is>
-          <t>isNodeLocked()</t>
-        </is>
-      </c>
-      <c r="B7" s="36" t="inlineStr">
-        <is>
-          <t>RoadmapService.java</t>
-        </is>
-      </c>
-      <c r="C7" s="37" t="n">
-        <v>14</v>
-      </c>
-      <c r="D7" s="37" t="n">
-        <v>19</v>
-      </c>
-      <c r="E7" s="37" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" s="37" t="n">
-        <v>7</v>
-      </c>
-      <c r="G7" s="37" t="n">
-        <v>7</v>
-      </c>
-      <c r="H7" s="37" t="n">
-        <v>7</v>
-      </c>
-      <c r="I7" s="37" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="30" t="inlineStr">
-        <is>
-          <t>B - DANH SÁCH ĐƯỜNG CƠ SỞ (BASIS PATHS)</t>
-        </is>
-      </c>
-      <c r="B9" s="27" t="n"/>
-      <c r="C9" s="27" t="n"/>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="27" t="n"/>
-      <c r="F9" s="27" t="n"/>
-      <c r="G9" s="27" t="n"/>
-      <c r="H9" s="27" t="n"/>
-      <c r="I9" s="28" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="31" t="inlineStr">
-        <is>
-          <t>HÀM</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="inlineStr">
-        <is>
-          <t>Path ID</t>
-        </is>
-      </c>
-      <c r="C10" s="31" t="inlineStr">
-        <is>
-          <t>Điều kiện</t>
-        </is>
-      </c>
-      <c r="D10" s="31" t="inlineStr">
-        <is>
-          <t>Chi tiết luồng thực thi</t>
-        </is>
-      </c>
-      <c r="E10" s="31" t="inlineStr">
-        <is>
-          <t>Kết quả mong đợi</t>
-        </is>
-      </c>
-      <c r="F10" s="31" t="inlineStr">
-        <is>
-          <t>Test Method</t>
-        </is>
-      </c>
-      <c r="G10" s="31" t="inlineStr">
-        <is>
-          <t>Input ví dụ</t>
-        </is>
-      </c>
-      <c r="H10" s="31" t="inlineStr">
-        <is>
-          <t>Output</t>
-        </is>
-      </c>
-      <c r="I10" s="31" t="inlineStr">
-        <is>
-          <t>Pass/Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="32" t="inlineStr">
-        <is>
-          <t>calculatePercent()</t>
-        </is>
-      </c>
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C11" s="33" t="inlineStr">
-        <is>
-          <t>total==0 TRUE</t>
-        </is>
-      </c>
-      <c r="D11" s="33" t="inlineStr">
-        <is>
-          <t>Start -&gt; [total==0 TRUE] -&gt; return 0.0 -&gt; End</t>
-        </is>
-      </c>
-      <c r="E11" s="33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F11" s="33" t="inlineStr">
-        <is>
-          <t>calculatePercent_totalZero</t>
-        </is>
-      </c>
-      <c r="G11" s="33" t="inlineStr">
-        <is>
-          <t>completed=0, total=0</t>
-        </is>
-      </c>
-      <c r="H11" s="34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I11" s="34" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="35" t="inlineStr">
-        <is>
-          <t>calculatePercent()</t>
-        </is>
-      </c>
-      <c r="B12" s="37" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C12" s="36" t="inlineStr">
-        <is>
-          <t>total==0 FALSE</t>
-        </is>
-      </c>
-      <c r="D12" s="36" t="inlineStr">
-        <is>
-          <t>Start -&gt; [total==0 FALSE] -&gt; return Math.round -&gt; End</t>
-        </is>
-      </c>
-      <c r="E12" s="36" t="inlineStr">
-        <is>
-          <t>% hợp lệ</t>
-        </is>
-      </c>
-      <c r="F12" s="36" t="inlineStr">
-        <is>
-          <t>calculatePercent_normalCase</t>
-        </is>
-      </c>
-      <c r="G12" s="36" t="inlineStr">
-        <is>
-          <t>completed=5, total=10</t>
-        </is>
-      </c>
-      <c r="H12" s="37" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="I12" s="37" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="32" t="inlineStr">
-        <is>
-          <t>isNodeLocked()</t>
-        </is>
-      </c>
-      <c r="B13" s="34" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C13" s="33" t="inlineStr">
-        <is>
-          <t>tier null -&gt; tier=1, tier&lt;=1 TRUE</t>
-        </is>
-      </c>
-      <c r="D13" s="33" t="inlineStr">
-        <is>
-          <t>Start -&gt; [tier null-&gt;1] -&gt; [tier&lt;=1 TRUE] -&gt; return false -&gt; End</t>
-        </is>
-      </c>
-      <c r="E13" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F13" s="33" t="inlineStr">
-        <is>
-          <t>isNodeLocked_tier1Null</t>
-        </is>
-      </c>
-      <c r="G13" s="33" t="inlineStr">
-        <is>
-          <t>node.tier=null</t>
-        </is>
-      </c>
-      <c r="H13" s="34" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I13" s="34" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="35" t="inlineStr">
-        <is>
-          <t>isNodeLocked()</t>
-        </is>
-      </c>
-      <c r="B14" s="37" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C14" s="36" t="inlineStr">
-        <is>
-          <t>tier=1, tier&lt;=1 TRUE</t>
-        </is>
-      </c>
-      <c r="D14" s="36" t="inlineStr">
-        <is>
-          <t>Start -&gt; [tier=1] -&gt; [tier&lt;=1 TRUE] -&gt; return false -&gt; End</t>
-        </is>
-      </c>
-      <c r="E14" s="36" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F14" s="36" t="inlineStr">
-        <is>
-          <t>isNodeLocked_explicitTier1</t>
-        </is>
-      </c>
-      <c r="G14" s="36" t="inlineStr">
-        <is>
-          <t>node.tier=1</t>
-        </is>
-      </c>
-      <c r="H14" s="37" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I14" s="37" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="32" t="inlineStr">
-        <is>
-          <t>isNodeLocked()</t>
-        </is>
-      </c>
-      <c r="B15" s="34" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C15" s="33" t="inlineStr">
-        <is>
-          <t>tier=2, tất cả tier1 DONE</t>
-        </is>
-      </c>
-      <c r="D15" s="33" t="inlineStr">
-        <is>
-          <t>Start -&gt; [tier=2] -&gt; doneNodeIds đầy đủ -&gt; anyMatch=FALSE -&gt; return false</t>
-        </is>
-      </c>
-      <c r="E15" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F15" s="33" t="inlineStr">
-        <is>
-          <t>isNodeLocked_tier2AllDone</t>
-        </is>
-      </c>
-      <c r="G15" s="33" t="inlineStr">
-        <is>
-          <t>node.tier=2, tier1 DONE</t>
-        </is>
-      </c>
-      <c r="H15" s="34" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I15" s="34" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="35" t="inlineStr">
-        <is>
-          <t>isNodeLocked()</t>
-        </is>
-      </c>
-      <c r="B16" s="37" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="C16" s="36" t="inlineStr">
-        <is>
-          <t>tier=2, tier1 chưa DONE</t>
-        </is>
-      </c>
-      <c r="D16" s="36" t="inlineStr">
-        <is>
-          <t>Start -&gt; [tier=2] -&gt; doneNodeIds thiếu -&gt; anyMatch=TRUE -&gt; return true</t>
-        </is>
-      </c>
-      <c r="E16" s="36" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F16" s="36" t="inlineStr">
-        <is>
-          <t>isNodeLocked_tier2NotDone</t>
-        </is>
-      </c>
-      <c r="G16" s="36" t="inlineStr">
-        <is>
-          <t>node.tier=2, tier1 chưa DONE</t>
-        </is>
-      </c>
-      <c r="H16" s="37" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I16" s="37" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="32" t="inlineStr">
-        <is>
-          <t>isNodeLocked()</t>
-        </is>
-      </c>
-      <c r="B17" s="34" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="C17" s="33" t="inlineStr">
-        <is>
-          <t>tier=3, tier1 chưa DONE</t>
-        </is>
-      </c>
-      <c r="D17" s="33" t="inlineStr">
-        <is>
-          <t>Start -&gt; [tier=3] -&gt; anyMatch(tier&lt;3 AND !done)=TRUE -&gt; return true</t>
-        </is>
-      </c>
-      <c r="E17" s="33" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F17" s="33" t="inlineStr">
-        <is>
-          <t>isNodeLocked_tier3Tier1NotDone</t>
-        </is>
-      </c>
-      <c r="G17" s="33" t="inlineStr">
-        <is>
-          <t>node.tier=3, tier1 chưa DONE</t>
-        </is>
-      </c>
-      <c r="H17" s="34" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I17" s="34" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="35" t="inlineStr">
-        <is>
-          <t>isNodeLocked()</t>
-        </is>
-      </c>
-      <c r="B18" s="37" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="C18" s="36" t="inlineStr">
-        <is>
-          <t>tier=3, tier2 chưa DONE</t>
-        </is>
-      </c>
-      <c r="D18" s="36" t="inlineStr">
-        <is>
-          <t>Start -&gt; [tier=3] -&gt; anyMatch(tier2 NOT done)=TRUE -&gt; return true</t>
-        </is>
-      </c>
-      <c r="E18" s="36" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F18" s="36" t="inlineStr">
-        <is>
-          <t>isNodeLocked_tier3Tier2NotDone</t>
-        </is>
-      </c>
-      <c r="G18" s="36" t="inlineStr">
-        <is>
-          <t>node.tier=3, tier2 chưa DONE</t>
-        </is>
-      </c>
-      <c r="H18" s="37" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I18" s="37" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="32" t="inlineStr">
-        <is>
-          <t>isNodeLocked()</t>
-        </is>
-      </c>
-      <c r="B19" s="34" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="C19" s="33" t="inlineStr">
-        <is>
-          <t>tier=3, tất cả done</t>
-        </is>
-      </c>
-      <c r="D19" s="33" t="inlineStr">
-        <is>
-          <t>Start -&gt; [tier=3] -&gt; anyMatch=FALSE -&gt; return false</t>
-        </is>
-      </c>
-      <c r="E19" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F19" s="33" t="inlineStr">
-        <is>
-          <t>isNodeLocked_tier3AllDone</t>
-        </is>
-      </c>
-      <c r="G19" s="33" t="inlineStr">
-        <is>
-          <t>node.tier=3, tất cả DONE</t>
-        </is>
-      </c>
-      <c r="H19" s="34" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I19" s="34" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A9:I9"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/BaoCao-KiemThu-CareerCompass.xlsx
+++ b/BaoCao-KiemThu-CareerCompass.xlsx
@@ -1635,8 +1635,8 @@
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="F9:H9"/>
@@ -9210,7 +9210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9240,7 +9240,7 @@
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="54" t="inlineStr">
         <is>
-          <t>KỲ BÁO CÁO — từ 22/07/2026, 71 commit của 3 thành viên, 399 trường hợp kiểm thử tự động</t>
+          <t>KỲ BÁO CÁO — từ 22/07/2026, 72 commit của 3 thành viên, 399 trường hợp kiểm thử tự động</t>
         </is>
       </c>
     </row>
@@ -9281,11 +9281,11 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Kiểm thử đơn vị tầng dịch vụ · Kiểm thử hộp đen chương IV · Kiểm thử giao diện đầu-cuối · Khắc phục khiếm khuyết</t>
+          <t>Kiểm thử đơn vị tầng dịch vụ · Kiểm thử hộp đen chương IV · Xây dựng bộ kiểm thử API và giao diện · Khắc phục khiếm khuyết</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E8" s="5" t="inlineStr"/>
       <c r="F8" s="5" t="inlineStr"/>
@@ -9314,12 +9314,12 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>NhwNgocc</t>
+          <t>Trần Tô Như Ngọc</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Bản thuyết minh kiểm chứng phần mềm bằng văn bản, gồm bốn phần</t>
+          <t>Thực hiện kiểm thử API và kiểm thử giao diện đầu-cuối, lập báo cáo kết quả · Bản thuyết minh kiểm chứng phần mềm bằng văn bản</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Kiểm thử API: phân bổ theo nhóm chức năng, phép kiểm, lỗi</t>
+          <t>Kiểm thử API: phân bổ theo nhóm chức năng, phép kiểm, lỗi. Bộ kiểm thử do Nguyễn Thành Phát và Vòng Minh Quân xây dựng</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Nguyễn Thành Phát · Vòng Minh Quân</t>
+          <t>Trần Tô Như Ngọc</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr"/>
@@ -9654,12 +9654,12 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Kiểm thử giao diện đầu-cuối: 17 kịch bản, ma trận truy vết</t>
+          <t>Kiểm thử giao diện đầu-cuối: 17 kịch bản, ma trận truy vết. Bộ kiểm thử do Nguyễn Thành Phát xây dựng</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Nguyễn Thành Phát</t>
+          <t>Trần Tô Như Ngọc</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr"/>
@@ -9693,69 +9693,56 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="55" t="inlineStr">
+        <is>
+          <t>Với sheet 05 và 06, cột "Người thực hiện" ghi người CHẠY kiểm thử và LẬP BÁO CÁO — đó mới là nội dung của hai sheet này. Người xây dựng bộ kiểm thử ghi trong cột Nội dung và ở Bảng 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>BẢNG 3 — CÁC PHẦN VIỆC KHÔNG HIỆN THÀNH SHEET RIÊNG</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Phần việc</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Nội dung</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr"/>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>Người thực hiện</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr"/>
-      <c r="G34" s="4" t="inlineStr"/>
-      <c r="H34" s="4" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Kiểm thử đơn vị tầng dịch vụ</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>24 lớp kiểm thử, phủ 9 phân hệ nghiệp vụ</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Nguyễn Thành Phát</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr"/>
-      <c r="G35" s="5" t="inlineStr"/>
-      <c r="H35" s="5" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Kiểm thử tầng điều khiển</t>
+          <t>Kiểm thử đơn vị tầng dịch vụ</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>8 lớp kiểm thử, kèm 2 lớp hỗ trợ CSRF và bảo mật</t>
+          <t>24 lớp kiểm thử, phủ 9 phân hệ nghiệp vụ</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Vòng Minh Quân</t>
+          <t>Nguyễn Thành Phát</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr"/>
@@ -9765,12 +9752,12 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Kiểm thử bộ xử lý ngoại lệ</t>
+          <t>Kiểm thử tầng điều khiển</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Đối chiếu loại ngoại lệ với mã trạng thái HTTP</t>
+          <t>8 lớp kiểm thử, kèm 2 lớp hỗ trợ CSRF và bảo mật</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -9785,17 +9772,17 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Bản thuyết minh bằng văn bản</t>
+          <t>Kiểm thử bộ xử lý ngoại lệ</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Bốn phần: đơn vị, API, giao diện, kỹ thuật dựa trên kinh nghiệm</t>
+          <t>Đối chiếu loại ngoại lệ với mã trạng thái HTTP</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>NhwNgocc</t>
+          <t>Vòng Minh Quân</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr"/>
@@ -9805,17 +9792,17 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Sửa lỗi và tái cấu trúc giao diện</t>
+          <t>Bản thuyết minh bằng văn bản</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Lỗi rời trang KCPMS-22, trang cố vấn AI</t>
+          <t>Bốn phần: đơn vị, API, giao diện, kỹ thuật dựa trên kinh nghiệm</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Vòng Minh Quân</t>
+          <t>Trần Tô Như Ngọc</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr"/>
@@ -9825,17 +9812,17 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Quy trình CI/CD và triển khai</t>
+          <t>Xây dựng bộ kiểm thử API</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>GitHub Actions, Docker, VPS, chặn deploy khi đỏ</t>
+          <t>Tập lệnh Postman, biến môi trường, bảo đảm chạy lại được nhiều lần</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Vòng Minh Quân · Nguyễn Thành Phát</t>
+          <t>Nguyễn Thành Phát · Vòng Minh Quân</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr"/>
@@ -9845,12 +9832,12 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Phân tích tĩnh và đo bao phủ</t>
+          <t>Xây dựng bộ kiểm thử giao diện</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>SonarCloud, JaCoCo, ngưỡng chặn 65% nhánh</t>
+          <t>CodeceptJS và Playwright, mô hình Page Object</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -9865,32 +9852,92 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Khắc phục khiếm khuyết ứng dụng</t>
+          <t>Sửa lỗi và tái cấu trúc giao diện</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>11 khiếm khuyết, kèm kiểm thử hồi quy</t>
+          <t>Lỗi rời trang KCPMS-22, trang cố vấn AI</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Nguyễn Thành Phát</t>
+          <t>Vòng Minh Quân</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr"/>
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
     </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="55" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Quy trình CI/CD và triển khai</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>GitHub Actions, Docker, VPS, chặn deploy khi đỏ</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Vòng Minh Quân · Nguyễn Thành Phát</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr"/>
+      <c r="G43" s="5" t="inlineStr"/>
+      <c r="H43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Phân tích tĩnh và đo bao phủ</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>SonarCloud, JaCoCo, ngưỡng chặn 65% nhánh</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Nguyễn Thành Phát</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="5" t="inlineStr"/>
+      <c r="H44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Khắc phục khiếm khuyết ứng dụng</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>11 khiếm khuyết, kèm kiểm thử hồi quy</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Nguyễn Thành Phát</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr"/>
+      <c r="G45" s="5" t="inlineStr"/>
+      <c r="H45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="55" t="inlineStr">
         <is>
           <t>Các phần trên nằm trong mã nguồn và tài liệu kèm theo, không trình bày thành bảng riêng trong tệp Excel này. Chi tiết theo tuần xem tệp BaoCao-CongViec-Theo-Tuan.docx.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="58">
+  <mergeCells count="63">
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B25:C25"/>
@@ -9902,31 +9949,36 @@
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D45:E45"/>
     <mergeCell ref="A6:H6"/>
+    <mergeCell ref="B43:C43"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D44:E44"/>
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="D41:E41"/>
+    <mergeCell ref="A46:H46"/>
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B44:C44"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D43:E43"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="D37:E37"/>
     <mergeCell ref="D28:E28"/>
-    <mergeCell ref="A33:H33"/>
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A32:H32"/>
     <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B35:C35"/>
     <mergeCell ref="D39:E39"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="A4:H4"/>
@@ -9937,18 +9989,18 @@
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D42:E42"/>
-    <mergeCell ref="A43:H43"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="D38:E38"/>
+    <mergeCell ref="B45:C45"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="D26:E26"/>
     <mergeCell ref="A31:H31"/>
-    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BaoCao-KiemThu-CareerCompass.xlsx
+++ b/BaoCao-KiemThu-CareerCompass.xlsx
@@ -33,7 +33,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -153,6 +153,11 @@
     </font>
     <font>
       <name val="Consolas"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007F6000"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -362,7 +367,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -536,6 +541,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1635,8 +1643,8 @@
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F22:H22"/>
     <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F22:H22"/>
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="F9:H9"/>
@@ -3165,7 +3173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3195,451 +3203,445 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="30" t="inlineStr">
+    <row r="3" ht="44" customHeight="1">
+      <c r="A3" s="64" t="inlineStr">
+        <is>
+          <t>MỐC THỜI GIAN ĐO: các chỉ số ở sheet này được đo ngày 06/09/2026, ngay sau khi bổ sung phần kiểm thử hộp trắng — giữ nguyên để phép so sánh trước/sau còn ý nghĩa. Nhóm tiếp tục bổ sung test sau mốc đó, nên số liệu HIỆN TẠI (đo 12/09/2026) cao hơn: bao phủ dòng 78,6%, bao phủ nhánh 72,5%. Xem sheet "00. Tong quan" để biết trạng thái mới nhất.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>A - BẢNG SO SÁNH CHỈ SỐ BAO PHỦ (JaCoCo)</t>
         </is>
       </c>
-      <c r="B4" s="27" t="n"/>
-      <c r="C4" s="27" t="n"/>
-      <c r="D4" s="27" t="n"/>
-      <c r="E4" s="27" t="n"/>
-      <c r="F4" s="28" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="B5" s="27" t="n"/>
+      <c r="C5" s="27" t="n"/>
+      <c r="D5" s="27" t="n"/>
+      <c r="E5" s="27" t="n"/>
+      <c r="F5" s="28" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>CHỈ SỐ BAO PHỦ</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>TRƯỚC</t>
         </is>
       </c>
-      <c r="C5" s="31" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>SAU</t>
         </is>
       </c>
-      <c r="D5" s="31" t="inlineStr">
+      <c r="D6" s="31" t="inlineStr">
         <is>
           <t>TĂNG (pp)</t>
         </is>
       </c>
-      <c r="E5" s="31" t="inlineStr">
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t>% TĂNG</t>
         </is>
       </c>
-      <c r="F5" s="31" t="inlineStr">
+      <c r="F6" s="31" t="inlineStr">
         <is>
           <t>NGUỒN</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="38" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="38" t="inlineStr">
         <is>
           <t>Bao phủ Instruction</t>
         </is>
       </c>
-      <c r="B6" s="40" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>60.1%</t>
         </is>
       </c>
-      <c r="C6" s="40" t="inlineStr">
+      <c r="C7" s="40" t="inlineStr">
         <is>
           <t>76.1%</t>
         </is>
       </c>
-      <c r="D6" s="45" t="inlineStr">
+      <c r="D7" s="45" t="inlineStr">
         <is>
           <t>+16.0 pp</t>
         </is>
       </c>
-      <c r="E6" s="40" t="inlineStr">
+      <c r="E7" s="40" t="inlineStr">
         <is>
           <t>+26.6%</t>
         </is>
       </c>
-      <c r="F6" s="40" t="inlineStr">
+      <c r="F7" s="40" t="inlineStr">
         <is>
           <t>JaCoCo</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="35" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>Bao phủ dòng lệnh (Line)</t>
         </is>
       </c>
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>60.1%</t>
         </is>
       </c>
-      <c r="C7" s="37" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>75.5%</t>
         </is>
       </c>
-      <c r="D7" s="45" t="inlineStr">
+      <c r="D8" s="45" t="inlineStr">
         <is>
           <t>+15.4 pp</t>
         </is>
       </c>
-      <c r="E7" s="37" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>+25.6%</t>
         </is>
       </c>
-      <c r="F7" s="37" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>JaCoCo</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="38" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="38" t="inlineStr">
         <is>
           <t>Bao phủ nhánh (Branch)</t>
         </is>
       </c>
-      <c r="B8" s="40" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>48.2%</t>
         </is>
       </c>
-      <c r="C8" s="40" t="inlineStr">
+      <c r="C9" s="40" t="inlineStr">
         <is>
           <t>67.5%</t>
         </is>
       </c>
-      <c r="D8" s="45" t="inlineStr">
+      <c r="D9" s="45" t="inlineStr">
         <is>
           <t>+19.3 pp</t>
         </is>
       </c>
-      <c r="E8" s="40" t="inlineStr">
+      <c r="E9" s="40" t="inlineStr">
         <is>
           <t>+40.0%</t>
         </is>
       </c>
-      <c r="F8" s="40" t="inlineStr">
+      <c r="F9" s="40" t="inlineStr">
         <is>
           <t>JaCoCo</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="35" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>Độ phức tạp được phủ</t>
         </is>
       </c>
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>53.4%</t>
         </is>
       </c>
-      <c r="C9" s="37" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>67.4%</t>
         </is>
       </c>
-      <c r="D9" s="45" t="inlineStr">
+      <c r="D10" s="45" t="inlineStr">
         <is>
           <t>+14.0 pp</t>
         </is>
       </c>
-      <c r="E9" s="37" t="inlineStr">
+      <c r="E10" s="37" t="inlineStr">
         <is>
           <t>+26.3%</t>
         </is>
       </c>
-      <c r="F9" s="37" t="inlineStr">
+      <c r="F10" s="37" t="inlineStr">
         <is>
           <t>JaCoCo</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="38" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>Số phương thức được phủ</t>
         </is>
       </c>
-      <c r="B10" s="40" t="inlineStr">
+      <c r="B11" s="40" t="inlineStr">
         <is>
           <t>65.1%</t>
         </is>
       </c>
-      <c r="C10" s="40" t="inlineStr">
+      <c r="C11" s="40" t="inlineStr">
         <is>
           <t>78.5%</t>
         </is>
       </c>
-      <c r="D10" s="45" t="inlineStr">
+      <c r="D11" s="45" t="inlineStr">
         <is>
           <t>+13.4 pp</t>
         </is>
       </c>
-      <c r="E10" s="40" t="inlineStr">
+      <c r="E11" s="40" t="inlineStr">
         <is>
           <t>+20.6%</t>
         </is>
       </c>
-      <c r="F10" s="40" t="inlineStr">
+      <c r="F11" s="40" t="inlineStr">
         <is>
           <t>JaCoCo</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="30" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>B - KẾT QUẢ CHẠY TEST SUITE</t>
         </is>
       </c>
-      <c r="B12" s="27" t="n"/>
-      <c r="C12" s="27" t="n"/>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="27" t="n"/>
-      <c r="F12" s="28" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="B13" s="27" t="n"/>
+      <c r="C13" s="27" t="n"/>
+      <c r="D13" s="27" t="n"/>
+      <c r="E13" s="27" t="n"/>
+      <c r="F13" s="28" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>CHỈ SỐ</t>
         </is>
       </c>
-      <c r="B13" s="31" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>GIÁ TRỊ</t>
         </is>
       </c>
-      <c r="C13" s="31" t="inlineStr">
+      <c r="C14" s="31" t="inlineStr">
         <is>
           <t>NGƯỠNG</t>
         </is>
       </c>
-      <c r="D13" s="31" t="inlineStr">
+      <c r="D14" s="31" t="inlineStr">
         <is>
           <t>KẾT QUẢ</t>
         </is>
       </c>
-      <c r="E13" s="31" t="inlineStr">
+      <c r="E14" s="31" t="inlineStr">
         <is>
           <t>GHI CHÚ</t>
         </is>
       </c>
-      <c r="F13" s="31" t="inlineStr">
+      <c r="F14" s="31" t="inlineStr">
         <is>
           <t>NGUỒN</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="32" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>Tổng số test</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>370</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D14" s="40" t="inlineStr">
+      <c r="D15" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E14" s="33" t="inlineStr">
+      <c r="E15" s="33" t="inlineStr">
         <is>
           <t>Bao gồm unit + slice tests</t>
         </is>
       </c>
-      <c r="F14" s="33" t="inlineStr">
+      <c r="F15" s="33" t="inlineStr">
         <is>
           <t>Maven Surefire</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="35" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>Test thất bại</t>
         </is>
       </c>
-      <c r="B15" s="37" t="inlineStr">
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C15" s="37" t="inlineStr">
+      <c r="C16" s="37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D15" s="40" t="inlineStr">
+      <c r="D16" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E15" s="36" t="inlineStr">
+      <c r="E16" s="36" t="inlineStr">
         <is>
           <t>Không có test nào bị đỏ</t>
         </is>
       </c>
-      <c r="F15" s="36" t="inlineStr">
+      <c r="F16" s="36" t="inlineStr">
         <is>
           <t>Maven Surefire</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="32" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>Branch coverage</t>
         </is>
       </c>
-      <c r="B16" s="34" t="inlineStr">
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t>67.5%</t>
         </is>
       </c>
-      <c r="C16" s="34" t="inlineStr">
+      <c r="C17" s="34" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="D16" s="40" t="inlineStr">
+      <c r="D17" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E16" s="33" t="inlineStr">
+      <c r="E17" s="33" t="inlineStr">
         <is>
           <t>Vượt ngưỡng JaCoCo check</t>
         </is>
       </c>
-      <c r="F16" s="33" t="inlineStr">
+      <c r="F17" s="33" t="inlineStr">
         <is>
           <t>JaCoCo</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="35" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>Line coverage</t>
         </is>
       </c>
-      <c r="B17" s="37" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>75.5%</t>
         </is>
       </c>
-      <c r="C17" s="37" t="inlineStr">
+      <c r="C18" s="37" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D17" s="40" t="inlineStr">
+      <c r="D18" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E17" s="36" t="inlineStr">
+      <c r="E18" s="36" t="inlineStr">
         <is>
           <t>Không đặt ngưỡng riêng</t>
         </is>
       </c>
-      <c r="F17" s="36" t="inlineStr">
+      <c r="F18" s="36" t="inlineStr">
         <is>
           <t>JaCoCo</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="32" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>Kết quả build</t>
         </is>
       </c>
-      <c r="B18" s="34" t="inlineStr">
+      <c r="B19" s="34" t="inlineStr">
         <is>
           <t>BUILD SUCCESS</t>
         </is>
       </c>
-      <c r="C18" s="34" t="inlineStr">
+      <c r="C19" s="34" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D18" s="40" t="inlineStr">
+      <c r="D19" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E18" s="33" t="inlineStr">
+      <c r="E19" s="33" t="inlineStr">
         <is>
           <t>mvn clean test thành công</t>
         </is>
       </c>
-      <c r="F18" s="33" t="inlineStr">
+      <c r="F19" s="33" t="inlineStr">
         <is>
           <t>Maven</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="30" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>C - NHẬN XÉT VÀ KẾT LUẬN</t>
         </is>
       </c>
-      <c r="B20" s="27" t="n"/>
-      <c r="C20" s="27" t="n"/>
-      <c r="D20" s="27" t="n"/>
-      <c r="E20" s="27" t="n"/>
-      <c r="F20" s="28" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="31" t="inlineStr">
-        <is>
-          <t>VẤN ĐỀ</t>
-        </is>
-      </c>
-      <c r="B21" s="31" t="inlineStr">
-        <is>
-          <t>NỘI DUNG NHẬN XÉT</t>
-        </is>
-      </c>
+      <c r="B21" s="28" t="n"/>
       <c r="C21" s="27" t="n"/>
       <c r="D21" s="27" t="n"/>
       <c r="E21" s="27" t="n"/>
       <c r="F21" s="28" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="32" t="inlineStr">
-        <is>
-          <t>Branch coverage tăng 19.3 pp (48.2% -&gt; 67.5%)</t>
-        </is>
-      </c>
-      <c r="B22" s="33" t="inlineStr">
-        <is>
-          <t>Đây là mức tăng lớn nhất, cho thấy việc bổ sung test white-box đã bao phủ được nhiều nhánh if/else bị bỏ sót.</t>
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>VẤN ĐỀ</t>
+        </is>
+      </c>
+      <c r="B22" s="31" t="inlineStr">
+        <is>
+          <t>NỘI DUNG NHẬN XÉT</t>
         </is>
       </c>
       <c r="C22" s="27" t="n"/>
@@ -3648,14 +3650,14 @@
       <c r="F22" s="28" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="35" t="inlineStr">
-        <is>
-          <t>370 test, 0 failures</t>
-        </is>
-      </c>
-      <c r="B23" s="36" t="inlineStr">
-        <is>
-          <t>Toàn bộ bộ test ổn định, không có regression (lỗi hồi quy).</t>
+      <c r="A23" s="32" t="inlineStr">
+        <is>
+          <t>Branch coverage tăng 19.3 pp (48.2% -&gt; 67.5%)</t>
+        </is>
+      </c>
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>Đây là mức tăng lớn nhất, cho thấy việc bổ sung test white-box đã bao phủ được nhiều nhánh if/else bị bỏ sót.</t>
         </is>
       </c>
       <c r="C23" s="27" t="n"/>
@@ -3664,14 +3666,14 @@
       <c r="F23" s="28" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="32" t="inlineStr">
-        <is>
-          <t>Branch gate 65% đạt (67.5%)</t>
-        </is>
-      </c>
-      <c r="B24" s="33" t="inlineStr">
-        <is>
-          <t>JaCoCo check sẽ fail build nếu branch &lt; 65%. Project vượt ngưỡng này, đảm bảo CI/CD hoạt động trơn tru.</t>
+      <c r="A24" s="35" t="inlineStr">
+        <is>
+          <t>370 test, 0 failures</t>
+        </is>
+      </c>
+      <c r="B24" s="36" t="inlineStr">
+        <is>
+          <t>Toàn bộ bộ test ổn định, không có regression (lỗi hồi quy).</t>
         </is>
       </c>
       <c r="C24" s="27" t="n"/>
@@ -3680,14 +3682,14 @@
       <c r="F24" s="28" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="35" t="inlineStr">
-        <is>
-          <t>GlobalExceptionHandler 100%</t>
-        </is>
-      </c>
-      <c r="B25" s="36" t="inlineStr">
-        <is>
-          <t>File mới thêm đã được test đầy đủ 16/16 nhánh, 158/158 instruction.</t>
+      <c r="A25" s="32" t="inlineStr">
+        <is>
+          <t>Branch gate 65% đạt (67.5%)</t>
+        </is>
+      </c>
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>JaCoCo check sẽ fail build nếu branch &lt; 65%. Project vượt ngưỡng này, đảm bảo CI/CD hoạt động trơn tru.</t>
         </is>
       </c>
       <c r="C25" s="27" t="n"/>
@@ -3695,8 +3697,24 @@
       <c r="E25" s="27" t="n"/>
       <c r="F25" s="28" t="n"/>
     </row>
+    <row r="26">
+      <c r="A26" s="35" t="inlineStr">
+        <is>
+          <t>GlobalExceptionHandler 100%</t>
+        </is>
+      </c>
+      <c r="B26" s="36" t="inlineStr">
+        <is>
+          <t>File mới thêm đã được test đầy đủ 16/16 nhánh, 158/158 instruction.</t>
+        </is>
+      </c>
+      <c r="C26" s="27" t="n"/>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="27" t="n"/>
+      <c r="F26" s="28" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B24:F24"/>
@@ -3706,6 +3724,7 @@
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="B22:F22"/>
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="A20:F20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3718,7 +3737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3754,2548 +3773,2557 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="30" t="inlineStr">
+    <row r="3" ht="44" customHeight="1">
+      <c r="A3" s="64" t="inlineStr">
+        <is>
+          <t>MỐC THỜI GIAN ĐO: các chỉ số ở sheet này được đo ngày 06/09/2026, ngay sau khi bổ sung phần kiểm thử hộp trắng — giữ nguyên để phép so sánh trước/sau còn ý nghĩa. Nhóm tiếp tục bổ sung test sau mốc đó, nên số liệu HIỆN TẠI (đo 12/09/2026) cao hơn: bao phủ dòng 78,6%, bao phủ nhánh 72,5%. Xem sheet "00. Tong quan" để biết trạng thái mới nhất.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>CHI TIẾT ĐỘ BAO PHỦ TỪNG CLASS (WHITE-BOX)</t>
         </is>
       </c>
-      <c r="B4" s="27" t="n"/>
-      <c r="C4" s="27" t="n"/>
-      <c r="D4" s="27" t="n"/>
-      <c r="E4" s="27" t="n"/>
-      <c r="F4" s="27" t="n"/>
-      <c r="G4" s="27" t="n"/>
-      <c r="H4" s="27" t="n"/>
-      <c r="I4" s="28" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="B5" s="27" t="n"/>
+      <c r="C5" s="27" t="n"/>
+      <c r="D5" s="27" t="n"/>
+      <c r="E5" s="27" t="n"/>
+      <c r="F5" s="27" t="n"/>
+      <c r="G5" s="27" t="n"/>
+      <c r="H5" s="27" t="n"/>
+      <c r="I5" s="28" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>Package</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
       </c>
-      <c r="C5" s="31" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>Instruction Covered</t>
         </is>
       </c>
-      <c r="D5" s="31" t="inlineStr">
+      <c r="D6" s="31" t="inlineStr">
         <is>
           <t>Instruction Total</t>
         </is>
       </c>
-      <c r="E5" s="31" t="inlineStr">
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t>Instruction %</t>
         </is>
       </c>
-      <c r="F5" s="31" t="inlineStr">
+      <c r="F6" s="31" t="inlineStr">
         <is>
           <t>Branch Covered</t>
         </is>
       </c>
-      <c r="G5" s="31" t="inlineStr">
+      <c r="G6" s="31" t="inlineStr">
         <is>
           <t>Branch Total</t>
         </is>
       </c>
-      <c r="H5" s="31" t="inlineStr">
+      <c r="H6" s="31" t="inlineStr">
         <is>
           <t>Branch %</t>
         </is>
       </c>
-      <c r="I5" s="31" t="inlineStr">
+      <c r="I6" s="31" t="inlineStr">
         <is>
           <t>Missed Lines</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="33" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>vn.uth.careercompass</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>CareerCompassApplication</t>
         </is>
       </c>
-      <c r="C6" s="34" t="n">
+      <c r="C7" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="34" t="n">
+      <c r="D7" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="E6" s="44" t="inlineStr">
+      <c r="E7" s="44" t="inlineStr">
         <is>
           <t>37.5%</t>
         </is>
       </c>
-      <c r="F6" s="34" t="n">
+      <c r="F7" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="34" t="n">
+      <c r="G7" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="46" t="inlineStr">
+      <c r="H7" s="46" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I6" s="34" t="n">
+      <c r="I7" s="34" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="36" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>admin.config</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>TemplateDataSeeder</t>
         </is>
       </c>
-      <c r="C7" s="37" t="n">
+      <c r="C8" s="37" t="n">
         <v>50</v>
       </c>
-      <c r="D7" s="37" t="n">
+      <c r="D8" s="37" t="n">
         <v>271</v>
       </c>
-      <c r="E7" s="44" t="inlineStr">
+      <c r="E8" s="44" t="inlineStr">
         <is>
           <t>18.5%</t>
         </is>
       </c>
-      <c r="F7" s="37" t="n">
+      <c r="F8" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="G7" s="37" t="n">
+      <c r="G8" s="37" t="n">
         <v>26</v>
       </c>
-      <c r="H7" s="44" t="inlineStr">
+      <c r="H8" s="44" t="inlineStr">
         <is>
           <t>19.2%</t>
         </is>
       </c>
-      <c r="I7" s="37" t="n">
+      <c r="I8" s="37" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="33" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>admin.mapper</t>
         </is>
       </c>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>UserAdminMapper</t>
         </is>
       </c>
-      <c r="C8" s="34" t="n">
+      <c r="C9" s="34" t="n">
         <v>34</v>
       </c>
-      <c r="D8" s="34" t="n">
+      <c r="D9" s="34" t="n">
         <v>44</v>
       </c>
-      <c r="E8" s="47" t="inlineStr">
+      <c r="E9" s="47" t="inlineStr">
         <is>
           <t>77.3%</t>
         </is>
       </c>
-      <c r="F8" s="34" t="n">
+      <c r="F9" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="34" t="n">
+      <c r="G9" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="H8" s="47" t="inlineStr">
+      <c r="H9" s="47" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="I8" s="34" t="n">
+      <c r="I9" s="34" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>admin.service</t>
         </is>
       </c>
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>AdminDashboardService</t>
         </is>
       </c>
-      <c r="C9" s="37" t="n">
+      <c r="C10" s="37" t="n">
         <v>82</v>
       </c>
-      <c r="D9" s="37" t="n">
+      <c r="D10" s="37" t="n">
         <v>82</v>
       </c>
-      <c r="E9" s="45" t="inlineStr">
+      <c r="E10" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F9" s="37" t="n">
+      <c r="F10" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="37" t="n">
+      <c r="G10" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="48" t="inlineStr">
+      <c r="H10" s="48" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I9" s="37" t="n">
+      <c r="I10" s="37" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="33" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>admin.service</t>
         </is>
       </c>
-      <c r="B10" s="32" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>AdminUserService</t>
         </is>
       </c>
-      <c r="C10" s="34" t="n">
+      <c r="C11" s="34" t="n">
         <v>150</v>
       </c>
-      <c r="D10" s="34" t="n">
+      <c r="D11" s="34" t="n">
         <v>150</v>
       </c>
-      <c r="E10" s="45" t="inlineStr">
+      <c r="E11" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F10" s="34" t="n">
+      <c r="F11" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="G10" s="34" t="n">
+      <c r="G11" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="H10" s="45" t="inlineStr">
+      <c r="H11" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I10" s="34" t="n">
+      <c r="I11" s="34" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>admin.service</t>
         </is>
       </c>
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>CounselorTemplateService</t>
         </is>
       </c>
-      <c r="C11" s="37" t="n">
+      <c r="C12" s="37" t="n">
         <v>495</v>
       </c>
-      <c r="D11" s="37" t="n">
+      <c r="D12" s="37" t="n">
         <v>495</v>
       </c>
-      <c r="E11" s="45" t="inlineStr">
+      <c r="E12" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F11" s="37" t="n">
+      <c r="F12" s="37" t="n">
         <v>28</v>
       </c>
-      <c r="G11" s="37" t="n">
+      <c r="G12" s="37" t="n">
         <v>30</v>
       </c>
-      <c r="H11" s="45" t="inlineStr">
+      <c r="H12" s="45" t="inlineStr">
         <is>
           <t>93.3%</t>
         </is>
       </c>
-      <c r="I11" s="37" t="n">
+      <c r="I12" s="37" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="33" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>admin.web</t>
         </is>
       </c>
-      <c r="B12" s="32" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>AdminDashboardController</t>
         </is>
       </c>
-      <c r="C12" s="34" t="n">
+      <c r="C13" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="34" t="n">
+      <c r="D13" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="E12" s="44" t="inlineStr">
+      <c r="E13" s="44" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F12" s="34" t="n">
+      <c r="F13" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="34" t="n">
+      <c r="G13" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="46" t="inlineStr">
+      <c r="H13" s="46" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I12" s="34" t="n">
+      <c r="I13" s="34" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="36" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>admin.web</t>
         </is>
       </c>
-      <c r="B13" s="35" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>AdminUserController</t>
         </is>
       </c>
-      <c r="C13" s="37" t="n">
+      <c r="C14" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="37" t="n">
+      <c r="D14" s="37" t="n">
         <v>81</v>
       </c>
-      <c r="E13" s="44" t="inlineStr">
+      <c r="E14" s="44" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F13" s="37" t="n">
+      <c r="F14" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="37" t="n">
+      <c r="G14" s="37" t="n">
         <v>8</v>
       </c>
-      <c r="H13" s="44" t="inlineStr">
+      <c r="H14" s="44" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I13" s="37" t="n">
+      <c r="I14" s="37" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="33" t="inlineStr">
         <is>
           <t>admin.web</t>
         </is>
       </c>
-      <c r="B14" s="32" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>CounselorTemplateController</t>
         </is>
       </c>
-      <c r="C14" s="34" t="n">
+      <c r="C15" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="34" t="n">
+      <c r="D15" s="34" t="n">
         <v>401</v>
       </c>
-      <c r="E14" s="44" t="inlineStr">
+      <c r="E15" s="44" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F14" s="34" t="n">
+      <c r="F15" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="34" t="n">
+      <c r="G15" s="34" t="n">
         <v>20</v>
       </c>
-      <c r="H14" s="44" t="inlineStr">
+      <c r="H15" s="44" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I14" s="34" t="n">
+      <c r="I15" s="34" t="n">
         <v>82</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="36" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>config</t>
         </is>
       </c>
-      <c r="B15" s="35" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>DataSeeder</t>
         </is>
       </c>
-      <c r="C15" s="37" t="n">
+      <c r="C16" s="37" t="n">
         <v>56</v>
       </c>
-      <c r="D15" s="37" t="n">
+      <c r="D16" s="37" t="n">
         <v>118</v>
       </c>
-      <c r="E15" s="44" t="inlineStr">
+      <c r="E16" s="44" t="inlineStr">
         <is>
           <t>47.5%</t>
         </is>
       </c>
-      <c r="F15" s="37" t="n">
+      <c r="F16" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="G15" s="37" t="n">
+      <c r="G16" s="37" t="n">
         <v>9</v>
       </c>
-      <c r="H15" s="44" t="inlineStr">
+      <c r="H16" s="44" t="inlineStr">
         <is>
           <t>44.4%</t>
         </is>
       </c>
-      <c r="I15" s="37" t="n">
+      <c r="I16" s="37" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="33" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>config</t>
         </is>
       </c>
-      <c r="B16" s="32" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>GlobalExceptionHandler</t>
         </is>
       </c>
-      <c r="C16" s="34" t="n">
+      <c r="C17" s="34" t="n">
         <v>158</v>
       </c>
-      <c r="D16" s="34" t="n">
+      <c r="D17" s="34" t="n">
         <v>158</v>
       </c>
-      <c r="E16" s="45" t="inlineStr">
+      <c r="E17" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F16" s="34" t="n">
+      <c r="F17" s="34" t="n">
         <v>16</v>
       </c>
-      <c r="G16" s="34" t="n">
+      <c r="G17" s="34" t="n">
         <v>16</v>
       </c>
-      <c r="H16" s="45" t="inlineStr">
+      <c r="H17" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I16" s="34" t="n">
+      <c r="I17" s="34" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="36" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>config</t>
         </is>
       </c>
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B18" s="35" t="inlineStr">
         <is>
           <t>GlobalModelAdvice</t>
         </is>
       </c>
-      <c r="C17" s="37" t="n">
+      <c r="C18" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="37" t="n">
+      <c r="D18" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="45" t="inlineStr">
+      <c r="E18" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F17" s="37" t="n">
+      <c r="F18" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="37" t="n">
+      <c r="G18" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="48" t="inlineStr">
+      <c r="H18" s="48" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I17" s="37" t="n">
+      <c r="I18" s="37" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="33" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="33" t="inlineStr">
         <is>
           <t>config</t>
         </is>
       </c>
-      <c r="B18" s="32" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>OnboardingInterceptor</t>
         </is>
       </c>
-      <c r="C18" s="34" t="n">
+      <c r="C19" s="34" t="n">
         <v>80</v>
       </c>
-      <c r="D18" s="34" t="n">
+      <c r="D19" s="34" t="n">
         <v>122</v>
       </c>
-      <c r="E18" s="47" t="inlineStr">
+      <c r="E19" s="47" t="inlineStr">
         <is>
           <t>65.6%</t>
         </is>
       </c>
-      <c r="F18" s="34" t="n">
+      <c r="F19" s="34" t="n">
         <v>18</v>
       </c>
-      <c r="G18" s="34" t="n">
+      <c r="G19" s="34" t="n">
         <v>40</v>
       </c>
-      <c r="H18" s="44" t="inlineStr">
+      <c r="H19" s="44" t="inlineStr">
         <is>
           <t>45.0%</t>
         </is>
       </c>
-      <c r="I18" s="34" t="n">
+      <c r="I19" s="34" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="36" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>config</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>SecurityConfig</t>
         </is>
       </c>
-      <c r="C19" s="37" t="n">
+      <c r="C20" s="37" t="n">
         <v>134</v>
       </c>
-      <c r="D19" s="37" t="n">
+      <c r="D20" s="37" t="n">
         <v>134</v>
       </c>
-      <c r="E19" s="45" t="inlineStr">
+      <c r="E20" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F19" s="37" t="n">
+      <c r="F20" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="37" t="n">
+      <c r="G20" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="48" t="inlineStr">
+      <c r="H20" s="48" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I19" s="37" t="n">
+      <c r="I20" s="37" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="33" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="33" t="inlineStr">
         <is>
           <t>config</t>
         </is>
       </c>
-      <c r="B20" s="32" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>WebMvcConfig</t>
         </is>
       </c>
-      <c r="C20" s="34" t="n">
+      <c r="C21" s="34" t="n">
         <v>93</v>
       </c>
-      <c r="D20" s="34" t="n">
+      <c r="D21" s="34" t="n">
         <v>93</v>
       </c>
-      <c r="E20" s="45" t="inlineStr">
+      <c r="E21" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F20" s="34" t="n">
+      <c r="F21" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="34" t="n">
+      <c r="G21" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="46" t="inlineStr">
+      <c r="H21" s="46" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I20" s="34" t="n">
+      <c r="I21" s="34" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="36" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="36" t="inlineStr">
         <is>
           <t>dashboard.controller</t>
         </is>
       </c>
-      <c r="B21" s="35" t="inlineStr">
+      <c r="B22" s="35" t="inlineStr">
         <is>
           <t>DashboardController</t>
         </is>
       </c>
-      <c r="C21" s="37" t="n">
+      <c r="C22" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="37" t="n">
+      <c r="D22" s="37" t="n">
         <v>20</v>
       </c>
-      <c r="E21" s="44" t="inlineStr">
+      <c r="E22" s="44" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F21" s="37" t="n">
+      <c r="F22" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="37" t="n">
+      <c r="G22" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="48" t="inlineStr">
+      <c r="H22" s="48" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I21" s="37" t="n">
+      <c r="I22" s="37" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="33" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="33" t="inlineStr">
         <is>
           <t>dashboard.dto</t>
         </is>
       </c>
-      <c r="B22" s="32" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>ActivityLogDTO</t>
         </is>
       </c>
-      <c r="C22" s="34" t="n">
+      <c r="C23" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="D22" s="34" t="n">
+      <c r="D23" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="E22" s="45" t="inlineStr">
+      <c r="E23" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F22" s="34" t="n">
+      <c r="F23" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="34" t="n">
+      <c r="G23" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="46" t="inlineStr">
+      <c r="H23" s="46" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I22" s="34" t="n">
+      <c r="I23" s="34" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="36" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>dashboard.service</t>
         </is>
       </c>
-      <c r="B23" s="35" t="inlineStr">
+      <c r="B24" s="35" t="inlineStr">
         <is>
           <t>DashboardService</t>
         </is>
       </c>
-      <c r="C23" s="37" t="n">
+      <c r="C24" s="37" t="n">
         <v>52</v>
       </c>
-      <c r="D23" s="37" t="n">
+      <c r="D24" s="37" t="n">
         <v>52</v>
       </c>
-      <c r="E23" s="45" t="inlineStr">
+      <c r="E24" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F23" s="37" t="n">
+      <c r="F24" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="37" t="n">
+      <c r="G24" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="48" t="inlineStr">
+      <c r="H24" s="48" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I23" s="37" t="n">
+      <c r="I24" s="37" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="33" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="33" t="inlineStr">
         <is>
           <t>kernel.entity</t>
         </is>
       </c>
-      <c r="B24" s="32" t="inlineStr">
+      <c r="B25" s="32" t="inlineStr">
         <is>
           <t>AuthProvider</t>
         </is>
       </c>
-      <c r="C24" s="34" t="n">
+      <c r="C25" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="D24" s="34" t="n">
+      <c r="D25" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="E24" s="45" t="inlineStr">
+      <c r="E25" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F24" s="34" t="n">
+      <c r="F25" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="34" t="n">
+      <c r="G25" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="46" t="inlineStr">
+      <c r="H25" s="46" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I24" s="34" t="n">
+      <c r="I25" s="34" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="36" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>kernel.entity</t>
         </is>
       </c>
-      <c r="B25" s="35" t="inlineStr">
+      <c r="B26" s="35" t="inlineStr">
         <is>
           <t>PasswordResetToken</t>
         </is>
       </c>
-      <c r="C25" s="37" t="n">
+      <c r="C26" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="D25" s="37" t="n">
+      <c r="D26" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="E25" s="45" t="inlineStr">
+      <c r="E26" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F25" s="37" t="n">
+      <c r="F26" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="G25" s="37" t="n">
+      <c r="G26" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="H25" s="45" t="inlineStr">
+      <c r="H26" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I25" s="37" t="n">
+      <c r="I26" s="37" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="33" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="33" t="inlineStr">
         <is>
           <t>kernel.entity</t>
         </is>
       </c>
-      <c r="B26" s="32" t="inlineStr">
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>RoleName</t>
         </is>
       </c>
-      <c r="C26" s="34" t="n">
+      <c r="C27" s="34" t="n">
         <v>21</v>
       </c>
-      <c r="D26" s="34" t="n">
+      <c r="D27" s="34" t="n">
         <v>21</v>
       </c>
-      <c r="E26" s="45" t="inlineStr">
+      <c r="E27" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F26" s="34" t="n">
+      <c r="F27" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="34" t="n">
+      <c r="G27" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="46" t="inlineStr">
+      <c r="H27" s="46" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I26" s="34" t="n">
+      <c r="I27" s="34" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="36" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="36" t="inlineStr">
         <is>
           <t>kernel.entity</t>
         </is>
       </c>
-      <c r="B27" s="35" t="inlineStr">
+      <c r="B28" s="35" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="C27" s="37" t="n">
+      <c r="C28" s="37" t="n">
         <v>9</v>
       </c>
-      <c r="D27" s="37" t="n">
+      <c r="D28" s="37" t="n">
         <v>9</v>
       </c>
-      <c r="E27" s="45" t="inlineStr">
+      <c r="E28" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F27" s="37" t="n">
+      <c r="F28" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="G27" s="37" t="n">
+      <c r="G28" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="H27" s="45" t="inlineStr">
+      <c r="H28" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I27" s="37" t="n">
+      <c r="I28" s="37" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="33" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="33" t="inlineStr">
         <is>
           <t>kernel.exception</t>
         </is>
       </c>
-      <c r="B28" s="32" t="inlineStr">
+      <c r="B29" s="32" t="inlineStr">
         <is>
           <t>EmailAlreadyExistsException</t>
         </is>
       </c>
-      <c r="C28" s="34" t="n">
+      <c r="C29" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="D28" s="34" t="n">
+      <c r="D29" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="E28" s="45" t="inlineStr">
+      <c r="E29" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F28" s="34" t="n">
+      <c r="F29" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="34" t="n">
+      <c r="G29" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="46" t="inlineStr">
+      <c r="H29" s="46" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I28" s="34" t="n">
+      <c r="I29" s="34" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="36" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>kernel.security</t>
         </is>
       </c>
-      <c r="B29" s="35" t="inlineStr">
+      <c r="B30" s="35" t="inlineStr">
         <is>
           <t>CustomUserDetails</t>
         </is>
       </c>
-      <c r="C29" s="37" t="n">
+      <c r="C30" s="37" t="n">
         <v>17</v>
       </c>
-      <c r="D29" s="37" t="n">
+      <c r="D30" s="37" t="n">
         <v>39</v>
       </c>
-      <c r="E29" s="44" t="inlineStr">
+      <c r="E30" s="44" t="inlineStr">
         <is>
           <t>43.6%</t>
         </is>
       </c>
-      <c r="F29" s="37" t="n">
+      <c r="F30" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="37" t="n">
+      <c r="G30" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="48" t="inlineStr">
+      <c r="H30" s="48" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I29" s="37" t="n">
+      <c r="I30" s="37" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="33" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="33" t="inlineStr">
         <is>
           <t>kernel.service</t>
         </is>
       </c>
-      <c r="B30" s="32" t="inlineStr">
+      <c r="B31" s="32" t="inlineStr">
         <is>
           <t>ActivityLogService</t>
         </is>
       </c>
-      <c r="C30" s="34" t="n">
+      <c r="C31" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="D30" s="34" t="n">
+      <c r="D31" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="E30" s="45" t="inlineStr">
+      <c r="E31" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F30" s="34" t="n">
+      <c r="F31" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="34" t="n">
+      <c r="G31" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="46" t="inlineStr">
+      <c r="H31" s="46" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I30" s="34" t="n">
+      <c r="I31" s="34" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="36" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="36" t="inlineStr">
         <is>
           <t>kernel.service</t>
         </is>
       </c>
-      <c r="B31" s="35" t="inlineStr">
+      <c r="B32" s="35" t="inlineStr">
         <is>
           <t>AuthService</t>
         </is>
       </c>
-      <c r="C31" s="37" t="n">
+      <c r="C32" s="37" t="n">
         <v>53</v>
       </c>
-      <c r="D31" s="37" t="n">
+      <c r="D32" s="37" t="n">
         <v>53</v>
       </c>
-      <c r="E31" s="45" t="inlineStr">
+      <c r="E32" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F31" s="37" t="n">
+      <c r="F32" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="G31" s="37" t="n">
+      <c r="G32" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="H31" s="45" t="inlineStr">
+      <c r="H32" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I31" s="37" t="n">
+      <c r="I32" s="37" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="33" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="33" t="inlineStr">
         <is>
           <t>kernel.service</t>
         </is>
       </c>
-      <c r="B32" s="32" t="inlineStr">
+      <c r="B33" s="32" t="inlineStr">
         <is>
           <t>AuthenticatedUserService</t>
         </is>
       </c>
-      <c r="C32" s="34" t="n">
+      <c r="C33" s="34" t="n">
         <v>82</v>
       </c>
-      <c r="D32" s="34" t="n">
+      <c r="D33" s="34" t="n">
         <v>84</v>
       </c>
-      <c r="E32" s="45" t="inlineStr">
+      <c r="E33" s="45" t="inlineStr">
         <is>
           <t>97.6%</t>
         </is>
       </c>
-      <c r="F32" s="34" t="n">
+      <c r="F33" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="G32" s="34" t="n">
+      <c r="G33" s="34" t="n">
         <v>18</v>
       </c>
-      <c r="H32" s="45" t="inlineStr">
+      <c r="H33" s="45" t="inlineStr">
         <is>
           <t>83.3%</t>
         </is>
       </c>
-      <c r="I32" s="34" t="n">
+      <c r="I33" s="34" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="36" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="36" t="inlineStr">
         <is>
           <t>kernel.service</t>
         </is>
       </c>
-      <c r="B33" s="35" t="inlineStr">
+      <c r="B34" s="35" t="inlineStr">
         <is>
           <t>CustomOidcUserService</t>
         </is>
       </c>
-      <c r="C33" s="37" t="n">
+      <c r="C34" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="37" t="n">
+      <c r="D34" s="37" t="n">
         <v>86</v>
       </c>
-      <c r="E33" s="44" t="inlineStr">
+      <c r="E34" s="44" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F33" s="37" t="n">
+      <c r="F34" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="G33" s="37" t="n">
+      <c r="G34" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="48" t="inlineStr">
+      <c r="H34" s="48" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I33" s="37" t="n">
+      <c r="I34" s="37" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="33" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="33" t="inlineStr">
         <is>
           <t>kernel.service</t>
         </is>
       </c>
-      <c r="B34" s="32" t="inlineStr">
+      <c r="B35" s="32" t="inlineStr">
         <is>
           <t>CustomUserDetailsService</t>
         </is>
       </c>
-      <c r="C34" s="34" t="n">
+      <c r="C35" s="34" t="n">
         <v>20</v>
       </c>
-      <c r="D34" s="34" t="n">
+      <c r="D35" s="34" t="n">
         <v>20</v>
       </c>
-      <c r="E34" s="45" t="inlineStr">
+      <c r="E35" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F34" s="34" t="n">
+      <c r="F35" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G34" s="34" t="n">
+      <c r="G35" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="46" t="inlineStr">
+      <c r="H35" s="46" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I34" s="34" t="n">
+      <c r="I35" s="34" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="36" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="36" t="inlineStr">
         <is>
           <t>kernel.service</t>
         </is>
       </c>
-      <c r="B35" s="35" t="inlineStr">
+      <c r="B36" s="35" t="inlineStr">
         <is>
           <t>MarkdownRenderer</t>
         </is>
       </c>
-      <c r="C35" s="37" t="n">
+      <c r="C36" s="37" t="n">
         <v>28</v>
       </c>
-      <c r="D35" s="37" t="n">
+      <c r="D36" s="37" t="n">
         <v>28</v>
       </c>
-      <c r="E35" s="45" t="inlineStr">
+      <c r="E36" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F35" s="37" t="n">
+      <c r="F36" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="G35" s="37" t="n">
+      <c r="G36" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="H35" s="45" t="inlineStr">
+      <c r="H36" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I35" s="37" t="n">
+      <c r="I36" s="37" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="33" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="33" t="inlineStr">
         <is>
           <t>kernel.service</t>
         </is>
       </c>
-      <c r="B36" s="32" t="inlineStr">
+      <c r="B37" s="32" t="inlineStr">
         <is>
           <t>PasswordResetService</t>
         </is>
       </c>
-      <c r="C36" s="34" t="n">
+      <c r="C37" s="34" t="n">
         <v>93</v>
       </c>
-      <c r="D36" s="34" t="n">
+      <c r="D37" s="34" t="n">
         <v>93</v>
       </c>
-      <c r="E36" s="45" t="inlineStr">
+      <c r="E37" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F36" s="34" t="n">
+      <c r="F37" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="G36" s="34" t="n">
+      <c r="G37" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="H36" s="45" t="inlineStr">
+      <c r="H37" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I36" s="34" t="n">
+      <c r="I37" s="34" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="36" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="36" t="inlineStr">
         <is>
           <t>kernel.service</t>
         </is>
       </c>
-      <c r="B37" s="35" t="inlineStr">
+      <c r="B38" s="35" t="inlineStr">
         <is>
           <t>SmtpEmailService</t>
         </is>
       </c>
-      <c r="C37" s="37" t="n">
+      <c r="C38" s="37" t="n">
         <v>22</v>
       </c>
-      <c r="D37" s="37" t="n">
+      <c r="D38" s="37" t="n">
         <v>22</v>
       </c>
-      <c r="E37" s="45" t="inlineStr">
+      <c r="E38" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F37" s="37" t="n">
+      <c r="F38" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="G37" s="37" t="n">
+      <c r="G38" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="48" t="inlineStr">
+      <c r="H38" s="48" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I37" s="37" t="n">
+      <c r="I38" s="37" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="33" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="33" t="inlineStr">
         <is>
           <t>kernel.service</t>
         </is>
       </c>
-      <c r="B38" s="32" t="inlineStr">
+      <c r="B39" s="32" t="inlineStr">
         <is>
           <t>UserProfileService</t>
         </is>
       </c>
-      <c r="C38" s="34" t="n">
+      <c r="C39" s="34" t="n">
         <v>110</v>
       </c>
-      <c r="D38" s="34" t="n">
+      <c r="D39" s="34" t="n">
         <v>110</v>
       </c>
-      <c r="E38" s="45" t="inlineStr">
+      <c r="E39" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F38" s="34" t="n">
+      <c r="F39" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="G38" s="34" t="n">
+      <c r="G39" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="H38" s="45" t="inlineStr">
+      <c r="H39" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I38" s="34" t="n">
+      <c r="I39" s="34" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="36" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="36" t="inlineStr">
         <is>
           <t>kernel.web.controller</t>
         </is>
       </c>
-      <c r="B39" s="35" t="inlineStr">
+      <c r="B40" s="35" t="inlineStr">
         <is>
           <t>AuthController</t>
         </is>
       </c>
-      <c r="C39" s="37" t="n">
+      <c r="C40" s="37" t="n">
         <v>119</v>
       </c>
-      <c r="D39" s="37" t="n">
+      <c r="D40" s="37" t="n">
         <v>119</v>
       </c>
-      <c r="E39" s="45" t="inlineStr">
+      <c r="E40" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F39" s="37" t="n">
+      <c r="F40" s="37" t="n">
         <v>7</v>
       </c>
-      <c r="G39" s="37" t="n">
+      <c r="G40" s="37" t="n">
         <v>8</v>
       </c>
-      <c r="H39" s="45" t="inlineStr">
+      <c r="H40" s="45" t="inlineStr">
         <is>
           <t>87.5%</t>
         </is>
       </c>
-      <c r="I39" s="37" t="n">
+      <c r="I40" s="37" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="33" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="33" t="inlineStr">
         <is>
           <t>kernel.web.controller</t>
         </is>
       </c>
-      <c r="B40" s="32" t="inlineStr">
+      <c r="B41" s="32" t="inlineStr">
         <is>
           <t>HomeController</t>
         </is>
       </c>
-      <c r="C40" s="34" t="n">
+      <c r="C41" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="D40" s="34" t="n">
+      <c r="D41" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="E40" s="45" t="inlineStr">
+      <c r="E41" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F40" s="34" t="n">
+      <c r="F41" s="34" t="n">
         <v>11</v>
       </c>
-      <c r="G40" s="34" t="n">
+      <c r="G41" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="H40" s="45" t="inlineStr">
+      <c r="H41" s="45" t="inlineStr">
         <is>
           <t>91.7%</t>
         </is>
       </c>
-      <c r="I40" s="34" t="n">
+      <c r="I41" s="34" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="36" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="36" t="inlineStr">
         <is>
           <t>marketpulse.config</t>
         </is>
       </c>
-      <c r="B41" s="35" t="inlineStr">
+      <c r="B42" s="35" t="inlineStr">
         <is>
           <t>JobTrendSeeder</t>
         </is>
       </c>
-      <c r="C41" s="37" t="n">
+      <c r="C42" s="37" t="n">
         <v>7</v>
       </c>
-      <c r="D41" s="37" t="n">
+      <c r="D42" s="37" t="n">
         <v>180</v>
       </c>
-      <c r="E41" s="44" t="inlineStr">
+      <c r="E42" s="44" t="inlineStr">
         <is>
           <t>3.9%</t>
         </is>
       </c>
-      <c r="F41" s="37" t="n">
+      <c r="F42" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="37" t="n">
+      <c r="G42" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="H41" s="44" t="inlineStr">
+      <c r="H42" s="44" t="inlineStr">
         <is>
           <t>25.0%</t>
         </is>
       </c>
-      <c r="I41" s="37" t="n">
+      <c r="I42" s="37" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="33" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="33" t="inlineStr">
         <is>
           <t>marketpulse.controller</t>
         </is>
       </c>
-      <c r="B42" s="32" t="inlineStr">
+      <c r="B43" s="32" t="inlineStr">
         <is>
           <t>MarketPulseController</t>
         </is>
       </c>
-      <c r="C42" s="34" t="n">
+      <c r="C43" s="34" t="n">
         <v>14</v>
       </c>
-      <c r="D42" s="34" t="n">
+      <c r="D43" s="34" t="n">
         <v>14</v>
       </c>
-      <c r="E42" s="45" t="inlineStr">
+      <c r="E43" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F42" s="34" t="n">
+      <c r="F43" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G42" s="34" t="n">
+      <c r="G43" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="46" t="inlineStr">
+      <c r="H43" s="46" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I42" s="34" t="n">
+      <c r="I43" s="34" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="36" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="36" t="inlineStr">
         <is>
           <t>marketpulse.dto</t>
         </is>
       </c>
-      <c r="B43" s="35" t="inlineStr">
+      <c r="B44" s="35" t="inlineStr">
         <is>
           <t>JobTrendDTO</t>
         </is>
       </c>
-      <c r="C43" s="37" t="n">
+      <c r="C44" s="37" t="n">
         <v>18</v>
       </c>
-      <c r="D43" s="37" t="n">
+      <c r="D44" s="37" t="n">
         <v>18</v>
       </c>
-      <c r="E43" s="45" t="inlineStr">
+      <c r="E44" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F43" s="37" t="n">
+      <c r="F44" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="37" t="n">
+      <c r="G44" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="48" t="inlineStr">
+      <c r="H44" s="48" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I43" s="37" t="n">
+      <c r="I44" s="37" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="33" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="33" t="inlineStr">
         <is>
           <t>marketpulse.service</t>
         </is>
       </c>
-      <c r="B44" s="32" t="inlineStr">
+      <c r="B45" s="32" t="inlineStr">
         <is>
           <t>KeywordAnalysisService</t>
         </is>
       </c>
-      <c r="C44" s="34" t="n">
+      <c r="C45" s="34" t="n">
         <v>139</v>
       </c>
-      <c r="D44" s="34" t="n">
+      <c r="D45" s="34" t="n">
         <v>139</v>
       </c>
-      <c r="E44" s="45" t="inlineStr">
+      <c r="E45" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F44" s="34" t="n">
+      <c r="F45" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="G44" s="34" t="n">
+      <c r="G45" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="H44" s="45" t="inlineStr">
+      <c r="H45" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I44" s="34" t="n">
+      <c r="I45" s="34" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="36" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="36" t="inlineStr">
         <is>
           <t>marketpulse.service</t>
         </is>
       </c>
-      <c r="B45" s="35" t="inlineStr">
+      <c r="B46" s="35" t="inlineStr">
         <is>
           <t>MarketPulseService</t>
         </is>
       </c>
-      <c r="C45" s="37" t="n">
+      <c r="C46" s="37" t="n">
         <v>28</v>
       </c>
-      <c r="D45" s="37" t="n">
+      <c r="D46" s="37" t="n">
         <v>28</v>
       </c>
-      <c r="E45" s="45" t="inlineStr">
+      <c r="E46" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F45" s="37" t="n">
+      <c r="F46" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="G45" s="37" t="n">
+      <c r="G46" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="48" t="inlineStr">
+      <c r="H46" s="48" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I45" s="37" t="n">
+      <c r="I46" s="37" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="33" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="33" t="inlineStr">
         <is>
           <t>marketpulse.service</t>
         </is>
       </c>
-      <c r="B46" s="32" t="inlineStr">
+      <c r="B47" s="32" t="inlineStr">
         <is>
           <t>ScraperService</t>
         </is>
       </c>
-      <c r="C46" s="34" t="n">
+      <c r="C47" s="34" t="n">
         <v>343</v>
       </c>
-      <c r="D46" s="34" t="n">
+      <c r="D47" s="34" t="n">
         <v>350</v>
       </c>
-      <c r="E46" s="45" t="inlineStr">
+      <c r="E47" s="45" t="inlineStr">
         <is>
           <t>98.0%</t>
         </is>
       </c>
-      <c r="F46" s="34" t="n">
+      <c r="F47" s="34" t="n">
         <v>18</v>
       </c>
-      <c r="G46" s="34" t="n">
+      <c r="G47" s="34" t="n">
         <v>20</v>
       </c>
-      <c r="H46" s="45" t="inlineStr">
+      <c r="H47" s="45" t="inlineStr">
         <is>
           <t>90.0%</t>
         </is>
       </c>
-      <c r="I46" s="34" t="n">
+      <c r="I47" s="34" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="36" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="36" t="inlineStr">
         <is>
           <t>mentor.controller</t>
         </is>
       </c>
-      <c r="B47" s="35" t="inlineStr">
+      <c r="B48" s="35" t="inlineStr">
         <is>
           <t>MentorController</t>
         </is>
       </c>
-      <c r="C47" s="37" t="n">
+      <c r="C48" s="37" t="n">
         <v>108</v>
       </c>
-      <c r="D47" s="37" t="n">
+      <c r="D48" s="37" t="n">
         <v>152</v>
       </c>
-      <c r="E47" s="47" t="inlineStr">
+      <c r="E48" s="47" t="inlineStr">
         <is>
           <t>71.1%</t>
         </is>
       </c>
-      <c r="F47" s="37" t="n">
+      <c r="F48" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="G47" s="37" t="n">
+      <c r="G48" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="H47" s="47" t="inlineStr">
+      <c r="H48" s="47" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="I47" s="37" t="n">
+      <c r="I48" s="37" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="33" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="33" t="inlineStr">
         <is>
           <t>mentor.entity</t>
         </is>
       </c>
-      <c r="B48" s="32" t="inlineStr">
+      <c r="B49" s="32" t="inlineStr">
         <is>
           <t>Sender</t>
         </is>
       </c>
-      <c r="C48" s="34" t="n">
+      <c r="C49" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="D48" s="34" t="n">
+      <c r="D49" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="E48" s="45" t="inlineStr">
+      <c r="E49" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F48" s="34" t="n">
+      <c r="F49" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G48" s="34" t="n">
+      <c r="G49" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="46" t="inlineStr">
+      <c r="H49" s="46" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I48" s="34" t="n">
+      <c r="I49" s="34" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="36" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="36" t="inlineStr">
         <is>
           <t>mentor.service</t>
         </is>
       </c>
-      <c r="B49" s="35" t="inlineStr">
+      <c r="B50" s="35" t="inlineStr">
         <is>
           <t>LlmClient</t>
         </is>
       </c>
-      <c r="C49" s="37" t="n">
+      <c r="C50" s="37" t="n">
         <v>9</v>
       </c>
-      <c r="D49" s="37" t="n">
+      <c r="D50" s="37" t="n">
         <v>104</v>
       </c>
-      <c r="E49" s="44" t="inlineStr">
+      <c r="E50" s="44" t="inlineStr">
         <is>
           <t>8.7%</t>
         </is>
       </c>
-      <c r="F49" s="37" t="n">
+      <c r="F50" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="G49" s="37" t="n">
+      <c r="G50" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="H49" s="44" t="inlineStr">
+      <c r="H50" s="44" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I49" s="37" t="n">
+      <c r="I50" s="37" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="33" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="33" t="inlineStr">
         <is>
           <t>mentor.service</t>
         </is>
       </c>
-      <c r="B50" s="32" t="inlineStr">
+      <c r="B51" s="32" t="inlineStr">
         <is>
           <t>MentorService</t>
         </is>
       </c>
-      <c r="C50" s="34" t="n">
+      <c r="C51" s="34" t="n">
         <v>175</v>
       </c>
-      <c r="D50" s="34" t="n">
+      <c r="D51" s="34" t="n">
         <v>175</v>
       </c>
-      <c r="E50" s="45" t="inlineStr">
+      <c r="E51" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F50" s="34" t="n">
+      <c r="F51" s="34" t="n">
         <v>14</v>
       </c>
-      <c r="G50" s="34" t="n">
+      <c r="G51" s="34" t="n">
         <v>16</v>
       </c>
-      <c r="H50" s="45" t="inlineStr">
+      <c r="H51" s="45" t="inlineStr">
         <is>
           <t>87.5%</t>
         </is>
       </c>
-      <c r="I50" s="34" t="n">
+      <c r="I51" s="34" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="36" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="36" t="inlineStr">
         <is>
           <t>onboarding.controller</t>
         </is>
       </c>
-      <c r="B51" s="35" t="inlineStr">
+      <c r="B52" s="35" t="inlineStr">
         <is>
           <t>OnboardingController</t>
         </is>
       </c>
-      <c r="C51" s="37" t="n">
+      <c r="C52" s="37" t="n">
         <v>13</v>
       </c>
-      <c r="D51" s="37" t="n">
+      <c r="D52" s="37" t="n">
         <v>295</v>
       </c>
-      <c r="E51" s="44" t="inlineStr">
+      <c r="E52" s="44" t="inlineStr">
         <is>
           <t>4.4%</t>
         </is>
       </c>
-      <c r="F51" s="37" t="n">
+      <c r="F52" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="G51" s="37" t="n">
+      <c r="G52" s="37" t="n">
         <v>40</v>
       </c>
-      <c r="H51" s="44" t="inlineStr">
+      <c r="H52" s="44" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I51" s="37" t="n">
+      <c r="I52" s="37" t="n">
         <v>66</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="33" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="33" t="inlineStr">
         <is>
           <t>onboarding.service</t>
         </is>
       </c>
-      <c r="B52" s="32" t="inlineStr">
+      <c r="B53" s="32" t="inlineStr">
         <is>
           <t>OnboardingService</t>
         </is>
       </c>
-      <c r="C52" s="34" t="n">
+      <c r="C53" s="34" t="n">
         <v>99</v>
       </c>
-      <c r="D52" s="34" t="n">
+      <c r="D53" s="34" t="n">
         <v>99</v>
       </c>
-      <c r="E52" s="45" t="inlineStr">
+      <c r="E53" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F52" s="34" t="n">
+      <c r="F53" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="G52" s="34" t="n">
+      <c r="G53" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="H52" s="47" t="inlineStr">
+      <c r="H53" s="47" t="inlineStr">
         <is>
           <t>75.0%</t>
         </is>
       </c>
-      <c r="I52" s="34" t="n">
+      <c r="I53" s="34" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="36" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="36" t="inlineStr">
         <is>
           <t>onboarding.service</t>
         </is>
       </c>
-      <c r="B53" s="35" t="inlineStr">
+      <c r="B54" s="35" t="inlineStr">
         <is>
           <t>TranscriptAnalysisService</t>
         </is>
       </c>
-      <c r="C53" s="37" t="n">
+      <c r="C54" s="37" t="n">
         <v>95</v>
       </c>
-      <c r="D53" s="37" t="n">
+      <c r="D54" s="37" t="n">
         <v>100</v>
       </c>
-      <c r="E53" s="45" t="inlineStr">
+      <c r="E54" s="45" t="inlineStr">
         <is>
           <t>95.0%</t>
         </is>
       </c>
-      <c r="F53" s="37" t="n">
+      <c r="F54" s="37" t="n">
         <v>10</v>
       </c>
-      <c r="G53" s="37" t="n">
+      <c r="G54" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="H53" s="45" t="inlineStr">
+      <c r="H54" s="45" t="inlineStr">
         <is>
           <t>83.3%</t>
         </is>
       </c>
-      <c r="I53" s="37" t="n">
+      <c r="I54" s="37" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="33" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="33" t="inlineStr">
         <is>
           <t>portfolio.controller</t>
         </is>
       </c>
-      <c r="B54" s="32" t="inlineStr">
+      <c r="B55" s="32" t="inlineStr">
         <is>
           <t>PortfolioController</t>
         </is>
       </c>
-      <c r="C54" s="34" t="n">
+      <c r="C55" s="34" t="n">
         <v>51</v>
       </c>
-      <c r="D54" s="34" t="n">
+      <c r="D55" s="34" t="n">
         <v>98</v>
       </c>
-      <c r="E54" s="47" t="inlineStr">
+      <c r="E55" s="47" t="inlineStr">
         <is>
           <t>52.0%</t>
         </is>
       </c>
-      <c r="F54" s="34" t="n">
+      <c r="F55" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="G54" s="34" t="n">
+      <c r="G55" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="H54" s="45" t="inlineStr">
+      <c r="H55" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I54" s="34" t="n">
+      <c r="I55" s="34" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="36" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="36" t="inlineStr">
         <is>
           <t>portfolio.controller</t>
         </is>
       </c>
-      <c r="B55" s="35" t="inlineStr">
+      <c r="B56" s="35" t="inlineStr">
         <is>
           <t>PublicPortfolioController</t>
         </is>
       </c>
-      <c r="C55" s="37" t="n">
+      <c r="C56" s="37" t="n">
         <v>47</v>
       </c>
-      <c r="D55" s="37" t="n">
+      <c r="D56" s="37" t="n">
         <v>53</v>
       </c>
-      <c r="E55" s="45" t="inlineStr">
+      <c r="E56" s="45" t="inlineStr">
         <is>
           <t>88.7%</t>
         </is>
       </c>
-      <c r="F55" s="37" t="n">
+      <c r="F56" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="G55" s="37" t="n">
+      <c r="G56" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="48" t="inlineStr">
+      <c r="H56" s="48" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I55" s="37" t="n">
+      <c r="I56" s="37" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="33" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="33" t="inlineStr">
         <is>
           <t>portfolio.dto</t>
         </is>
       </c>
-      <c r="B56" s="32" t="inlineStr">
+      <c r="B57" s="32" t="inlineStr">
         <is>
           <t>OwnerInfoDTO</t>
         </is>
       </c>
-      <c r="C56" s="34" t="n">
+      <c r="C57" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="D56" s="34" t="n">
+      <c r="D57" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="E56" s="45" t="inlineStr">
+      <c r="E57" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F56" s="34" t="n">
+      <c r="F57" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G56" s="34" t="n">
+      <c r="G57" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="46" t="inlineStr">
+      <c r="H57" s="46" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I56" s="34" t="n">
+      <c r="I57" s="34" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="36" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="36" t="inlineStr">
         <is>
           <t>portfolio.entity</t>
         </is>
       </c>
-      <c r="B57" s="35" t="inlineStr">
+      <c r="B58" s="35" t="inlineStr">
         <is>
           <t>ProjectRepository</t>
         </is>
       </c>
-      <c r="C57" s="37" t="n">
+      <c r="C58" s="37" t="n">
         <v>7</v>
       </c>
-      <c r="D57" s="37" t="n">
+      <c r="D58" s="37" t="n">
         <v>7</v>
       </c>
-      <c r="E57" s="45" t="inlineStr">
+      <c r="E58" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F57" s="37" t="n">
+      <c r="F58" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="G57" s="37" t="n">
+      <c r="G58" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="48" t="inlineStr">
+      <c r="H58" s="48" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I57" s="37" t="n">
+      <c r="I58" s="37" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="33" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="33" t="inlineStr">
         <is>
           <t>portfolio.service</t>
         </is>
       </c>
-      <c r="B58" s="32" t="inlineStr">
+      <c r="B59" s="32" t="inlineStr">
         <is>
           <t>PortfolioService</t>
         </is>
       </c>
-      <c r="C58" s="34" t="n">
+      <c r="C59" s="34" t="n">
         <v>409</v>
       </c>
-      <c r="D58" s="34" t="n">
+      <c r="D59" s="34" t="n">
         <v>431</v>
       </c>
-      <c r="E58" s="45" t="inlineStr">
+      <c r="E59" s="45" t="inlineStr">
         <is>
           <t>94.9%</t>
         </is>
       </c>
-      <c r="F58" s="34" t="n">
+      <c r="F59" s="34" t="n">
         <v>31</v>
       </c>
-      <c r="G58" s="34" t="n">
+      <c r="G59" s="34" t="n">
         <v>40</v>
       </c>
-      <c r="H58" s="47" t="inlineStr">
+      <c r="H59" s="47" t="inlineStr">
         <is>
           <t>77.5%</t>
         </is>
       </c>
-      <c r="I58" s="34" t="n">
+      <c r="I59" s="34" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="36" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="36" t="inlineStr">
         <is>
           <t>profile.controller</t>
         </is>
       </c>
-      <c r="B59" s="35" t="inlineStr">
+      <c r="B60" s="35" t="inlineStr">
         <is>
           <t>ProfileController</t>
         </is>
       </c>
-      <c r="C59" s="37" t="n">
+      <c r="C60" s="37" t="n">
         <v>148</v>
       </c>
-      <c r="D59" s="37" t="n">
+      <c r="D60" s="37" t="n">
         <v>149</v>
       </c>
-      <c r="E59" s="45" t="inlineStr">
+      <c r="E60" s="45" t="inlineStr">
         <is>
           <t>99.3%</t>
         </is>
       </c>
-      <c r="F59" s="37" t="n">
+      <c r="F60" s="37" t="n">
         <v>9</v>
       </c>
-      <c r="G59" s="37" t="n">
+      <c r="G60" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="H59" s="47" t="inlineStr">
+      <c r="H60" s="47" t="inlineStr">
         <is>
           <t>75.0%</t>
         </is>
       </c>
-      <c r="I59" s="37" t="n">
+      <c r="I60" s="37" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="33" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="33" t="inlineStr">
         <is>
           <t>profile.service</t>
         </is>
       </c>
-      <c r="B60" s="32" t="inlineStr">
+      <c r="B61" s="32" t="inlineStr">
         <is>
           <t>ProfileService</t>
         </is>
       </c>
-      <c r="C60" s="34" t="n">
+      <c r="C61" s="34" t="n">
         <v>125</v>
       </c>
-      <c r="D60" s="34" t="n">
+      <c r="D61" s="34" t="n">
         <v>125</v>
       </c>
-      <c r="E60" s="45" t="inlineStr">
+      <c r="E61" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F60" s="34" t="n">
+      <c r="F61" s="34" t="n">
         <v>18</v>
       </c>
-      <c r="G60" s="34" t="n">
+      <c r="G61" s="34" t="n">
         <v>18</v>
       </c>
-      <c r="H60" s="45" t="inlineStr">
+      <c r="H61" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I60" s="34" t="n">
+      <c r="I61" s="34" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="36" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="36" t="inlineStr">
         <is>
           <t>roadmap.controller</t>
         </is>
       </c>
-      <c r="B61" s="35" t="inlineStr">
+      <c r="B62" s="35" t="inlineStr">
         <is>
           <t>RoadmapController</t>
         </is>
       </c>
-      <c r="C61" s="37" t="n">
+      <c r="C62" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D61" s="37" t="n">
+      <c r="D62" s="37" t="n">
         <v>53</v>
       </c>
-      <c r="E61" s="44" t="inlineStr">
+      <c r="E62" s="44" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F61" s="37" t="n">
+      <c r="F62" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="G61" s="37" t="n">
+      <c r="G62" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="48" t="inlineStr">
+      <c r="H62" s="48" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I61" s="37" t="n">
+      <c r="I62" s="37" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="33" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="33" t="inlineStr">
         <is>
           <t>roadmap.controller</t>
         </is>
       </c>
-      <c r="B62" s="32" t="inlineStr">
+      <c r="B63" s="32" t="inlineStr">
         <is>
           <t>RoadmapPageController</t>
         </is>
       </c>
-      <c r="C62" s="34" t="n">
+      <c r="C63" s="34" t="n">
         <v>242</v>
       </c>
-      <c r="D62" s="34" t="n">
+      <c r="D63" s="34" t="n">
         <v>259</v>
       </c>
-      <c r="E62" s="45" t="inlineStr">
+      <c r="E63" s="45" t="inlineStr">
         <is>
           <t>93.4%</t>
         </is>
       </c>
-      <c r="F62" s="34" t="n">
+      <c r="F63" s="34" t="n">
         <v>26</v>
       </c>
-      <c r="G62" s="34" t="n">
+      <c r="G63" s="34" t="n">
         <v>34</v>
       </c>
-      <c r="H62" s="47" t="inlineStr">
+      <c r="H63" s="47" t="inlineStr">
         <is>
           <t>76.5%</t>
         </is>
       </c>
-      <c r="I62" s="34" t="n">
+      <c r="I63" s="34" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="36" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="36" t="inlineStr">
         <is>
           <t>roadmap.controller</t>
         </is>
       </c>
-      <c r="B63" s="35" t="inlineStr">
+      <c r="B64" s="35" t="inlineStr">
         <is>
           <t>SkillGapController</t>
         </is>
       </c>
-      <c r="C63" s="37" t="n">
+      <c r="C64" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D63" s="37" t="n">
+      <c r="D64" s="37" t="n">
         <v>66</v>
       </c>
-      <c r="E63" s="44" t="inlineStr">
+      <c r="E64" s="44" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F63" s="37" t="n">
+      <c r="F64" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="G63" s="37" t="n">
+      <c r="G64" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="H63" s="44" t="inlineStr">
+      <c r="H64" s="44" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I63" s="37" t="n">
+      <c r="I64" s="37" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="33" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="33" t="inlineStr">
         <is>
           <t>roadmap.controller</t>
         </is>
       </c>
-      <c r="B64" s="32" t="inlineStr">
+      <c r="B65" s="32" t="inlineStr">
         <is>
           <t>SkillGapPageController</t>
         </is>
       </c>
-      <c r="C64" s="34" t="n">
+      <c r="C65" s="34" t="n">
         <v>241</v>
       </c>
-      <c r="D64" s="34" t="n">
+      <c r="D65" s="34" t="n">
         <v>249</v>
       </c>
-      <c r="E64" s="45" t="inlineStr">
+      <c r="E65" s="45" t="inlineStr">
         <is>
           <t>96.8%</t>
         </is>
       </c>
-      <c r="F64" s="34" t="n">
+      <c r="F65" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="G64" s="34" t="n">
+      <c r="G65" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="H64" s="47" t="inlineStr">
+      <c r="H65" s="47" t="inlineStr">
         <is>
           <t>75.0%</t>
         </is>
       </c>
-      <c r="I64" s="34" t="n">
+      <c r="I65" s="34" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="36" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="36" t="inlineStr">
         <is>
           <t>roadmap.dto</t>
         </is>
       </c>
-      <c r="B65" s="35" t="inlineStr">
+      <c r="B66" s="35" t="inlineStr">
         <is>
           <t>RoadmapTemplateDTO</t>
         </is>
       </c>
-      <c r="C65" s="37" t="n">
+      <c r="C66" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="D65" s="37" t="n">
+      <c r="D66" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="E65" s="45" t="inlineStr">
+      <c r="E66" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F65" s="37" t="n">
+      <c r="F66" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="G65" s="37" t="n">
+      <c r="G66" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="H65" s="48" t="inlineStr">
+      <c r="H66" s="48" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I65" s="37" t="n">
+      <c r="I66" s="37" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="33" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="33" t="inlineStr">
         <is>
           <t>roadmap.dto</t>
         </is>
       </c>
-      <c r="B66" s="32" t="inlineStr">
+      <c r="B67" s="32" t="inlineStr">
         <is>
           <t>SkillGapReportDTO</t>
         </is>
       </c>
-      <c r="C66" s="34" t="n">
+      <c r="C67" s="34" t="n">
         <v>34</v>
       </c>
-      <c r="D66" s="34" t="n">
+      <c r="D67" s="34" t="n">
         <v>34</v>
       </c>
-      <c r="E66" s="45" t="inlineStr">
+      <c r="E67" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F66" s="34" t="n">
+      <c r="F67" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G66" s="34" t="n">
+      <c r="G67" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H66" s="46" t="inlineStr">
+      <c r="H67" s="46" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I66" s="34" t="n">
+      <c r="I67" s="34" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="36" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="36" t="inlineStr">
         <is>
           <t>roadmap.entity</t>
         </is>
       </c>
-      <c r="B67" s="35" t="inlineStr">
+      <c r="B68" s="35" t="inlineStr">
         <is>
           <t>ProgressStatus</t>
         </is>
       </c>
-      <c r="C67" s="37" t="n">
+      <c r="C68" s="37" t="n">
         <v>21</v>
       </c>
-      <c r="D67" s="37" t="n">
+      <c r="D68" s="37" t="n">
         <v>21</v>
       </c>
-      <c r="E67" s="45" t="inlineStr">
+      <c r="E68" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F67" s="37" t="n">
+      <c r="F68" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="G67" s="37" t="n">
+      <c r="G68" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="H67" s="48" t="inlineStr">
+      <c r="H68" s="48" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I67" s="37" t="n">
+      <c r="I68" s="37" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="33" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="33" t="inlineStr">
         <is>
           <t>roadmap.service</t>
         </is>
       </c>
-      <c r="B68" s="32" t="inlineStr">
+      <c r="B69" s="32" t="inlineStr">
         <is>
           <t>PdfService</t>
         </is>
       </c>
-      <c r="C68" s="34" t="n">
+      <c r="C69" s="34" t="n">
         <v>368</v>
       </c>
-      <c r="D68" s="34" t="n">
+      <c r="D69" s="34" t="n">
         <v>384</v>
       </c>
-      <c r="E68" s="45" t="inlineStr">
+      <c r="E69" s="45" t="inlineStr">
         <is>
           <t>95.8%</t>
         </is>
       </c>
-      <c r="F68" s="34" t="n">
+      <c r="F69" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="G68" s="34" t="n">
+      <c r="G69" s="34" t="n">
         <v>14</v>
       </c>
-      <c r="H68" s="45" t="inlineStr">
+      <c r="H69" s="45" t="inlineStr">
         <is>
           <t>85.7%</t>
         </is>
       </c>
-      <c r="I68" s="34" t="n">
+      <c r="I69" s="34" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="36" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="36" t="inlineStr">
         <is>
           <t>roadmap.service</t>
         </is>
       </c>
-      <c r="B69" s="35" t="inlineStr">
+      <c r="B70" s="35" t="inlineStr">
         <is>
           <t>ProgressService</t>
         </is>
       </c>
-      <c r="C69" s="37" t="n">
+      <c r="C70" s="37" t="n">
         <v>97</v>
       </c>
-      <c r="D69" s="37" t="n">
+      <c r="D70" s="37" t="n">
         <v>97</v>
       </c>
-      <c r="E69" s="45" t="inlineStr">
+      <c r="E70" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F69" s="37" t="n">
+      <c r="F70" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="G69" s="37" t="n">
+      <c r="G70" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="H69" s="45" t="inlineStr">
+      <c r="H70" s="45" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I69" s="37" t="n">
+      <c r="I70" s="37" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="33" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="33" t="inlineStr">
         <is>
           <t>roadmap.service</t>
         </is>
       </c>
-      <c r="B70" s="32" t="inlineStr">
+      <c r="B71" s="32" t="inlineStr">
         <is>
           <t>RoadmapService</t>
         </is>
       </c>
-      <c r="C70" s="34" t="n">
+      <c r="C71" s="34" t="n">
         <v>439</v>
       </c>
-      <c r="D70" s="34" t="n">
+      <c r="D71" s="34" t="n">
         <v>445</v>
       </c>
-      <c r="E70" s="45" t="inlineStr">
+      <c r="E71" s="45" t="inlineStr">
         <is>
           <t>98.7%</t>
         </is>
       </c>
-      <c r="F70" s="34" t="n">
+      <c r="F71" s="34" t="n">
         <v>41</v>
       </c>
-      <c r="G70" s="34" t="n">
+      <c r="G71" s="34" t="n">
         <v>42</v>
       </c>
-      <c r="H70" s="45" t="inlineStr">
+      <c r="H71" s="45" t="inlineStr">
         <is>
           <t>97.6%</t>
         </is>
       </c>
-      <c r="I70" s="34" t="n">
+      <c r="I71" s="34" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="36" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="36" t="inlineStr">
         <is>
           <t>roadmap.service</t>
         </is>
       </c>
-      <c r="B71" s="35" t="inlineStr">
+      <c r="B72" s="35" t="inlineStr">
         <is>
           <t>SkillGapService</t>
         </is>
       </c>
-      <c r="C71" s="37" t="n">
+      <c r="C72" s="37" t="n">
         <v>404</v>
       </c>
-      <c r="D71" s="37" t="n">
+      <c r="D72" s="37" t="n">
         <v>418</v>
       </c>
-      <c r="E71" s="45" t="inlineStr">
+      <c r="E72" s="45" t="inlineStr">
         <is>
           <t>96.7%</t>
         </is>
       </c>
-      <c r="F71" s="37" t="n">
+      <c r="F72" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="G71" s="37" t="n">
+      <c r="G72" s="37" t="n">
         <v>8</v>
       </c>
-      <c r="H71" s="47" t="inlineStr">
+      <c r="H72" s="47" t="inlineStr">
         <is>
           <t>75.0%</t>
         </is>
       </c>
-      <c r="I71" s="37" t="n">
+      <c r="I72" s="37" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="31" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
         <is>
           <t>TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="B73" s="49" t="n"/>
-      <c r="C73" s="31" t="n">
+      <c r="B74" s="49" t="n"/>
+      <c r="C74" s="31" t="n">
         <v>5798</v>
       </c>
-      <c r="D73" s="31" t="n">
+      <c r="D74" s="31" t="n">
         <v>7622</v>
       </c>
-      <c r="E73" s="50" t="inlineStr">
+      <c r="E74" s="50" t="inlineStr">
         <is>
           <t>76.1%</t>
         </is>
       </c>
-      <c r="F73" s="31" t="n">
+      <c r="F74" s="31" t="n">
         <v>369</v>
       </c>
-      <c r="G73" s="31" t="n">
+      <c r="G74" s="31" t="n">
         <v>547</v>
       </c>
-      <c r="H73" s="50" t="inlineStr">
+      <c r="H74" s="50" t="inlineStr">
         <is>
           <t>67.5%</t>
         </is>
       </c>
-      <c r="I73" s="31" t="n">
+      <c r="I74" s="31" t="n">
         <v>390</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9240,7 +9268,7 @@
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="54" t="inlineStr">
         <is>
-          <t>KỲ BÁO CÁO — từ 22/07/2026, 72 commit của 3 thành viên, 399 trường hợp kiểm thử tự động</t>
+          <t>KỲ BÁO CÁO — từ 22/07/2026, 74 commit của 3 thành viên, 399 trường hợp kiểm thử tự động</t>
         </is>
       </c>
     </row>
@@ -9285,7 +9313,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E8" s="5" t="inlineStr"/>
       <c r="F8" s="5" t="inlineStr"/>
